--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_10.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_10.xlsx
@@ -618,83 +618,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01907</t>
+          <t>X ≈ -0.01906</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.428915869170837</v>
+        <v>5.4641300633537</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-10.19107598667802</v>
+        <v>-7.309844614503561</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7971429939356938</v>
+        <v>3.5909960065134</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.33774126327402</v>
+        <v>-9.587866890465321</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.70529504124519</v>
+        <v>-16.15572414135791</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>24.77501535724201</v>
+        <v>24.84028999612825</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.57654229323227</v>
+        <v>11.64266126930998</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.137451393413272</v>
+        <v>-1.07104776057777</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.096295193965844</v>
+        <v>-1.029899767249972</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.090788312923344</v>
+        <v>-8.0234921462458</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>4.631634427529349</v>
+        <v>4.698714639315646</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.354632088828268</v>
+        <v>4.422073925674951</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.235164166263637</v>
+        <v>3.303945304163626</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-3.216052364240461</v>
+        <v>-3.14699692002408</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-3.873675614030894</v>
+        <v>-3.803815394285856</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.953622057072771</v>
+        <v>3.022853709798227</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.820851020749956</v>
+        <v>2.890278311038529</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.76057927831917</v>
+        <v>-9.691016493847513</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.933566740956429</v>
+        <v>3.002945754065657</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-3.121270927235287</v>
+        <v>-3.052078049009921</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-3.664874897493739</v>
+        <v>-3.595006706113914</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.741909047407354</v>
+        <v>-3.671909047909914</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-3.468368242137934</v>
+        <v>-3.398645585288804</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.545321637428323</v>
+        <v>-3.475467289719624</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8661604695055729</v>
+        <v>0.8992142106376804</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5337508965647686</v>
+        <v>0.5672293843829337</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.136811802637389</v>
+        <v>8.17431758610406</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.911721888007406</v>
+        <v>2.94846112459205</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.58766082980871</v>
+        <v>11.65659454218843</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.73445794091802</v>
+        <v>2.799587741383689</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.488399269371072</v>
+        <v>6.554484455906909</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.213370996406759</v>
+        <v>6.279813607414589</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.256737845897497</v>
+        <v>6.323169837942366</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.9621501585048549</v>
+        <v>1.029488271259041</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.763337194598272</v>
+        <v>5.830420202334182</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.9576947364916393</v>
+        <v>1.02511930779373</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1627403209465115</v>
+        <v>-0.09397517201595917</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.383610615432282</v>
+        <v>-0.3145475130519202</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.040363914926445</v>
+        <v>-0.9704968909294678</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-4.98179313900657</v>
+        <v>-4.912586410168359</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.5811009726778877</v>
+        <v>-0.5116839258838368</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.223162314564114</v>
+        <v>-5.15359154140247</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.009009560470922</v>
+        <v>-4.939646161014196</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.82371242573808</v>
+        <v>-4.754523115422451</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.367835832592988</v>
+        <v>-5.297970340829849</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.988102222285008</v>
+        <v>-9.918107348017458</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.172386312845106</v>
+        <v>-5.102664553102805</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744264047</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.446205946798997</v>
+        <v>0.8991424749272738</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.84403911783167</v>
+        <v>5.083784927594102</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.14719649003545</v>
+        <v>8.173673382855448</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.44139402590867</v>
+        <v>11.98689677643428</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6113582082774087</v>
+        <v>2.614375394205801</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.7968258832101398</v>
+        <v>2.79937599693752</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-9.446848968979054</v>
+        <v>-7.012154755479671</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2490421244970804</v>
+        <v>1.755971615822105</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-9.68810386689939</v>
+        <v>-7.25161698145515</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.977683578784756</v>
+        <v>1.029429458859603</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.447977547300759</v>
+        <v>-7.752514811095814</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.76124967054465</v>
+        <v>1.025064739622628</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.641718671960369</v>
+        <v>4.436313770770184</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.91659451955373</v>
+        <v>13.2804501218578</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.514719872313755</v>
+        <v>8.095616948448956</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.390549766077108</v>
+        <v>-0.378015523410518</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.524992792088959</v>
+        <v>-0.511670282410158</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>6.876062388440346</v>
+        <v>8.45804420978989</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.339205764121267</v>
+        <v>4.137550931824741</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-2.229394340093634</v>
+        <v>-0.2145181930652171</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.984816995141493</v>
+        <v>3.784711381394175</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-2.849514615153844</v>
+        <v>-0.8326476830644367</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-2.57575448483513</v>
+        <v>-0.5585725732944553</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.652464494569763</v>
+        <v>-0.6345581988115612</v>
       </c>
     </row>
     <row r="9">
@@ -868,79 +868,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-17.16828251578595</v>
+        <v>-15.6880519395819</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-9.872941697879703</v>
+        <v>-8.089160472678827</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.592194137676763</v>
+        <v>-1.622826559001012</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.166271146151182</v>
+        <v>5.594313282135538</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-10.31396853117472</v>
+        <v>-14.64504474546028</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-6.306846506904485</v>
+        <v>-10.46625398079904</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.25138939166392</v>
+        <v>-5.02202201778001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.529623554536137</v>
+        <v>-5.300450197179615</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3396038244609016</v>
+        <v>-1.278623565732872</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.26021802073172</v>
+        <v>-6.031231494837058</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.988294222633016</v>
+        <v>-1.7759019627456</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.267979788715131</v>
+        <v>-2.054571479861536</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.276519217206996</v>
+        <v>0.8119569061182759</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.778152534859501</v>
+        <v>-3.396271925886694</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>5.235945383709044</v>
+        <v>3.924990463444125</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>5.831096081262892</v>
+        <v>4.519072807958793</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>9.537072266084948</v>
+        <v>8.378352388034571</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>5.596189394363677</v>
+        <v>4.283685748971237</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.973416256686235</v>
+        <v>0.5066643629044165</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>13.68516620193532</v>
+        <v>12.67876177640319</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>9.304057445839128</v>
+        <v>8.144288257571354</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>13.07479854270547</v>
+        <v>12.06853878471801</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.663485147122479</v>
+        <v>4.349015612801466</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.589293747188485</v>
+        <v>4.274532710281285</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>32</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-9.858622149520457</v>
+        <v>-9.825655860443028</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.19162669070014</v>
+        <v>-10.16154070478629</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.518057812541315</v>
+        <v>-8.488260173655895</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-6.124516749302536</v>
+        <v>-6.092361704733648</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.382567356664282</v>
+        <v>-3.319243730035382</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.413892494247591</v>
+        <v>-9.351621941907453</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-16.40292562409343</v>
+        <v>-16.33700358519732</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.137348601601587</v>
+        <v>-1.070964071356528</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.317125403394229</v>
+        <v>-7.250783915019795</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.245057732733038</v>
+        <v>1.312383789926955</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.518638114690759</v>
+        <v>1.585688645589265</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.872772006250713</v>
+        <v>-1.805371755784236</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.994110303497145</v>
+        <v>-2.925367581056058</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1005764355249781</v>
+        <v>-0.0315216591114762</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.475400615199597</v>
+        <v>5.545281457340515</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.281174727205503</v>
+        <v>-3.211971406645461</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-6.534182544470383</v>
+        <v>-6.464788189777394</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-6.64084392015738</v>
+        <v>-6.571282717215297</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.427075244160584</v>
+        <v>-6.357719995732957</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.121213117304933</v>
+        <v>-3.052025317448582</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.5427050786441541</v>
+        <v>-0.4728372168787089</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.6187757148437996</v>
+        <v>-0.5487759889060229</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.779732477603311</v>
+        <v>2.849456197015812</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.4203216374269019</v>
+        <v>-0.3504672897210455</v>
       </c>
     </row>
     <row r="11">
@@ -1032,79 +1032,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.150192465502158</v>
+        <v>5.896669320884484</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.497947363539673</v>
+        <v>1.336927280301246</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.066738119416378</v>
+        <v>-0.09298927235197851</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.678025668346585</v>
+        <v>5.544786670118334</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>10.79947766696576</v>
+        <v>11.56181030708025</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.664821504685136</v>
+        <v>7.514269938488425</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.22309964474058</v>
+        <v>10.97928352124416</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8668490074822728</v>
+        <v>0.1199707158386332</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.988895661885124</v>
+        <v>-4.073445578292876</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.924585024604333</v>
+        <v>-4.844178710193191</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-9.983388579434319</v>
+        <v>-10.92982674608375</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.93336923037343</v>
+        <v>-4.85223492026774</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-9.222320140343108</v>
+        <v>-10.21376606091385</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-9.446187256026192</v>
+        <v>-10.43766272650421</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-10.10586665580851</v>
+        <v>-11.09686568161558</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-7.346836181657501</v>
+        <v>-8.384944227190893</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.975426945377933</v>
+        <v>-2.152123740647028</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.089433638108915</v>
+        <v>-0.1336512736200817</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.305572486084543</v>
+        <v>0.08187369051708515</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.49263960117878</v>
+        <v>0.2683604762348963</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.950463199750601</v>
+        <v>-0.2735464332390407</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>3.047405363994329</v>
+        <v>1.77689818816971</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.323018071256705</v>
+        <v>2.051811968367694</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>5.422069666920926</v>
+        <v>4.104319944323407</v>
       </c>
     </row>
     <row r="12">
@@ -1114,79 +1114,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.731457511162439</v>
+        <v>-2.788116438295916</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.958484872656911</v>
+        <v>-3.147134836498601</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.760083219884208</v>
+        <v>-9.949104972623061</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.256601770693301</v>
+        <v>-8.524529279968256</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.397484952017784</v>
+        <v>-3.324920153617498</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.025431533013005</v>
+        <v>1.192458820794435</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.240878221943028</v>
+        <v>0.4080917781269449</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.511722955234511</v>
+        <v>-8.528730290540146</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.9983356052374361</v>
+        <v>2.328888368364417</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.02711825103777</v>
+        <v>-4.952139183957527</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.63049326529508</v>
+        <v>-0.3448401955468725</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.032903815309197</v>
+        <v>-4.958411950937112</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.425088477485936</v>
+        <v>6.897108808118411</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.081820339645418</v>
+        <v>4.508401319340081</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.95722576023514</v>
+        <v>-2.66818092594287</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.016277112812638</v>
+        <v>4.443783625499094</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.881555286467794</v>
+        <v>4.309651279192984</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.203245433924657</v>
+        <v>-0.1376243925729099</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.0124818041152821</v>
+        <v>0.08231398236061693</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.925808449796222</v>
+        <v>-1.89654036334074</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.46904488801799</v>
+        <v>-2.451986284644946</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.672051485447838</v>
+        <v>-3.400221812329306</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.39887783517932</v>
+        <v>-3.126945356551964</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-8.731491850193343</v>
+        <v>-7.551554246241857</v>
       </c>
     </row>
     <row r="13">
@@ -1199,240 +1199,240 @@
         <v>62</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.500435830602157</v>
+        <v>2.67240364786646</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.367464262486941</v>
+        <v>6.40725852143445</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.310677455958874</v>
+        <v>3.349177588300861</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.799177619625048</v>
+        <v>5.841113520561493</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.433213120444044</v>
+        <v>5.502836899808585</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.43935579144619</v>
+        <v>10.50892308167801</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.451065063037383</v>
+        <v>6.518308333451394</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.17004292550331</v>
+        <v>6.237654050176737</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2106864319218147</v>
+        <v>-0.1431180072839453</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9956572826766532</v>
+        <v>-0.9271354600577908</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.53975991639372</v>
+        <v>-5.471538044955231</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9999842818290503</v>
+        <v>-0.9313685012410247</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.138047555717918</v>
+        <v>-2.068064619287625</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.970763851959866</v>
+        <v>-3.900480472790768</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.64308530480988</v>
+        <v>-4.571974394001415</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.430162808934142</v>
+        <v>-2.35970390220028</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-5.786806104698684</v>
+        <v>-5.716149774223787</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.284276930525976</v>
+        <v>-4.215131840851761</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.715574144666355</v>
+        <v>-5.608870456147031</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.530429031016439</v>
+        <v>-5.419726549183281</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.463185691997083</v>
+        <v>-4.36101101089055</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-3.540219949462077</v>
+        <v>-4.437863892872613</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.654356566372243</v>
+        <v>-1.584636688897987</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.495000943218628</v>
+        <v>1.564855290926268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008849</t>
+          <t>X ≈ -0.008848</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>64</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5444510746103077</v>
+        <v>-1.349498053548082</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6750927026071381</v>
+        <v>-0.1329495958064228</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7974315595987918</v>
+        <v>-0.03197990483372593</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.193222594947706</v>
+        <v>3.232495801649563</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.83037922921315</v>
+        <v>2.897829017797804</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.570435051789943</v>
+        <v>4.637299892620348</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.358212941882378</v>
+        <v>5.424276975714839</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.417637366616205</v>
+        <v>0.4840325822946028</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.015605277199342</v>
+        <v>2.082003288055404</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.246114681398161</v>
+        <v>1.313446309250324</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.03661737942694288</v>
+        <v>0.03043312205011972</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7.471058036791021</v>
+        <v>7.538511543959302</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.678571026743136</v>
+        <v>1.747348741134893</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.016610677283417</v>
+        <v>3.085695142032264</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.478521673350009</v>
+        <v>5.548422330539019</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1636608102336439</v>
+        <v>-0.09442245972381613</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>2.822232992578662</v>
+        <v>2.891679803766976</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.4022911049748501</v>
+        <v>-0.3328323093928702</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.3734133898217</v>
+        <v>1.443673053954321</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.120925531248275</v>
+        <v>3.192220838959614</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.579313557400489</v>
+        <v>2.650895122983719</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>4.065704007323212</v>
+        <v>4.137051831999408</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.779673521448508</v>
+        <v>2.849394267978624</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.704678362573098</v>
+        <v>2.77453271028002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007572</t>
+          <t>X ≈ -0.00757</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.190209311395733</v>
+        <v>-3.123435808485631</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8399575086687534</v>
+        <v>0.8670552075449365</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6236227095468578</v>
+        <v>-0.5799530808699345</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.119455812456692</v>
+        <v>4.113328086131347</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.844694141058966</v>
+        <v>4.857905703021572</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.22903020793072</v>
+        <v>7.211401133376313</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.255987334716075</v>
+        <v>4.270925596476388</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.875450505951434</v>
+        <v>2.908880264700251</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.390301442099016</v>
+        <v>8.363362930801628</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.601839193625999</v>
+        <v>7.586622891120925</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.690463711415958</v>
+        <v>5.697818754331593</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.414756611328265</v>
+        <v>5.421543034210899</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.366012133320716</v>
+        <v>5.374962034659809</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.046836917429722</v>
+        <v>4.070100225312501</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.566188652081074</v>
+        <v>5.575384062322847</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.786119312076096</v>
+        <v>1.836844406184838</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.748585634107997</v>
+        <v>2.788192150851351</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>7.02982228301299</v>
+        <v>7.025189464956256</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>6.153039332243431</v>
+        <v>6.159387111532503</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>6.998354124988467</v>
+        <v>6.351577385252881</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>8.647830318508973</v>
+        <v>7.978761756450474</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>8.574262899384472</v>
+        <v>7.902554799849646</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.212511498074782</v>
+        <v>4.920852884604471</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>7.237645395539879</v>
+        <v>6.578880536367585</v>
       </c>
     </row>
     <row r="16">
@@ -1445,76 +1445,76 @@
         <v>105</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5344201161108657</v>
+        <v>0.5679272461349214</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1969190989538703</v>
+        <v>0.2306403998322253</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.263710887746008</v>
+        <v>-1.229969080776719</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.03446555143011</v>
+        <v>-0.998603736573628</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.556131268777115</v>
+        <v>-7.027418908888961</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.420445883502346</v>
+        <v>-5.88358311938088</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.354917789888745</v>
+        <v>-3.82407974110518</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.094390661223137</v>
+        <v>-4.111978341192</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7404573392372669</v>
+        <v>0.2661541971387464</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.613472234458833</v>
+        <v>6.13068424468922</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.839279742145763</v>
+        <v>7.356811167824453</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.663336175258166</v>
+        <v>5.728679558212178</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.343854929815642</v>
+        <v>8.409613497526998</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.274891474327355</v>
+        <v>5.342022239009793</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.471425605587562</v>
+        <v>7.538645329601302</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>8.068475028818732</v>
+        <v>8.134873026639838</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>9.840037787868937</v>
+        <v>9.905982029789186</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>8.783798756502279</v>
+        <v>8.853455666480258</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>7.096972110246433</v>
+        <v>7.168977402728153</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>7.283650423663033</v>
+        <v>7.358270714554422</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7.695203938253506</v>
+        <v>7.770783831478319</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>5.718004701187347</v>
+        <v>5.790175965307533</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>6.944700017317821</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>4.014202172097121</v>
+        <v>4.084056519803973</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>124</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.153759001144621</v>
+        <v>-4.125468258878215</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.68954557732296</v>
+        <v>-3.660160961143532</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.160528134254598</v>
+        <v>-5.131276178723688</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.021219342040716</v>
+        <v>-3.438094146615086</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.6229012668675438</v>
+        <v>0.2360969766186969</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.424054570787376</v>
+        <v>2.04382452642696</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.919681163360629</v>
+        <v>-2.764582688083856</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.421659835822204</v>
+        <v>3.031290425184594</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.09363969201192646</v>
+        <v>-0.9428718442290744</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.06109574561584452</v>
+        <v>-0.9219841408091298</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.016713853046134</v>
+        <v>0.6210142798883282</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.67415446633035</v>
+        <v>-2.069733716212383</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.225411094657424</v>
+        <v>1.293515204662214</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.005389341678629</v>
+        <v>1.073911862820133</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.763219547211953</v>
+        <v>2.831935954028687</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.358688063564585</v>
+        <v>3.426573015626538</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.614834877624489</v>
+        <v>1.68351591175275</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.315561994473228</v>
+        <v>2.38520705364639</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.142630294514348</v>
+        <v>4.213749642753285</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.718173702783865</v>
+        <v>2.789849079476184</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.176558577340707</v>
+        <v>2.248510405979083</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.132415741749831</v>
+        <v>6.20492250908611</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.600893791718157</v>
+        <v>5.672945608664932</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>4.720807394831162</v>
+        <v>4.79066174253844</v>
       </c>
     </row>
     <row r="18">
@@ -1606,79 +1606,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.472548589222214</v>
+        <v>2.494642366807945</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.485001087968442</v>
+        <v>1.512064423135804</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6208820845174401</v>
+        <v>-0.5788119130269891</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6849981860849397</v>
+        <v>-0.644951351402888</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2494232990154259</v>
+        <v>0.3130106587157044</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.496346520102918</v>
+        <v>-0.7921724709373592</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6209599698577009</v>
+        <v>-0.9203895870595318</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.202424063658164</v>
+        <v>-2.494326642988995</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.443381564511327</v>
+        <v>0.1366386327681184</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.286261729111381</v>
+        <v>-2.206802187181218</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.315191801200463</v>
+        <v>-3.227941491779085</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.20303616134229</v>
+        <v>-6.095689059857122</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-7.333603738944127</v>
+        <v>-7.216051668933297</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.297522090190206</v>
+        <v>-4.201028688089956</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.96117607346153</v>
+        <v>-4.859071329568962</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-5.670645101566507</v>
+        <v>-5.563579646186689</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-5.807130604973516</v>
+        <v>-5.699403307470845</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.912754612721308</v>
+        <v>-5.806110689299778</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.389192037249067</v>
+        <v>-4.294778689019552</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.241202653369797</v>
+        <v>-2.16224690118797</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.788360673840359</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.864815699953972</v>
+        <v>-2.781252606121264</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.241202871624019</v>
+        <v>-3.156128542989855</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.625386996904176</v>
+        <v>-1.933259497511827</v>
       </c>
     </row>
     <row r="19">
@@ -1688,79 +1688,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7969138802924931</v>
+        <v>-0.7521704673757341</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.769324225961768</v>
+        <v>1.78845870658278</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.672282927493107</v>
+        <v>4.668735630626493</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.957752372814433</v>
+        <v>3.956185794140502</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6886114952733564</v>
+        <v>0.7463366258073663</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8801995571931158</v>
+        <v>0.9308777141641329</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8670949476279759</v>
+        <v>-0.7955427068117871</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.754289544781017</v>
+        <v>1.802460186656866</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8297326405388219</v>
+        <v>0.8848948913090879</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5341983823057106</v>
+        <v>0.5942000069491584</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6430079133313527</v>
+        <v>-0.5695107008694151</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.013269508479908</v>
+        <v>1.069036484294159</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.056899292352419</v>
+        <v>-1.967380341605683</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8258006095256718</v>
+        <v>-0.7507943517023676</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.006070724914423</v>
+        <v>-0.9278097013482665</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.4067954679081893</v>
+        <v>-0.334745557641476</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.99791880221828</v>
+        <v>-1.908454816398965</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.104051181374388</v>
+        <v>-2.01382519777642</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.399427223743331</v>
+        <v>-1.31860139951808</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.2481401160452705</v>
+        <v>0.309313899036944</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4730992745293321</v>
+        <v>0.2478900585845452</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.6854561858447568</v>
+        <v>0.1720440971753305</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.474794459123224</v>
+        <v>-0.03425042111173582</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.028331346164656</v>
+        <v>-2.513928828181164</v>
       </c>
     </row>
     <row r="20">
@@ -1773,158 +1773,158 @@
         <v>243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.863128037414995</v>
+        <v>-3.829853745096166</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5089269239049727</v>
+        <v>-0.4752539152916313</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9270747346660642</v>
+        <v>0.962429158334551</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.016074060799426</v>
+        <v>-0.9798803433805219</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.019338080183076</v>
+        <v>-2.953665050287398</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3754277746375294</v>
+        <v>-0.3099531716512587</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3234828598276493</v>
+        <v>-0.2570908086777024</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.241014375708673</v>
+        <v>-2.174279123793241</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.790204467930224</v>
+        <v>-1.723498099122722</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.381720756714905</v>
+        <v>-3.312708643330815</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.108772469247661</v>
+        <v>-3.038649001168892</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.852323066243294</v>
+        <v>-5.77676445983019</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.334257757968494</v>
+        <v>-5.255545158307349</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.147178086281478</v>
+        <v>-5.068867413917388</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.574390763458638</v>
+        <v>-4.496236764697933</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.038313277252279</v>
+        <v>-5.957854690722648</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.409809056860354</v>
+        <v>-7.32637183368923</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.926315106700301</v>
+        <v>-7.845383791645162</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-6.475624042534008</v>
+        <v>-6.400190258105987</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.934670781893004</v>
+        <v>-7.861896985643369</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.066348557146192</v>
+        <v>-7.996411935717539</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-6.907735711554139</v>
+        <v>-6.837689995891978</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-6.632960545072009</v>
+        <v>-6.563215283409924</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-6.297379250595625</v>
+        <v>-6.227524902888348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 9.205e-05</t>
+          <t>X ≈ 9.16e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>289</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4145798113403671</v>
+        <v>-0.381305519021538</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.74805079564387</v>
+        <v>-0.7143777870305286</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.537732849883945</v>
+        <v>-2.502378426215458</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.597416880413164</v>
+        <v>-3.56122316299426</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1731725286305661</v>
+        <v>0.2388455585262435</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.743900010981591</v>
+        <v>1.809374613967861</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.06834280342139465</v>
+        <v>-0.001950752271447698</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3484315262467064</v>
+        <v>-0.2816962743312743</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.685535192579998</v>
+        <v>-1.618828823772496</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1936332453180682</v>
+        <v>-0.3266273778372408</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.08055683278337966</v>
+        <v>-0.05256773567531781</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.872300275604445</v>
+        <v>1.736527231393566</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.437350011703373</v>
+        <v>1.299010289982732</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.239832276460085</v>
+        <v>-2.164847595080651</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.864597872557205</v>
+        <v>-1.78960719975295</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9235048076899872</v>
+        <v>-0.8506790310124899</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.5344289142904373</v>
+        <v>0.3957700610474149</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.2625960242962719</v>
+        <v>-0.4010510786857324</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.04647286136437856</v>
+        <v>-0.1842752656311859</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.589532871972246</v>
+        <v>-1.726369333526158</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.094670997233166</v>
+        <v>-1.024734375804513</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-6.360937471560902</v>
+        <v>-6.290891755898741</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.740141543833168</v>
+        <v>-5.670396282171083</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-6.508124405592909</v>
+        <v>-6.438270057885632</v>
       </c>
     </row>
     <row r="22">
@@ -1934,79 +1934,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.807599860212541</v>
+        <v>1.692487154387912</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8531373793994064</v>
+        <v>-0.9756269391718035</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.621707607197088</v>
+        <v>-3.746986127699508</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.64450339819826</v>
+        <v>1.540072355842618</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.378542313779967</v>
+        <v>-1.129057020254308</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.513617197349141</v>
+        <v>-4.608762206660337</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.299797537559066</v>
+        <v>-1.3807058131462</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.242791075051237</v>
+        <v>-2.325586523477739</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.530164515858758</v>
+        <v>-3.617435522069876</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.646211043908686</v>
+        <v>-1.723680816587709</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6216113229269382</v>
+        <v>0.5503832819121328</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.318869295122987</v>
+        <v>-2.39503897742329</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2141602177788542</v>
+        <v>0.148471070534562</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3418690576057486</v>
+        <v>-0.07260891937779945</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6701558370533434</v>
+        <v>-0.7316424200680203</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.53908984830808</v>
+        <v>-2.807752588922604</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.006516875790261</v>
+        <v>-3.27843493702359</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.778166958552241</v>
+        <v>-3.721205466888463</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.562043795620433</v>
+        <v>-5.513077243248667</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.375000000000121</v>
+        <v>-4.456219291844157</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.918200408997919</v>
+        <v>-3.995420978204713</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.327488797973864</v>
+        <v>-2.399026136938275</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-3.05271363149177</v>
+        <v>-3.127895906061568</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.461988304093644</v>
+        <v>-3.538176319820032</v>
       </c>
     </row>
     <row r="23">
@@ -2016,489 +2016,489 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.87240086392584</v>
+        <v>1.052286520131986</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.020061323777</v>
+        <v>-2.828266852730927</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.662921177940689</v>
+        <v>2.833371464139809</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9637690817064595</v>
+        <v>-0.7830605563506765</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.002649372555801</v>
+        <v>-1.116056471354575</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.437085474270638</v>
+        <v>-2.222909472080929</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.911384681079831</v>
+        <v>-1.70048005763892</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.216922969353853</v>
+        <v>-1.008816159844436</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.851254546621746</v>
+        <v>-0.6442235009167376</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9756666737398234</v>
+        <v>-0.7698103999098933</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.292417910622682</v>
+        <v>-3.07556437027398</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.248967321063432</v>
+        <v>-3.029252106428657</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.051445831045875</v>
+        <v>-3.827073050237097</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.60041060895044</v>
+        <v>-4.690171044394738</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-6.887396651176182</v>
+        <v>-6.640718250192101</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.370258679476912</v>
+        <v>-3.147429311232962</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-3.179677048950516</v>
+        <v>-2.961604854871894</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.609335789721079</v>
+        <v>-3.716571181622861</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.743861977438613</v>
+        <v>-2.858259222451551</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.88149350649347</v>
+        <v>-2.671413412483524</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.398719889517473</v>
+        <v>-4.184833366857369</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.82532429580943</v>
+        <v>-3.613430137327917</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.927172505950637</v>
+        <v>-1.720832447499582</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.003113845219104</v>
+        <v>-1.796664700722857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003924</t>
+          <t>X ≈ 0.003922</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>260</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.030000845818101</v>
+        <v>3.06327513813693</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.134490380111906</v>
+        <v>-1.100817371498565</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.041830114399588</v>
+        <v>-1.006475690731101</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.6068130488913681</v>
+        <v>-0.5706193314724644</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1771975042558296</v>
+        <v>0.2428705341515069</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7850357107759649</v>
+        <v>-0.7195611077896942</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.038240427625901</v>
+        <v>3.104632478775848</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.611110383140854</v>
+        <v>1.677845635056286</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.269741872981911</v>
+        <v>1.336448241789412</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2697060349940301</v>
+        <v>-0.2020799314535893</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7634343410115818</v>
+        <v>-0.6938677662332182</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.64035695198239</v>
+        <v>1.708475612240456</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.66575588197334</v>
+        <v>1.734593883555448</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.594517160843701</v>
+        <v>2.662834508569169</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.942773178993605</v>
+        <v>2.771132880970129</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.537833228615028</v>
+        <v>3.366789566624945</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.403739534466105</v>
+        <v>3.232823267977793</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.45260227221695</v>
+        <v>4.279177927137084</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.668725435148836</v>
+        <v>4.738205801197971</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5.24038461538467</v>
+        <v>5.309666995781399</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.158722667925169</v>
+        <v>3.228659289353821</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.851998381513276</v>
+        <v>3.922044097175437</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.203696624918535</v>
+        <v>2.273441886580621</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.050832208726938</v>
+        <v>4.120686556434215</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005201</t>
+          <t>X ≈ 0.0052</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.187529902972109</v>
+        <v>2.026652105605095</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.457532747760176</v>
+        <v>4.308519450270893</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.444481613766236</v>
+        <v>3.299022061755295</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9850978206137668</v>
+        <v>0.8327886342058619</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7028866458506755</v>
+        <v>-0.8315524342597271</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.817053368702354</v>
+        <v>-1.951644036894521</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.593693032329682</v>
+        <v>-2.72738556911186</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1797055134006129</v>
+        <v>0.05979731407659017</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6584918027741367</v>
+        <v>-0.7823087633281745</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.62088382156297</v>
+        <v>1.511434171352427</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.450798542921504</v>
+        <v>1.340536476915517</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.185852304174198</v>
+        <v>2.818859329901166</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.321209991222702</v>
+        <v>1.686847283615492</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.244079586721902</v>
+        <v>2.33545455595614</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5.216727295053083</v>
+        <v>4.302833828979622</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.618804888534058</v>
+        <v>2.980571662672652</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.923307685613203</v>
+        <v>3.558128260027637</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.695517251974096</v>
+        <v>4.608725806244507</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.788833397361977</v>
+        <v>5.705674455891206</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.78289473684206</v>
+        <v>3.689877094053095</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.11688731030025</v>
+        <v>4.02838819480948</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.725142780973499</v>
+        <v>2.630956330316749</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.245531982543241</v>
+        <v>1.143316505353823</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.2923976608187075</v>
+        <v>0.1864269834081256</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.006478</t>
+          <t>X ≈ 0.006477</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6303001962853898</v>
+        <v>-0.3111091084913014</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8644979963445891</v>
+        <v>1.172944335669577</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.03128307125934526</v>
+        <v>0.3377226840847598</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.295130750259844</v>
+        <v>-0.9841175954046264</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4421709121463806</v>
+        <v>-0.1090942479734522</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.475865194845085</v>
+        <v>-1.135551394397538</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.70534832952837</v>
+        <v>-4.349133981074814</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.146917874258151</v>
+        <v>-2.801556483202383</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.025185394971309</v>
+        <v>3.33314248675029</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.475714576664615</v>
+        <v>3.777129493292698</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.180398120730047</v>
+        <v>7.095620435687742</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.28780728473977</v>
+        <v>6.208854609707402</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.163316066252627</v>
+        <v>5.079603680250834</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.168953120248979</v>
+        <v>6.072817973840088</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.737015746242385</v>
+        <v>7.00908684006739</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.332075795863709</v>
+        <v>7.603473762010282</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7.811479034230146</v>
+        <v>8.079312722593855</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.252507888073552</v>
+        <v>5.535447628528772</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.24163718597466</v>
+        <v>4.531826814331147</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.042177914110397</v>
+        <v>5.328428721860078</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>8.179959100204535</v>
+        <v>8.444419139260042</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.55799177462324</v>
+        <v>10.8075975680948</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>11.44626387362074</v>
+        <v>11.6918283781378</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>10.75682560183687</v>
+        <v>11.00624002735351</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.007756</t>
+          <t>X ≈ 0.007754</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.021947492707319</v>
+        <v>-8.052611819314301</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.181506264722955</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.275084341003001</v>
+        <v>-3.207760607871592</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.814964610717901</v>
+        <v>-1.714832274373144</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.354147439220206</v>
+        <v>-4.256505099861627</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.993069782735162</v>
+        <v>-1.86365656082306</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.490573595948597</v>
+        <v>-3.37089936236049</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.8705775168295204</v>
+        <v>0.02735978112171722</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.002974495285045</v>
+        <v>-2.87232950755174</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.776809906054545</v>
+        <v>-3.645245183588273</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.951726001258017</v>
+        <v>-4.841773776720458</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-5.230819904732897</v>
+        <v>-5.120523180168412</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.456760398582368</v>
+        <v>-2.56721465878924</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.953479528457322</v>
+        <v>-2.052999417588836</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-2.163135405175844</v>
+        <v>-1.975848597522351</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-2.292713036713799</v>
+        <v>-1.381461675579303</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-3.876082093181601</v>
+        <v>-2.985967047850913</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.531790146958045</v>
+        <v>-1.620219516377972</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-5.214217708663917</v>
+        <v>-4.345504606041885</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-5.751811594202834</v>
+        <v>-4.893952913720902</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.396461278563208</v>
+        <v>-3.230616728745836</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-4.921691696524668</v>
+        <v>-4.041756807801974</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-7.545467254680176</v>
+        <v>-6.708458565908138</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.273582506992078</v>
+        <v>-3.107820230896074</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.009033</t>
+          <t>X ≈ 0.009031</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1857493127275447</v>
+        <v>-0.2317562043410959</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.80465656797697</v>
+        <v>1.706194270036399</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.960625291458008</v>
+        <v>-2.004552051721866</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8139534883720927</v>
+        <v>0.6915848379262783</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.099846494045721</v>
+        <v>4.901248910833608</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.798639014029256</v>
+        <v>1.679124187840053</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.025772881975229</v>
+        <v>0.9071755039497305</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.235590329479919</v>
+        <v>2.901691331923892</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.95152499915369</v>
+        <v>1.806814877474963</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0148988907098726</v>
+        <v>-0.1024644349251602</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.777630250848425</v>
+        <v>3.580686116327669</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.335745649699135</v>
+        <v>2.165573076516033</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.211254431212026</v>
+        <v>-0.09395262670368254</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.335683775171226</v>
+        <v>-2.587758775877553</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.3309663811403354</v>
+        <v>0.1631888356327664</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.399554964587111</v>
+        <v>-2.65151515151512</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-2.696439356410458</v>
+        <v>-3.921795924856262</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.6869493205175132</v>
+        <v>-0.6175457195865306</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2597182142250816</v>
+        <v>-1.538017975025838</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.25290697674415</v>
+        <v>0.9215551076694908</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.872497265420648</v>
+        <v>2.651736212430734</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.959332907452463</v>
+        <v>2.575890251021598</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.908526678585751</v>
+        <v>0.5776376907764131</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.4929960560315507</v>
+        <v>-0.6345581988104954</v>
       </c>
     </row>
     <row r="29">
@@ -2511,158 +2511,158 @@
         <v>64</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5491214057508387</v>
+        <v>-0.5158471134320095</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.32399738448126</v>
+        <v>-2.288642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.60029069767446</v>
+        <v>-4.564096980255556</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.284439517301536</v>
+        <v>1.350112547197213</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.778395869691678</v>
+        <v>-4.712921266705408</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.261237998254295</v>
+        <v>2.327630049404242</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.267316647264266</v>
+        <v>-4.200581395348834</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.024199417758368</v>
+        <v>2.09090578656587</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3121359930110614</v>
+        <v>-0.2445098894706206</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.162776725895725</v>
+        <v>-3.095450247308698</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.245629370629331</v>
+        <v>1.313300349243264</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.441361847857813</v>
+        <v>-1.372361717612854</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.662718658892125</v>
+        <v>-1.593440594059402</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.321649897929426</v>
+        <v>-2.25158389163996</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.960910151691955</v>
+        <v>3.030303030303031</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.264316457543032</v>
+        <v>1.333885893325558</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.846833041447752</v>
+        <v>5.916545189504376</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.500456204379567</v>
+        <v>4.569936570428702</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.6875</v>
+        <v>4.756782380396729</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>7.269299591002003</v>
+        <v>7.339236212430656</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>10.31834453535944</v>
+        <v>10.3883902510216</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>10.59311970184157</v>
+        <v>10.66286496350365</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>10.5171783625731</v>
+        <v>10.58703271028038</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01159</t>
+          <t>X ≈ 0.01158</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>60</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.992545260915911</v>
+        <v>3.02581955323474</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.657369746271549</v>
+        <v>7.69104275488489</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.217669282185405</v>
+        <v>1.253023705853892</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.5038759689922898</v>
+        <v>0.5400696864111936</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3257707969749859</v>
+        <v>0.3912453999612566</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.552904664920966</v>
+        <v>4.619296716070913</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.392316647264259</v>
+        <v>-2.325581395348827</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.350800582241632</v>
+        <v>-7.28409421343413</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.12463599301104</v>
+        <v>-8.057009889470599</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.796037296037248</v>
+        <v>-9.728366317423315</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.587195181191099</v>
+        <v>-7.51819505094614</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.141885325558789</v>
+        <v>-6.072607260726066</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-6.80081656459609</v>
+        <v>-6.730750558306624</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-7.872423181641373</v>
+        <v>-7.803030303030297</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.339850209123654</v>
+        <v>-1.270280773341128</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.111500291885584</v>
+        <v>-3.04178814382896</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.228710462287076</v>
+        <v>-1.159230096237941</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.374999999999993</v>
+        <v>-4.305717619603264</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.918200408997905</v>
+        <v>-4.848263787569252</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-9.994155464640563</v>
+        <v>-9.924109748978402</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.05271363149177</v>
+        <v>-2.982968369829685</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.795321637426895</v>
+        <v>-4.725467289719617</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>53</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.703237084815242</v>
+        <v>6.736511377134072</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.14164647583129</v>
+        <v>10.17531948444463</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.154776200424436</v>
+        <v>1.190130624092923</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.988152698551993</v>
+        <v>8.024346415970896</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.73609046069776</v>
+        <v>5.801763490593437</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.149670168044167</v>
+        <v>2.215144771030438</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.283573322500423</v>
+        <v>-4.217181271350476</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.44892042084917</v>
+        <v>-6.382185168933738</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.520611902996329</v>
+        <v>-4.453905534188827</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.407654860935615</v>
+        <v>-3.340028757395174</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.020088046650443</v>
+        <v>-4.952761568063416</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.412389497295159</v>
+        <v>-3.344718518681226</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.65008826295211</v>
+        <v>-2.581088132707151</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.9021398316739138</v>
+        <v>0.9714178965066367</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.64358386019358</v>
+        <v>-1.573517853904114</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.935316263402385</v>
+        <v>-2.865923384791309</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.069409957551272</v>
+        <v>-2.999840521768746</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.287600920816402</v>
+        <v>-1.217888772759778</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.70210714777577</v>
+        <v>2.771587513824905</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.889150943396224</v>
+        <v>2.958433323792953</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.4591580815680842</v>
+        <v>0.529094702996737</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.3832030259254751</v>
+        <v>0.4532487415876361</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.228814260422588</v>
+        <v>-1.159068998760503</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.5820368531391367</v>
+        <v>0.6518912008464142</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.040164308534948</v>
+        <v>7.073438600853777</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4378683489664965</v>
+        <v>-0.4041953403531551</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>23.12243118694731</v>
+        <v>23.1577856106158</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.551495016611327</v>
+        <v>4.58768873403023</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.186225231587244</v>
+        <v>4.251898261482921</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.51624698745123</v>
+        <v>11.5817215904375</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.02909514111149036</v>
+        <v>0.09548719226143731</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.893397638450026</v>
+        <v>6.960132890365458</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.934913703472603</v>
+        <v>7.001620072280105</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.589649721274647</v>
+        <v>2.657275824815088</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.00686613124714</v>
+        <v>10.07419260983416</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.156343656343708</v>
+        <v>6.224014634957641</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.031852437856521</v>
+        <v>5.10085256810148</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.381924198250736</v>
+        <v>8.451202263083459</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.151564387784866</v>
+        <v>4.221630394074332</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.175195865977663</v>
+        <v>1.244588744588739</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.612530743257324</v>
+        <v>4.68210017903985</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.078975898590613</v>
+        <v>8.148688046647237</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.723670490093902</v>
+        <v>4.793150856143036</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.162860476746133</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.7960853052878107</v>
+        <v>0.8660219267164635</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.7201302496451447</v>
+        <v>0.7901759653073057</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.576523155301238</v>
+        <v>-2.506777893639153</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.9189640768588632</v>
+        <v>0.9888184245661407</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.674121405750853</v>
+        <v>-9.640847113432024</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>17.99070307960482</v>
+        <v>18.02437608821816</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.55100261551868</v>
+        <v>20.58635703918717</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.837209302325554</v>
+        <v>7.873403019744458</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.47193951730154</v>
+        <v>11.53761254719721</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7.659104130308265</v>
+        <v>7.724578733294535</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14.88623799825424</v>
+        <v>14.95263004940418</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.60768335273573</v>
+        <v>14.67441860465117</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.649199417758368</v>
+        <v>6.71590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.875364006988939</v>
+        <v>5.942990110529379</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.149723274104275</v>
+        <v>6.217049752691302</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.129370629370683</v>
+        <v>-6.061699650756751</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.746138152142258</v>
+        <v>8.815138282387217</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.524781341107875</v>
+        <v>4.594059405940598</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.865850102070574</v>
+        <v>7.93591610836004</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>8.460910151691955</v>
+        <v>8.530303030303031</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.326816457543032</v>
+        <v>8.396385893325558</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.22183304144778</v>
+        <v>8.291545189504404</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.437956204379482</v>
+        <v>8.507436570428617</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.625</v>
+        <v>12.69428238039673</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>12.08179959100199</v>
+        <v>12.15173621243064</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>12.00584453535944</v>
+        <v>12.0758902510216</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>12.28061970184151</v>
+        <v>12.35036496350359</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.20467836257304</v>
+        <v>16.27453271028032</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>30.94126320963382</v>
+        <v>30.97453750195265</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.91378000268181</v>
+        <v>22.94745301129515</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.78177184628797</v>
+        <v>13.81712626995645</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.06797853309481</v>
+        <v>13.10417225051371</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.70270874807076</v>
+        <v>12.76838177796644</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.88987336107749</v>
+        <v>12.95534796406376</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.11700722902358</v>
+        <v>12.18339928017352</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.146144891197274</v>
+        <v>4.212880143112706</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.187660956219908</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.413825545450536</v>
+        <v>3.481451648990976</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.3804925048735</v>
+        <v>11.44781898346053</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.79370629370631</v>
+        <v>18.86137727232024</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.66921507521905</v>
+        <v>17.73821520546401</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>17.44785826418481</v>
+        <v>17.51713632901753</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>16.78892702514751</v>
+        <v>16.85899303143697</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.691679382461182</v>
+        <v>9.761072261072258</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.557585688312258</v>
+        <v>9.627155124094784</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.452602272216922</v>
+        <v>9.522314420273545</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.668725435148907</v>
+        <v>9.738205801198042</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.16346153846154</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.312568821771272</v>
+        <v>9.382505443199925</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.544306073820977</v>
+        <v>1.614351789483138</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.819081240303163</v>
+        <v>1.888826501965248</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
   </sheetData>
@@ -3180,83 +3180,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01971</t>
+          <t>X &gt; -0.0197</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3342</v>
+        <v>3346</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1148830519015078</v>
+        <v>0.1139762762979188</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1226888108771718</v>
+        <v>0.1217632616148876</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1858524519742843</v>
+        <v>0.1848126376428283</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1429796771025025</v>
+        <v>0.141971053018402</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.03248697341578577</v>
+        <v>0.03092606874253079</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.001610155405963098</v>
+        <v>-0.003126379666163359</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.102746818655497</v>
+        <v>-0.1041644792903753</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1260867485150143</v>
+        <v>-0.1274850241412153</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.09730043329912519</v>
+        <v>-0.09873271388043037</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.04954660087756935</v>
+        <v>-0.05105750851823387</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.00367260346344267</v>
+        <v>0.002104828606753983</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.07928118393234485</v>
+        <v>-0.0807586144255481</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08297010911634572</v>
+        <v>-0.08447446709151052</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1673427639040526</v>
+        <v>-0.1687534665266242</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.002845809597587845</v>
+        <v>-0.004471373011050161</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.07640328114386108</v>
+        <v>-0.0779259500189724</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.01358366189560201</v>
+        <v>-0.01518583348625668</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.01114186894651681</v>
+        <v>-0.01275075321639463</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.01369567256002568</v>
+        <v>0.01206205535857663</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.02054692169755157</v>
+        <v>-0.02213553005103819</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.02200885856557022</v>
+        <v>0.02035371019122323</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.006117187128609203</v>
+        <v>-0.007741768094291501</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1022699182601343</v>
+        <v>-0.1037730705566986</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1902947074448633</v>
+        <v>-0.1916956220567414</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.0893194544642526</v>
+        <v>0.0882698316754329</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1723040353993852</v>
+        <v>0.1574706868454925</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1829117879119337</v>
+        <v>0.16844659142604</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2030192246208529</v>
+        <v>0.1887210251192215</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.09376313464085229</v>
+        <v>0.1086997634457205</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1208001759117749</v>
+        <v>-0.1224941460363453</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1589310116170779</v>
+        <v>-0.1606056840884449</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1212214946610288</v>
+        <v>-0.1229513893715506</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.09249468580344455</v>
+        <v>-0.09425863794832878</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.01086353792124584</v>
+        <v>-0.0127515162648848</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01859059232280202</v>
+        <v>-0.02046146477803745</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1006108930015444</v>
+        <v>-0.1023938458494484</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0989322703929858</v>
+        <v>-0.1007551626891328</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1526766924652705</v>
+        <v>-0.1544435880713806</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.01577513955182752</v>
+        <v>0.01378373339748151</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.09097947038362975</v>
+        <v>-0.09282459102710305</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.02721894599732622</v>
+        <v>-0.02914602156806012</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.03575861167583838</v>
+        <v>0.03375142451636037</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.00035061039077533</v>
+        <v>-0.002308557007580703</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.005630630630626854</v>
+        <v>-0.007577247677659216</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.03974491992965312</v>
+        <v>0.03772481129058036</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.01185415074404972</v>
+        <v>0.009863840457370543</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08607702193361177</v>
+        <v>-0.08794185126669163</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1741550709807171</v>
+        <v>-0.1759177401700711</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0841467842672472</v>
+        <v>0.08287661029176263</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.169897306904943</v>
+        <v>0.1547455685426442</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1299499839397882</v>
+        <v>0.1152031930333806</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1849830688719081</v>
+        <v>0.1703672517853647</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.01722991754228076</v>
+        <v>0.03189997954839185</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1398121851642813</v>
+        <v>-0.1419275805959685</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2031928960546523</v>
+        <v>-0.2052646874378681</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1634009846136593</v>
+        <v>-0.1655332605714577</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1347716578668283</v>
+        <v>-0.1369380292631988</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.017342442679535</v>
+        <v>-0.01968297797152019</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.05709011148511678</v>
+        <v>-0.05937301153633712</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1076577222536201</v>
+        <v>-0.1098924218410318</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.0985073983856708</v>
+        <v>-0.1008002533163364</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1511389968522963</v>
+        <v>-0.1533788098520432</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.02280754245693828</v>
+        <v>0.02032973513122016</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.05841351980563303</v>
+        <v>-0.06077055232664463</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.02353086954848749</v>
+        <v>-0.02593688193839228</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.07077563963506606</v>
+        <v>0.06825007785681692</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.03300002426473014</v>
+        <v>0.03052742463938074</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.02645102781136899</v>
+        <v>0.02399252532426743</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.07575181356025951</v>
+        <v>0.0732100873929511</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.07843981666615463</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.0522093450570793</v>
+        <v>-0.05459121661118616</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1403579570394911</v>
+        <v>-0.1426377854874659</v>
       </c>
     </row>
     <row r="9">
@@ -3430,161 +3430,161 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3283</v>
+        <v>3286</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.06264107533846897</v>
+        <v>0.07741165319438892</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1208089797561556</v>
+        <v>0.121745305031034</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.05947719178992372</v>
+        <v>0.06125117106865474</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1193770286350002</v>
+        <v>0.09125475953268847</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.01342952335847514</v>
+        <v>0.01461012588970334</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1458034734481188</v>
+        <v>-0.1616198139209004</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1440650320487364</v>
+        <v>-0.1596920819914587</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1628531734843364</v>
+        <v>-0.1783978702125566</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07366292305425048</v>
+        <v>-0.08930475569405161</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.01119953562555764</v>
+        <v>-0.02670685916758941</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.02260682298310002</v>
+        <v>-0.007866888715184928</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1324055307363352</v>
+        <v>-0.1174910394771231</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1160354969166661</v>
+        <v>-0.1311765492779671</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2283313221171497</v>
+        <v>-0.2433192348361004</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.0187185492052464</v>
+        <v>-0.03373487798290142</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.04349580394462293</v>
+        <v>-0.05864657504001514</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.007530047016238939</v>
+        <v>-0.0226848628238514</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.02724502077276725</v>
+        <v>0.0120798189089939</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.01824817518249233</v>
+        <v>0.003030614792123743</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.04088074231822958</v>
+        <v>0.02558937127818695</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.06354030920046227</v>
+        <v>0.04836132644712166</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.0971687362726783</v>
+        <v>0.08197297608242593</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.03606726527171134</v>
+        <v>-0.05121702615257107</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1242890452855647</v>
+        <v>-0.1393443438888227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.0146</t>
+          <t>X &gt; -0.01459</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3257</v>
+        <v>3261</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2001922001064287</v>
+        <v>0.1982753728568838</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2005871552607701</v>
+        <v>0.1846930647497587</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.07266216402392445</v>
+        <v>0.07416191723601173</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.04715742560907898</v>
+        <v>0.04906633172984698</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.09587114123316098</v>
+        <v>0.1269963177890432</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0966210605313691</v>
+        <v>-0.08262077860290873</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1192598636882849</v>
+        <v>-0.1224157102052814</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1359768977989404</v>
+        <v>-0.1391303730723621</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.07696195143478235</v>
+        <v>-0.08018700952693081</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.02271955575078977</v>
+        <v>0.01932598839197652</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.009050491229650959</v>
+        <v>0.005687504676643584</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.09939204264685486</v>
+        <v>-0.1026406834484206</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1351347976741764</v>
+        <v>-0.1384069498866509</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2159593996328724</v>
+        <v>-0.2191475644048637</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.06066551336115111</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.09039153284096813</v>
+        <v>-0.09374101986522021</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.08372275814323871</v>
+        <v>-0.08709023886538603</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.01721078325343939</v>
+        <v>-0.02066784998139326</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.002640447175394911</v>
+        <v>-0.0008304228352287168</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.0680389451088601</v>
+        <v>-0.07141440367677632</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.01022494887525482</v>
+        <v>-0.01370496403988852</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.006429168230624782</v>
+        <v>-0.009920352717294634</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.08156568796813701</v>
+        <v>-0.08495079370052139</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1698994697879712</v>
+        <v>-0.1731827144359741</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3225</v>
+        <v>3229</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3000005905523437</v>
+        <v>0.2976144250295718</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3037036957478279</v>
+        <v>0.2872261959436742</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.157903416504567</v>
+        <v>0.159017137709391</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1083957430035483</v>
+        <v>0.1099290437666554</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1303858798169486</v>
+        <v>0.1611492077024508</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.004170615297596214</v>
+        <v>0.009236773960026312</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.04231449424442246</v>
+        <v>0.03827391878193964</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1260408064743856</v>
+        <v>-0.1298957250868895</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.005121569895955247</v>
+        <v>-0.009125039574698235</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.01059092887840762</v>
+        <v>0.006511541303360957</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.005928362708573331</v>
+        <v>-0.009970605112521014</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.08179571432582833</v>
+        <v>-0.08576629685357773</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1067666686241466</v>
+        <v>-0.1107876435387354</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2171042848581237</v>
+        <v>-0.2210069725712884</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1155970222336933</v>
+        <v>-0.1196737619302581</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.05873104843176691</v>
+        <v>-0.06283876765804308</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.01971819592231583</v>
+        <v>-0.02388604734193933</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.04851208818250541</v>
+        <v>0.0442499808490453</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0664391765157859</v>
+        <v>0.06216755373110772</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.03774388355528657</v>
+        <v>-0.04187598644521984</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.004941425107006125</v>
+        <v>-0.009154876678209689</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.0003531714890314674</v>
+        <v>-0.004580191565835889</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1099568635645127</v>
+        <v>-0.1140313213260669</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1674146606827165</v>
+        <v>-0.1714257908035464</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3179</v>
+        <v>3182</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2008785942491969</v>
+        <v>0.2149131113572977</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2719530796048772</v>
+        <v>0.2717214973375164</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1447526155187404</v>
+        <v>0.1627394196933238</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.04227338485137722</v>
+        <v>0.02965301974448664</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02399544204805437</v>
+        <v>-0.007245220855303103</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1006706585562398</v>
+        <v>-0.1016169528573343</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1050010505567158</v>
+        <v>-0.1233311884825952</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1153213420999393</v>
+        <v>-0.1335863984757921</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.03805351919857003</v>
+        <v>0.05090735053208562</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.09647268221600314</v>
+        <v>0.07815907173088021</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.138445078615554</v>
+        <v>0.1513220531607828</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.002876315160868614</v>
+        <v>-0.01536276910358936</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.02513501734598833</v>
+        <v>0.03843925326096809</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.08355983167356129</v>
+        <v>-0.0701009950619067</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.02896177082841689</v>
+        <v>0.0424657793095875</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.0467275348108771</v>
+        <v>0.06008359456635759</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.005889129399839987</v>
+        <v>0.007549267424025174</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.03344999592185616</v>
+        <v>0.04687768636760836</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.0485089681986608</v>
+        <v>0.06187648257179035</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.05988846999686359</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.01876609095898374</v>
+        <v>-0.005249658840888571</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.04445411286438627</v>
+        <v>-0.03089366857638964</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.1596318704854767</v>
+        <v>-0.1460220927326077</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2482942703303266</v>
+        <v>-0.234581054647343</v>
       </c>
     </row>
     <row r="13">
@@ -3758,407 +3758,407 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3132</v>
+        <v>3136</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2598887465334627</v>
+        <v>0.2589626519453248</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.305423891787612</v>
+        <v>0.3218705379486266</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2933884023207725</v>
+        <v>0.3110636677949046</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1367967348866799</v>
+        <v>0.1551289080693579</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01162205698406638</v>
+        <v>0.04141965379618995</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1325757680721225</v>
+        <v>-0.1205989316800284</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1251978340201632</v>
+        <v>-0.1311262957734201</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.004328086730424729</v>
+        <v>-0.0104433439365863</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02364315583847088</v>
+        <v>0.01749308815316652</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1583528782131012</v>
+        <v>0.1519453344099801</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1649904496767931</v>
+        <v>0.1585999432885075</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.06343878838311667</v>
+        <v>0.05714369210952697</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.05589876701753838</v>
+        <v>-0.06216623128095478</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1310607473989691</v>
+        <v>-0.1372601489083678</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.08878003837630644</v>
+        <v>0.0822265409300087</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.002165328499863506</v>
+        <v>-0.004218127826149498</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.04921923398022443</v>
+        <v>-0.05555554524860185</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.03700193883462077</v>
+        <v>0.04958403063777439</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.04904960571842309</v>
+        <v>0.0615766978172374</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.03188775510204778</v>
+        <v>-0.01932067790209402</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.01800373773251351</v>
+        <v>0.03063997278761832</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.02498939815458812</v>
+        <v>0.01852887434855433</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.09601611047889236</v>
+        <v>-0.1022968152658734</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1209921355111874</v>
+        <v>-0.1272530040053326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009488</t>
+          <t>X &gt; -0.009487</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3070</v>
+        <v>3074</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1944444731744284</v>
+        <v>0.2102855726521824</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1829983207832555</v>
+        <v>0.1991333697716158</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2324529230616292</v>
+        <v>0.2497874598992027</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.02244246294734609</v>
+        <v>0.04044737066710979</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.09786935862979362</v>
+        <v>-0.06873254830295394</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3460805748115732</v>
+        <v>-0.3349874693599872</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2580083550682275</v>
+        <v>-0.265239811392135</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.129022224436774</v>
+        <v>-0.1364622243643723</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.0283755449072487</v>
+        <v>0.02073247914766085</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1816586208760285</v>
+        <v>0.1737094883647643</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2802003919231666</v>
+        <v>0.2721551011515899</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.08491508491508881</v>
+        <v>0.0770811533937632</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.01384885662685065</v>
+        <v>-0.0217089443400269</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.05351625473357302</v>
+        <v>-0.06135915343643461</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1843421397696332</v>
+        <v>0.1760978675291369</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.05128726482589485</v>
+        <v>0.0432900432900496</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.06665385591701778</v>
+        <v>0.05861388942819445</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1242720658379923</v>
+        <v>0.1355997704010647</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1452732775502952</v>
+        <v>0.1759448577215252</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.05896226415094219</v>
+        <v>0.08960097597540084</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.08830788908209541</v>
+        <v>0.1192158872274547</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.09699036869277222</v>
+        <v>0.1084105762248484</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.0645447397084169</v>
+        <v>-0.07239926413861753</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.1536278263519861</v>
+        <v>-0.1613814081321223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.00821</t>
+          <t>X &gt; -0.008209</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3006</v>
+        <v>3010</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.210176114910368</v>
+        <v>0.2434504072291972</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1725212614230642</v>
+        <v>0.2061942700364057</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2204241031220491</v>
+        <v>0.2557785267905359</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.045065829949543</v>
+        <v>-0.02742342653650809</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1602139726091494</v>
+        <v>-0.1318089404060956</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4507568888842641</v>
+        <v>-0.4407105229037569</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3775819289221332</v>
+        <v>-0.3862129258023757</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1406610181251935</v>
+        <v>-0.1496554694229033</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.01393407015152803</v>
+        <v>-0.02309520582578983</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1589955510578562</v>
+        <v>0.149475881541953</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2869456804682144</v>
+        <v>0.2772947046939507</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.07234145165179484</v>
+        <v>-0.08156720042556742</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.0498817483552827</v>
+        <v>-0.05932345991158172</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1188815653287563</v>
+        <v>-0.1282732647022158</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0716250771784388</v>
+        <v>0.06186904173756602</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.05586367094826272</v>
+        <v>0.0462181496664229</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.007985504371326613</v>
+        <v>-0.001624056923198225</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1354829916304183</v>
+        <v>0.1455597880445296</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.119125251207862</v>
+        <v>0.1489898395956502</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.006229235880397255</v>
+        <v>0.02363164998504175</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.03527250559161388</v>
+        <v>0.06538616261336472</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.01249347152965186</v>
+        <v>0.02275175882631686</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1251002848561384</v>
+        <v>-0.1345237777783126</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.2144833140736111</v>
+        <v>-0.2238061601515184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006933</t>
+          <t>X &gt; -0.006932</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2915</v>
+        <v>2918</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3163287988876746</v>
+        <v>0.3496030912065038</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1516853442706321</v>
+        <v>0.1853583528839735</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2467734204300669</v>
+        <v>0.2821278440985537</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1750731951155657</v>
+        <v>-0.1579748793005322</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3164563871353252</v>
+        <v>-0.2891268798150577</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6905032442222279</v>
+        <v>-0.6819696978104588</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5222319471008916</v>
+        <v>-0.5330452575534608</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2348175013811016</v>
+        <v>-0.2460863424658584</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2762961393161305</v>
+        <v>-0.2875071827174054</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.07335394172901033</v>
+        <v>-0.08500579250920737</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1182595258142669</v>
+        <v>0.1063940149863853</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2436367942696975</v>
+        <v>-0.2550717040535915</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2189542503218362</v>
+        <v>-0.2306580265670206</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2489262932639136</v>
+        <v>-0.2606414487602535</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.099903322586961</v>
+        <v>-0.1119635086030257</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.001848829321282608</v>
+        <v>-0.01023751023750918</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.07757010859815949</v>
+        <v>-0.08958262139039164</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.07974338075923271</v>
+        <v>-0.07134423192663775</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.06924050569583073</v>
+        <v>-0.04050863505074886</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2248971898560654</v>
+        <v>-0.1758786336491767</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2335929355663495</v>
+        <v>-0.1841102577543552</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2547864660122983</v>
+        <v>-0.2256861711853873</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.3229468276508882</v>
+        <v>-0.2939119384840154</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4471226665864165</v>
+        <v>-0.4382842876634285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005656</t>
+          <t>X &gt; -0.005655</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3081794792049521</v>
+        <v>0.3414537715237813</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.149995115003108</v>
+        <v>0.1836681236164495</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3032150048992719</v>
+        <v>0.3385694285677587</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1429606693458041</v>
+        <v>-0.1265969802555063</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.08330127589960057</v>
+        <v>-0.03760869174084291</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5137616153523297</v>
+        <v>-0.4878106472363797</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4163842554664754</v>
+        <v>-0.4102018090028352</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1279651235222374</v>
+        <v>-0.1017853613545014</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3142887070200828</v>
+        <v>-0.3081735335474463</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3232175532947466</v>
+        <v>-0.3170169741323292</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1702483470379761</v>
+        <v>-0.1642401126524291</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4643599835225132</v>
+        <v>-0.4784253771918472</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5389168709319634</v>
+        <v>-0.5531708278574072</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4553322952557579</v>
+        <v>-0.4697703812934435</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.3828177487287192</v>
+        <v>-0.3975354702139242</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2995731461047768</v>
+        <v>-0.3142675871561522</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.448156880530199</v>
+        <v>-0.4626840392268008</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.41094335385975</v>
+        <v>-0.4044775377683507</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3370171336936636</v>
+        <v>-0.3096149393403991</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5054656949875636</v>
+        <v>-0.4571035471086091</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.5298647048727787</v>
+        <v>-0.4810401828768036</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4779690541105026</v>
+        <v>-0.4502384372116026</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.5945137026408247</v>
+        <v>-0.5668053173353158</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.6138269755051979</v>
+        <v>-0.6070883348671572</v>
       </c>
     </row>
     <row r="18">
@@ -4168,79 +4168,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2686</v>
+        <v>2689</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5141662147088013</v>
+        <v>0.5474405070276305</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3272486689303022</v>
+        <v>0.3609216775436437</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.555450354584714</v>
+        <v>0.5908047782532009</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.01008498974261585</v>
+        <v>0.02610872767628791</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1159033292514664</v>
+        <v>-0.05023029935578904</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6493867855240865</v>
+        <v>-0.6045539575875409</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3469841003738168</v>
+        <v>-0.3016323672006536</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2918346302082782</v>
+        <v>-0.2462633820056155</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3244750353376631</v>
+        <v>-0.278905184523822</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3353184855926585</v>
+        <v>-0.2891196410464545</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.225044814949527</v>
+        <v>-0.2004511742645718</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.408509456393638</v>
+        <v>-0.4050441075605491</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6203676035205987</v>
+        <v>-0.6383285325924248</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5227669501254084</v>
+        <v>-0.5409554308546518</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5280555092263484</v>
+        <v>-0.5464586597290193</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.4684578780478219</v>
+        <v>-0.4867719511372073</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.5433955171687614</v>
+        <v>-0.5616534679815359</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.5368132954804778</v>
+        <v>-0.5331204865728907</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.5438214081157824</v>
+        <v>-0.5182044552123202</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.6542859799181926</v>
+        <v>-0.6068328612389564</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6548075518550931</v>
+        <v>-0.6069101244975315</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7831394616632608</v>
+        <v>-0.7571331777623342</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.8805265579276877</v>
+        <v>-0.8545439245588256</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.86010197994365</v>
+        <v>-0.855999085926392</v>
       </c>
     </row>
     <row r="19">
@@ -4250,79 +4250,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3958746618858555</v>
+        <v>0.4291489542046847</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2573173147602077</v>
+        <v>0.2909903233735491</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6265039918459152</v>
+        <v>0.6618584155144021</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.03068157916396785</v>
+        <v>0.06687529658287161</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1379700383414075</v>
+        <v>-0.07229700844573017</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.6586308284018685</v>
+        <v>-0.5931562254155978</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3304352223512907</v>
+        <v>-0.2640431712013438</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1764298993287596</v>
+        <v>-0.1096946474133276</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3708556353285388</v>
+        <v>-0.304149266521037</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2174762762526044</v>
+        <v>-0.1726213719716014</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.03839164128336847</v>
+        <v>-0.01653263032088859</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.05850448763834493</v>
+        <v>-0.0593402327464787</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2148701188305893</v>
+        <v>-0.2387350955129293</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.294761606094653</v>
+        <v>-0.3186077852474511</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.2602831261517338</v>
+        <v>-0.284469566571083</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.1542318041440112</v>
+        <v>-0.1783583870197987</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2254517870329096</v>
+        <v>-0.2495376986397773</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2120920078619051</v>
+        <v>-0.2127889318510228</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3115506989734911</v>
+        <v>-0.2887794327246311</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.5584319526627155</v>
+        <v>-0.5123422252815004</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5259352156277899</v>
+        <v>-0.4794274956560827</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.6574006284779088</v>
+        <v>-0.6341689205760375</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.7379353711943537</v>
+        <v>-0.7147237938928015</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.8138767104628215</v>
+        <v>-0.7905560471160769</v>
       </c>
     </row>
     <row r="20">
@@ -4335,814 +4335,814 @@
         <v>2327</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5014674593455624</v>
+        <v>0.5347417516643915</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1234653922387068</v>
+        <v>0.1571384008520482</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2683473692660598</v>
+        <v>0.3037017929345467</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3169662865395111</v>
+        <v>-0.2807725691206073</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.211143994475762</v>
+        <v>-0.1454709645800847</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7948573257944673</v>
+        <v>-0.7293827228081966</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2829268839726922</v>
+        <v>-0.2165348328227452</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.347348767178616</v>
+        <v>-0.2806135152631839</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4771389120060903</v>
+        <v>-0.4104325431985885</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2840190264300801</v>
+        <v>-0.2411640650594791</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.01513261829630608</v>
+        <v>0.03289557710244395</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1533843514975572</v>
+        <v>-0.1602007214205017</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.05180264579857408</v>
+        <v>-0.08421931932587512</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2477508477333288</v>
+        <v>-0.2799765837766302</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1942615338246583</v>
+        <v>-0.2269643031273176</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.1318733534626872</v>
+        <v>-0.1643796455117226</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.06854237356999704</v>
+        <v>-0.1012546043149385</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.04460443169362804</v>
+        <v>-0.05180244998060601</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.2152453426767309</v>
+        <v>-0.1967283072011909</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6298345509239383</v>
+        <v>-0.5857863481256089</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.6143757420447997</v>
+        <v>-0.544439120616147</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7762783696684892</v>
+        <v>-0.7062326540063282</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.8452934911107377</v>
+        <v>-0.7755482294486526</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.7063659004264764</v>
+        <v>-0.6365115527191989</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005466</t>
+          <t>X &gt; -0.0005469</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2084</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.010391022547488</v>
+        <v>1.043665314866317</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.19720403562782</v>
+        <v>0.2308770442411614</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.191537988367692</v>
+        <v>0.2268924120361788</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2354484414602638</v>
+        <v>-0.19925472404136</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1162989819286864</v>
+        <v>0.1819720118243637</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8437639385253348</v>
+        <v>-0.7782893355390641</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2781979482084225</v>
+        <v>-0.2118058970584755</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1265422686791808</v>
+        <v>-0.05980701676374878</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3240319397942102</v>
+        <v>-0.2573255709867084</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.07718131927970973</v>
+        <v>0.1169862864376086</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3793883458746095</v>
+        <v>0.3910459285995316</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.5111272164886387</v>
+        <v>0.4947057029717996</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5641458149774792</v>
+        <v>0.5187711695764818</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3235355337288581</v>
+        <v>0.2784209554384418</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.3164733043716339</v>
+        <v>0.270844338025114</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.5568334130828347</v>
+        <v>0.5111551126390736</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.7874690487138594</v>
+        <v>0.7412134795324548</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8744242122730839</v>
+        <v>0.8569500769025566</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5147316362413719</v>
+        <v>0.5266120258457647</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2219289827255295</v>
+        <v>0.2626277041377421</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.2545443126911096</v>
+        <v>0.3244809341197623</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.06133396751963716</v>
+        <v>0.008711748142523845</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.1704359603465306</v>
+        <v>-0.1006906986844456</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.0544387199604941</v>
+        <v>0.0154156277467834</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007307</t>
+          <t>X &gt; 0.0007301</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1795</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.239815296081517</v>
+        <v>1.273089588400346</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3493926964843865</v>
+        <v>0.383065705097728</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.630958195751937</v>
+        <v>0.6663126194204239</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3058378420257526</v>
+        <v>0.3420315594446564</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.10714218248755</v>
+        <v>0.1728152123832274</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.260385042373528</v>
+        <v>-1.194910439387257</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3119852110738535</v>
+        <v>-0.2455931599239065</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.09081748013488777</v>
+        <v>-0.02408222821945571</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1048261236075376</v>
+        <v>-0.03811975480003582</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1207832185380795</v>
+        <v>0.1884093220785203</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4275010518820466</v>
+        <v>0.4624689642404434</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2919745624025865</v>
+        <v>0.2947689777830078</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4235575069809414</v>
+        <v>0.3931504978230578</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7362448914695889</v>
+        <v>0.6717939978339942</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.6676318392643381</v>
+        <v>0.6025827750267112</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7951719901320615</v>
+        <v>0.7304142031768492</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.828209215203195</v>
+        <v>0.796830832146469</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.057487637548029</v>
+        <v>1.059491767133757</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.605087123599624</v>
+        <v>0.6410668599609934</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5135793871866241</v>
+        <v>0.5828617675833527</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.47177173584884</v>
+        <v>0.5417083572774928</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.9529197442730819</v>
+        <v>1.022965459935243</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.7263021530950482</v>
+        <v>0.7960474147571333</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.9846226522666868</v>
+        <v>1.054476999973964</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002008</t>
+          <t>X &gt; 0.002007</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.125878594249208</v>
+        <v>1.18926614439615</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5907030796048787</v>
+        <v>0.6546225905499981</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.484335948852078</v>
+        <v>1.548382355642929</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.03720930232558572</v>
+        <v>0.1025835660469454</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4052728506348728</v>
+        <v>0.4330156118207995</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.6075625363583441</v>
+        <v>-0.5125964832277248</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1137620017457124</v>
+        <v>-0.01872238230795631</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.341016686069068</v>
+        <v>0.4359109430921961</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5825327510917049</v>
+        <v>0.6772648805032375</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4753640069889329</v>
+        <v>0.570571722787875</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3885491580268905</v>
+        <v>0.4448978539571229</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.8158897177588784</v>
+        <v>0.8323709688302543</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4655770298977444</v>
+        <v>0.4420536721273649</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9525888277388859</v>
+        <v>0.8205750621697803</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.9360842157829481</v>
+        <v>0.8692494416933698</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.464254633297301</v>
+        <v>1.437574544645926</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.597719467576468</v>
+        <v>1.611339164353595</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.027853108337382</v>
+        <v>2.014992083291943</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.842638478627059</v>
+        <v>1.871072934065069</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.494565217391312</v>
+        <v>1.590004305530421</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.352702601035482</v>
+        <v>1.448527656280959</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.61119570592799</v>
+        <v>1.706906293802348</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.484633079767988</v>
+        <v>1.580311487567826</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.87691916524868</v>
+        <v>1.972393672847218</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003285</t>
+          <t>X &gt; 0.003284</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1187</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.191650406329735</v>
+        <v>1.224924698648564</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.527615831282723</v>
+        <v>1.561288839896065</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.178519394042233</v>
+        <v>1.21387381771072</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2969408459497416</v>
+        <v>0.3331345633686453</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7705972354223434</v>
+        <v>0.8362702653180207</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.132842178416503</v>
+        <v>-0.06736757543023231</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3526809512744293</v>
+        <v>0.4190730024243763</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7452672453531832</v>
+        <v>0.8120024972686153</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.9545685452751513</v>
+        <v>1.021274914082653</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8518740741030371</v>
+        <v>0.9195001776434779</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.343677934053893</v>
+        <v>1.361345054704728</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.870629370629374</v>
+        <v>1.837629208303717</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.637643618921032</v>
+        <v>1.553393315944234</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.393468209794747</v>
+        <v>2.255133231443949</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.966102840065517</v>
+        <v>2.82424524354056</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.718702906536102</v>
+        <v>2.631143366437485</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.837347207332414</v>
+        <v>2.801768567841954</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.490577776072854</v>
+        <v>3.50703340499259</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.032732952484032</v>
+        <v>3.102213318533167</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.630054759898904</v>
+        <v>2.699337140295633</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.84506833573667</v>
+        <v>2.915004957165323</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.021851275039303</v>
+        <v>3.091896990701464</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.369920460055546</v>
+        <v>2.439665721717631</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.883701108992639</v>
+        <v>2.953555456699917</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.004563</t>
+          <t>X &gt; 0.004561</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>927</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6760397113276113</v>
+        <v>0.7093140036464405</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.274269137607021</v>
+        <v>2.307942146220363</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.80127114398276</v>
+        <v>1.836625567651247</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5504209027552278</v>
+        <v>0.5866146201741316</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9370308169792949</v>
+        <v>1.002703846874972</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.05008157391734613</v>
+        <v>0.1155561769036169</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4005504013160603</v>
+        <v>-0.3341583501661134</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.502420194841001</v>
+        <v>0.569155446756433</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.8661704166842554</v>
+        <v>0.9328767854917572</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.166448861983561</v>
+        <v>1.234074965524002</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.934669510663419</v>
+        <v>1.937780150113433</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.935214946517426</v>
+        <v>1.873853517879184</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.629758841797404</v>
+        <v>1.50257115027118</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.337079075735708</v>
+        <v>2.140783358679592</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.972646218575434</v>
+        <v>2.839141914811655</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.488957616632625</v>
+        <v>2.424813256352543</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.678488517952957</v>
+        <v>2.680868651946241</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.220754292796194</v>
+        <v>3.290466440852818</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.573878534476648</v>
+        <v>2.643358900525783</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.897923408845735</v>
+        <v>1.967205789242463</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.757096246881218</v>
+        <v>2.827032868309871</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.789016056395035</v>
+        <v>2.859061772057196</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.416542031938647</v>
+        <v>2.486287293600732</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.556350422983023</v>
+        <v>2.6262047706903</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.00584</t>
+          <t>X &gt; 0.005838</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1830214513920652</v>
+        <v>0.2821200762969838</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.562131651033447</v>
+        <v>1.659183506192541</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.265288329804456</v>
+        <v>1.36239127599179</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4086378737541523</v>
+        <v>0.5067839041952666</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.471939517301529</v>
+        <v>1.597526955185799</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6591041303083145</v>
+        <v>0.7859196748067205</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.3148094268257253</v>
+        <v>0.441931047977711</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6076833527357266</v>
+        <v>0.7343330126397518</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.36348513204409</v>
+        <v>1.489086956323362</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.018221149846077</v>
+        <v>1.144131337348213</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.092498667523444</v>
+        <v>2.131457741279043</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.527281731144392</v>
+        <v>1.567401633123474</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.404221127821771</v>
+        <v>1.442813032743821</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.041233415499867</v>
+        <v>2.077654270419913</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.240671275175011</v>
+        <v>2.36448753693147</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.120423742536019</v>
+        <v>2.244588744588739</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.272453081291246</v>
+        <v>2.396385893325558</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.739715731004267</v>
+        <v>2.862973760932945</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.52522372941533</v>
+        <v>1.650293713285848</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.283082975679541</v>
+        <v>1.408568094682437</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.31355924765441</v>
+        <v>2.43745049814499</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.809850257820088</v>
+        <v>2.933033108164452</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.798502391398081</v>
+        <v>2.92179353493222</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.2948071179379</v>
+        <v>3.417389853137522</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.007117</t>
+          <t>X &gt; 0.007116</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>536</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4303562061895008</v>
+        <v>0.4636304985083299</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.774285169157118</v>
+        <v>1.807958177770459</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.640554854324712</v>
+        <v>1.675909277993199</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9267615411315546</v>
+        <v>0.9629552585504584</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.054029069540341</v>
+        <v>2.119702099436019</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.308357861651608</v>
+        <v>1.373832464637879</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.841461878851312</v>
+        <v>1.907853930001259</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.749474397511847</v>
+        <v>1.816209649427279</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.8581546416389685</v>
+        <v>0.9248610104464703</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2708863950486418</v>
+        <v>0.3385124985890826</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5452456621639783</v>
+        <v>0.6125721407510056</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.07958459450997424</v>
+        <v>0.1472555731239069</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2610635252765618</v>
+        <v>0.3300636555215206</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.7859753709586244</v>
+        <v>0.8552534357913473</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.8733127886377332</v>
+        <v>0.9433787949271988</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.5355370173636018</v>
+        <v>0.6049298959746778</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.588010487393781</v>
+        <v>0.6575799231763071</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.975564384731335</v>
+        <v>2.045276532787959</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.6991502342303164</v>
+        <v>0.768630600279451</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.1399253731343322</v>
+        <v>0.2092077535310608</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.5295607850318902</v>
+        <v>0.5994974064605429</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.453605729389281</v>
+        <v>0.523651445051442</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.168679403334103</v>
+        <v>0.2384246649961881</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.025573884961162</v>
+        <v>1.095428232668439</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.008394</t>
+          <t>X &gt; 0.008393</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.361054473646185</v>
+        <v>3.359152886568026</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.533416647444078</v>
+        <v>4.524376088218219</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.344972464764972</v>
+        <v>3.336357039187227</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.877410307350708</v>
+        <v>1.87340301974448</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.275959617804048</v>
+        <v>4.28761254719722</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.453073979554553</v>
+        <v>2.474578733294592</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.690258098756807</v>
+        <v>3.702630049404249</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.65793460901714</v>
+        <v>2.424418604651166</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.196938111225698</v>
+        <v>2.21590578656587</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.674358981863314</v>
+        <v>1.692990110529379</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.451230811792712</v>
+        <v>2.467049752691302</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.92088062691078</v>
+        <v>1.938300349243306</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.550158252644742</v>
+        <v>1.315138282387188</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.082570285831487</v>
+        <v>1.844059405940605</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.926151609608262</v>
+        <v>1.93591610836004</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.516186533601505</v>
+        <v>1.280303030303038</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.135861683673689</v>
+        <v>1.896385893325558</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.538415956020614</v>
+        <v>3.291545189504376</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.749513993324292</v>
+        <v>2.507436570428702</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.182788944723612</v>
+        <v>1.944282380396736</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.890844817132702</v>
+        <v>1.901736212430706</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.317402324304162</v>
+        <v>2.075890251021598</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.843433772193322</v>
+        <v>2.600364963503658</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.516236151517823</v>
+        <v>2.524532710280383</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.009672</t>
+          <t>X &gt; 0.00967</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>312</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.338699107069722</v>
+        <v>4.371973399388551</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.285574874476673</v>
+        <v>5.319247883090014</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.807412871928996</v>
+        <v>4.842767295597483</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.170542635658919</v>
+        <v>2.206736353077822</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.048862594224609</v>
+        <v>4.114535624120286</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.6334631046673</v>
+        <v>2.69893770765357</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.424699536715835</v>
+        <v>4.491091587865782</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.223067968120347</v>
+        <v>2.289803220035779</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.264584033142981</v>
+        <v>2.331290401950483</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.131774263399194</v>
+        <v>2.199400366939635</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.085620710001706</v>
+        <v>2.152947188588733</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.806526806526804</v>
+        <v>1.874197785140737</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.64357404957812</v>
+        <v>1.712574179823079</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.024781341107875</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.365850102070574</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.31988451066632</v>
+        <v>2.389277389277396</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.467842098568667</v>
+        <v>3.537411534351193</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.324397144011854</v>
+        <v>4.394109292068478</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.578981845405202</v>
+        <v>3.648462211454337</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.16346153846154</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.620261129463586</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.864818894333801</v>
+        <v>1.934864609995962</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.101132522354384</v>
+        <v>3.170877784016469</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.345704003598733</v>
+        <v>3.415558351306011</v>
       </c>
     </row>
     <row r="30">
@@ -5155,158 +5155,158 @@
         <v>248</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.600072142636307</v>
+        <v>5.633346434955136</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.684251466701653</v>
+        <v>7.717924475314994</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.647776809067125</v>
+        <v>6.683131232735612</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.91785446361591</v>
+        <v>3.954048181034814</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.762262097946696</v>
+        <v>4.827935127842373</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.546200904501873</v>
+        <v>4.611675507488144</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.983012191802679</v>
+        <v>5.049404242952626</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.898005933380894</v>
+        <v>3.964741185296326</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.326618772597079</v>
+        <v>2.393325141404581</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.76246078118249</v>
+        <v>2.830086884722931</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.440045854749435</v>
+        <v>3.507372333336463</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.951274531919701</v>
+        <v>2.018945510533634</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.439686539239005</v>
+        <v>2.508686669483964</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.234458760462715</v>
+        <v>4.303736825295438</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>3.575527521425414</v>
+        <v>3.64559352771488</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>2.154458538788731</v>
+        <v>2.223851417399807</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.036493876897872</v>
+        <v>4.106063312680398</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.931510460802592</v>
+        <v>4.001222608859216</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.341182010831183</v>
+        <v>3.410662376880317</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.512096774193552</v>
+        <v>1.58137915459028</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.1624447522923731</v>
+        <v>0.2323813737210259</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3167361098018517</v>
+        <v>-0.2466903941396907</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.167716476035118</v>
+        <v>1.237461737697203</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.495000943218258</v>
+        <v>1.564855290925536</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01223</t>
+          <t>X &gt; 0.01222</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>188</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.432261572972607</v>
+        <v>6.465535865291436</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.692830739179342</v>
+        <v>7.726503747792684</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.380789849561296</v>
+        <v>8.416144273229783</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.007422068283027</v>
+        <v>5.043615785701931</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.769811857727071</v>
+        <v>6.835484887622748</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.893146683499815</v>
+        <v>5.958621286486085</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.120280551445788</v>
+        <v>5.186672602595735</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.905555693161268</v>
+        <v>5.972290945076701</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.415156864566875</v>
+        <v>5.481863233374376</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.237066134648508</v>
+        <v>6.304692238188949</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.043340295380872</v>
+        <v>7.1106667739679</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.700416604671929</v>
+        <v>5.768087583285862</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.639755173418827</v>
+        <v>5.708755303663786</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.546057936852556</v>
+        <v>7.615336001685279</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6.887126697815255</v>
+        <v>6.95719270410472</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.354527172968552</v>
+        <v>5.423920051579628</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.752348372436657</v>
+        <v>5.821917808219183</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.179279849958391</v>
+        <v>6.248991998015015</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.799658332039137</v>
+        <v>4.869138698088271</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.390957446808507</v>
+        <v>3.460239827205235</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.783927250576511</v>
+        <v>1.853863872005164</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.771801982167943</v>
+        <v>2.841847697830104</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.514662255033059</v>
+        <v>2.584407516695144</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.502550702998633</v>
+        <v>3.57240505070591</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>135</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.325878594249204</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.731443820345618</v>
+        <v>6.765116828958959</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>11.2176692821854</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.175643221005245</v>
+        <v>7.241316250900923</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.362807834012031</v>
+        <v>7.428282436998302</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.812163924180219</v>
+        <v>8.878555975330165</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.75583150088389</v>
+        <v>10.82256675279932</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.02351215513709</v>
+        <v>10.09113825867753</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.77935290373391</v>
+        <v>11.84667938232094</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.278036778036778</v>
+        <v>9.345707756650711</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.894286300290382</v>
+        <v>8.963286430535341</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.15441097073751</v>
+        <v>10.22368903557023</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.23622047244094</v>
+        <v>10.30628647873041</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.609058299840108</v>
+        <v>8.678451178451184</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>9.215705346431918</v>
+        <v>9.285274782214444</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.110721930336638</v>
+        <v>9.180434078393262</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.623141389564758</v>
+        <v>5.692621755613892</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.587962962962962</v>
+        <v>3.657245343359691</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.304021813224267</v>
+        <v>2.37395843465292</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>3.709548239063146</v>
+        <v>3.779593954725307</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.984323405545275</v>
+        <v>4.05406866720736</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.649122807017541</v>
+        <v>4.718977154724818</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>107</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.138962706398729</v>
+        <v>6.172236998717558</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.607525509511412</v>
+        <v>8.641198518124753</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.102404484677614</v>
+        <v>8.1377589083461</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.650293414475108</v>
+        <v>3.686487131894012</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.957920825712748</v>
+        <v>8.023593855608425</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.275926560214856</v>
+        <v>6.341401163201127</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.11053706367485</v>
+        <v>11.17692911482479</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.76656185740863</v>
+        <v>11.83329710932406</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.938919043926589</v>
+        <v>10.00562541273409</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.96882195091417</v>
+        <v>12.03644805445461</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.24318121802951</v>
+        <v>12.31050769661653</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.09492843604993</v>
+        <v>10.16259941466386</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.905016656815128</v>
+        <v>9.974016787060087</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.61823928503311</v>
+        <v>10.68751734986583</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.82846692450048</v>
+        <v>11.89853293078995</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.55436809561719</v>
+        <v>10.62376097422826</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>10.42027440146826</v>
+        <v>10.48984383725079</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.380711546120651</v>
+        <v>9.450423694177275</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.858516952043111</v>
+        <v>5.927997318092245</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>5.110981308411212</v>
+        <v>5.180263688807941</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.69862202090858</v>
+        <v>2.768558642337233</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.491825843770648</v>
+        <v>4.561871559432809</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.701180449505109</v>
+        <v>5.770925711167195</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.625239110236642</v>
+        <v>5.695093457943919</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>10.96002493571262</v>
+        <v>10.99329922803145</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.746800640580481</v>
+        <v>5.780473649193823</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.307100176494345</v>
+        <v>4.342454600162831</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.373794668179237</v>
+        <v>2.40998838559814</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.886573663642999</v>
+        <v>6.952246693538676</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.854226081527834</v>
+        <v>5.919700684514105</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.959408729961616</v>
+        <v>10.02580078111156</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.90036627956501</v>
+        <v>10.96710153148044</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.94188234458764</v>
+        <v>11.00858871339514</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.82658351918406</v>
+        <v>13.8942096227245</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.1009427862994</v>
+        <v>14.16826926488643</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.04136107794645</v>
+        <v>15.10903205656038</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.25833327409344</v>
+        <v>10.3273334043384</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.476000853303</v>
+        <v>12.54527891813572</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.03658180938765</v>
+        <v>13.10664781567711</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>11.19261746876513</v>
+        <v>11.2620103473762</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.05852377461621</v>
+        <v>11.12809321039873</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.73402816339896</v>
+        <v>9.803740311455584</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.072102545842988</v>
+        <v>5.141582911892122</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.820121951219512</v>
+        <v>2.889404331616241</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1621028480223501</v>
+        <v>-0.09216622659369733</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>2.200966486578949</v>
+        <v>2.27101220224111</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>3.695253848183029</v>
+        <v>3.764999109845114</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.39980031379261</v>
+        <v>2.469654661499888</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01734</t>
+          <t>X &gt; 0.01733</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>7.195443811640516</v>
+        <v>7.228718103959345</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.512442210039659</v>
+        <v>2.546115218653</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.522017108272365</v>
+        <v>2.557371531940852</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3589484327603643</v>
+        <v>0.395142150179268</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.790780097011677</v>
+        <v>5.856453126907354</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.528669347699633</v>
+        <v>4.594143950685904</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.17290074404008</v>
+        <v>12.23963599595551</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>12.21441680906271</v>
+        <v>12.28112317787021</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.7884074852498</v>
+        <v>15.85603358879024</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.61349139004631</v>
+        <v>14.68081786863333</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.3343974865714</v>
+        <v>14.40206846518534</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.862080181127745</v>
+        <v>8.931080311372703</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.53927409473106</v>
+        <v>11.60855215956379</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.32961821801261</v>
+        <v>12.39968422430207</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>11.47540290531514</v>
+        <v>11.54479578392622</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.34130921116622</v>
+        <v>11.41087864694875</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.787050432752096</v>
+        <v>9.85676258080872</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.206072146408545</v>
+        <v>4.275552512457679</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>2.943840579710141</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-1.947185916244329</v>
+        <v>-1.877249294815677</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>2.324685115069578</v>
+        <v>2.394730830731739</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.048735643870543</v>
+        <v>4.118480905532628</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>2.523518942283239</v>
+        <v>2.593373289990517</v>
       </c>
     </row>
   </sheetData>
@@ -5824,83 +5824,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01971</t>
+          <t>X &lt; -0.0197</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.081760688511068</v>
+        <v>-9.048087679897726</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.42001187723488</v>
+        <v>-13.3846574535664</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.6845298281092</v>
+        <v>-12.64833611069029</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.252698163857879</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.616258188532257</v>
+        <v>-5.550783585545986</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5786978454893585</v>
+        <v>0.6454330974047906</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.052172224895116</v>
+        <v>-2.984546121354676</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.676363682417467</v>
+        <v>-5.609037203830439</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.843621920818016</v>
+        <v>2.912899985650739</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-5.061686129813481</v>
+        <v>-4.991620123524015</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.56807535555442</v>
+        <v>-1.498682476943344</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-4.600719774341023</v>
+        <v>-4.531150338558497</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.705703190436303</v>
+        <v>-4.635991042379679</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.938855389823324</v>
+        <v>-5.86937502377419</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-4.302536231884055</v>
+        <v>-4.233253851487326</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-6.295012003200846</v>
+        <v>-6.225075381772193</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-4.921691696524618</v>
+        <v>-4.851645980862457</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2990904430859729</v>
+        <v>-0.2293451814238878</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>3.972794304602075</v>
+        <v>4.042648652309353</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>85</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.83691210342522</v>
+        <v>-4.803637811106391</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.303414567453942</v>
+        <v>-8.626786702479457</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.74311503154008</v>
+        <v>-10.06480575151045</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-12.63337893296853</v>
+        <v>-11.94055046862761</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.292766365051406</v>
+        <v>-8.787968848151621</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1296923656024376</v>
+        <v>0.1951669685887083</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.709767410019005</v>
+        <v>1.776159461168952</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2547421762651396</v>
+        <v>0.3214774281805717</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8802123469475163</v>
+        <v>-0.8135059781400145</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.006988934187532</v>
+        <v>-3.939362830647092</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.732629667072196</v>
+        <v>-3.665303188485169</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.4823118058412206</v>
+        <v>-0.4146408272272879</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.3613323058481015</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.701251929343172</v>
+        <v>1.770529994175895</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.8400322508706</v>
+        <v>-4.769966244581134</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-3.202595307162852</v>
+        <v>-3.133025871380326</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.660519899728719</v>
+        <v>-5.590807751672095</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.267926148561607</v>
+        <v>-4.198445782512472</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.080882352941174</v>
+        <v>-4.011599972544445</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.800553350174425</v>
+        <v>-5.730616728745773</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.700037817581737</v>
+        <v>-4.629992101919576</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.895850886393724</v>
+        <v>-0.826105624731639</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.557619539043685</v>
+        <v>2.627473886750963</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>107</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.280324957778298</v>
+        <v>-6.75340168955956</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-6.850866543359764</v>
+        <v>-6.339568886738697</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.433818735057592</v>
+        <v>-8.904374758033292</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.191611884567628</v>
+        <v>-4.610535600950939</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6684499247008375</v>
+        <v>0.7339245276871083</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.69932211040382</v>
+        <v>2.765714161553767</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.486188025632927</v>
+        <v>1.552923277548359</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.5931246514032225</v>
+        <v>0.6598310202107243</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.984449077123216</v>
+        <v>-2.916822973582775</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.775510370755541</v>
+        <v>-1.708183892168513</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1854453957257718</v>
+        <v>-0.1177744171118391</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3753571749605769</v>
+        <v>-0.3063570447156181</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.272444892509739</v>
+        <v>1.341722957342462</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-4.059383542789242</v>
+        <v>-3.989317536499776</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.59516461466319</v>
+        <v>-1.525771736052114</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.663837748064452</v>
+        <v>-2.594268312281926</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.572559481916741</v>
+        <v>-5.502847333860117</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.421856879732587</v>
+        <v>-4.352376513683453</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-4.234813084112155</v>
+        <v>-4.165530703715426</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-5.712592932362448</v>
+        <v>-5.642656310933795</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-5.788547988005057</v>
+        <v>-5.718502272342896</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.775455064513579</v>
+        <v>-1.705709802851494</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.952341913974962</v>
+        <v>1.02219626168224</v>
       </c>
     </row>
     <row r="9">
@@ -6074,161 +6074,161 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.511330708076372</v>
+        <v>-2.8716163442012</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.790546920395123</v>
+        <v>-4.744854681012548</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.88649738448126</v>
+        <v>-3.87518142235124</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-5.357366211024747</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.403060482698464</v>
+        <v>-3.385464375879707</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6903541303083216</v>
+        <v>1.088919818565913</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.6987379982542947</v>
+        <v>1.092164933125176</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.201433352735734</v>
+        <v>1.589147286821714</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.100800582241632</v>
+        <v>-0.694946926612424</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.655885993011061</v>
+        <v>-2.243056401098528</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.381526725895725</v>
+        <v>-2.744190557386219</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4643793706293735</v>
+        <v>0.07783523296424022</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1211381521422297</v>
+        <v>0.5050607630073358</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.024781341107875</v>
+        <v>3.384757080359201</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.321649897929426</v>
+        <v>-1.924549007919026</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.726589848308045</v>
+        <v>-1.330162085976035</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.641933542456968</v>
+        <v>-2.239273021403122</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.528166958552248</v>
+        <v>-3.119307523673918</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.312043795620433</v>
+        <v>-2.903416142749592</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.90625</v>
+        <v>-3.491764131231179</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-4.449450408997954</v>
+        <v>-4.034310299197209</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-5.306655464640563</v>
+        <v>-4.885350059055924</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.906880298158434</v>
+        <v>-1.510100152775415</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.3609283625730981</v>
+        <v>0.7396489893501368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.0146</t>
+          <t>X &lt; -0.01459</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>154</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.956172687802081</v>
+        <v>-4.922898395483251</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.622200146201571</v>
+        <v>-5.257675193833066</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.500945436429319</v>
+        <v>-3.490566037735846</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.565388100271818</v>
+        <v>-3.562494416152944</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.580008534646524</v>
+        <v>-5.180336170751509</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4967400255358356</v>
+        <v>-0.7915502989634717</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3998911449435312</v>
+        <v>0.4666263968589632</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8572940887351379</v>
+        <v>-0.7905877199276361</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.929830798205863</v>
+        <v>-2.862204694665422</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.655471531090527</v>
+        <v>-2.588145052503499</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.337162837162829</v>
+        <v>-0.2694918585488963</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4863978924019676</v>
+        <v>0.5553980226469264</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.213093029419568</v>
+        <v>2.282371094252291</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.043240807020332</v>
+        <v>-0.9731748007308667</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.4481807573989514</v>
+        <v>-0.3787878787878753</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.5822744515478746</v>
+        <v>-0.5127050157653485</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.98595916634445</v>
+        <v>-1.916247018287827</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.419186652763294</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.9334415584415581</v>
+        <v>-0.8641591780448294</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.125992616790157</v>
+        <v>-2.056055995361504</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.201947672432766</v>
+        <v>-2.131901956770605</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.6284712072493406</v>
+        <v>-0.5587259455872555</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.243639401534132</v>
+        <v>1.31349374924141</v>
       </c>
     </row>
     <row r="11">
@@ -6241,76 +6241,76 @@
         <v>186</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.801780980218879</v>
+        <v>-5.76850668790005</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.415714032694588</v>
+        <v>-6.103283486249865</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.373728567276956</v>
+        <v>-4.349813173578731</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-4.012253063265817</v>
+        <v>-3.998937405787423</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.377522848289864</v>
+        <v>-4.866642771951724</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.039820600874478</v>
+        <v>-2.264726079539628</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.812686732928505</v>
+        <v>-2.746294681778558</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1345650731658452</v>
+        <v>0.2013003250812773</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.974456496220128</v>
+        <v>-1.907750127412626</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.210657498387413</v>
+        <v>-2.143031394846972</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.936298231272076</v>
+        <v>-1.868971752685049</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.602488908940515</v>
+        <v>-0.5348179303265823</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1140769016212104</v>
+        <v>-0.04507677137625166</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.815103921753035</v>
+        <v>1.884381986585758</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.0809038655114378</v>
+        <v>0.1509698718009034</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.9369393106736297</v>
+        <v>-0.8675464320625537</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.608667413424705</v>
+        <v>-1.539097977642179</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.788919646724288</v>
+        <v>-2.719207498667664</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.110430892394618</v>
+        <v>-3.040950526345483</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.310483870967737</v>
+        <v>-1.241201490571008</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.853684279965691</v>
+        <v>-1.783747658537038</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.9296393356083</v>
+        <v>-1.859593619946139</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.04196094331972233</v>
+        <v>0.02778431834236272</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.9573665346161135</v>
+        <v>1.027220882323391</v>
       </c>
     </row>
     <row r="12">
@@ -6320,79 +6320,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.24677097840037</v>
+        <v>-3.428081155985161</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.653073744429456</v>
+        <v>-4.613921784122205</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.293824970688156</v>
+        <v>-3.498749343791502</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.283480352846823</v>
+        <v>-2.084043788766152</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.355646689595019</v>
+        <v>-1.56877043152619</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3064131110709951</v>
+        <v>-0.2925152837994247</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.2172102776077693</v>
+        <v>0.03417511378192017</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.06473044036771114</v>
+        <v>0.1851482183850663</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.178386789138187</v>
+        <v>-2.348471895837562</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.952222199907617</v>
+        <v>-2.69220302251783</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.539931898309518</v>
+        <v>-3.705697028424574</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.66385338799131</v>
+        <v>-1.40933913573523</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.926275640961215</v>
+        <v>-2.103316653235133</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4234945209610856</v>
+        <v>-0.6076573322568279</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.944494725515632</v>
+        <v>-2.124169728549823</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.21150364141149</v>
+        <v>-2.38815190531929</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.483528370043175</v>
+        <v>-1.663699943584305</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.019546268897074</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-2.234457588723878</v>
+        <v>-2.41101836519362</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.7543103448275943</v>
+        <v>-0.9366189071569195</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.297510753825549</v>
+        <v>-1.47916507512295</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.9424313267095243</v>
+        <v>-1.125826487175829</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.6254472880484627</v>
+        <v>0.4362018733748982</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.84260939705586</v>
+        <v>1.647923268220289</v>
       </c>
     </row>
     <row r="13">
@@ -6405,404 +6405,404 @@
         <v>279</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.319511476672787</v>
+        <v>-3.288734437375631</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.18723286345562</v>
+        <v>-4.327736587838118</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.37756881305269</v>
+        <v>-4.530250734664371</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.948504983388702</v>
+        <v>-3.12306341135092</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.852458374788604</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0876755588797522</v>
+        <v>-0.04766325958797069</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.320888075835697</v>
+        <v>-1.254152823920265</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.636514867955917</v>
+        <v>-1.569808499148415</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.124635993011054</v>
+        <v>-3.057009889470613</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.207419583038586</v>
+        <v>-3.140093104451559</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.057942057942057</v>
+        <v>-1.990271079328124</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6824332764291938</v>
+        <v>-0.6134331461842351</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.167638483965014</v>
+        <v>0.2369165487977369</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.277007040786565</v>
+        <v>-2.206941034497099</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.32480413402233</v>
+        <v>-1.255411255411254</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.7446121138855375</v>
+        <v>-0.6750426781030114</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.713650829519985</v>
+        <v>-1.851311953352763</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.855950605656275</v>
+        <v>-1.992563429571305</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.9520609318996449</v>
+        <v>-1.091431905317556</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.495261340897599</v>
+        <v>-1.633978073283586</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.571216396540208</v>
+        <v>-1.501170680878047</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2211724128537824</v>
+        <v>-0.1514271511916974</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.06130918694585574</v>
+        <v>0.1311635346531332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009488</t>
+          <t>X &lt; -0.009487</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>341</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.079918507200077</v>
+        <v>-2.20406550423656</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.265110873883494</v>
+        <v>-2.390609502559883</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.970863273694093</v>
+        <v>-3.101504232489077</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.352295070852264</v>
+        <v>-1.502319523608115</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.259838908354439</v>
+        <v>-0.5203584672955444</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.968142031182957</v>
+        <v>1.864113617015526</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.19527589912893</v>
+        <v>1.261667950278877</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.04208568509724842</v>
+        <v>0.1088209370126805</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.374124197401983</v>
+        <v>-1.307417828594481</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.73104998718015</v>
+        <v>-2.663423883639709</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.622871478082317</v>
+        <v>-3.555544999495289</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.861149055026601</v>
+        <v>-1.793478076412669</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.944823946983135</v>
+        <v>-0.8758238167381762</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5830903790087447</v>
+        <v>-0.5138123141760218</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.699747565567911</v>
+        <v>-2.629681559278445</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.521597136937778</v>
+        <v>-1.452204258326702</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.655690831086702</v>
+        <v>-1.586121395304176</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.175827777265695</v>
+        <v>-2.274052478134109</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.3772930624826</v>
+        <v>-2.641251476218528</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.603739002932549</v>
+        <v>-1.871315287241757</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.853684279965691</v>
+        <v>-2.122316265703404</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.9296393356083</v>
+        <v>-2.029372906873135</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.4818436412669342</v>
+        <v>-0.4120983796048492</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3219804153590218</v>
+        <v>0.3918347630662993</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.00821</t>
+          <t>X &lt; -0.008209</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>405</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.840380574454954</v>
+        <v>-2.066997234497336</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.803414567453942</v>
+        <v>-2.033876338966252</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.377744313228192</v>
+        <v>-2.615589432832238</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6345351694188821</v>
+        <v>-0.7607433217189197</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2286962740582936</v>
+        <v>0.01683015110918973</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.381462852667049</v>
+        <v>2.303010105843612</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.854296966313264</v>
+        <v>1.920689017463211</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1015408465932239</v>
+        <v>0.168276098508656</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8397440711851232</v>
+        <v>-0.7730377023776214</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.104979973355043</v>
+        <v>-2.037353869814602</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.059121934740929</v>
+        <v>-2.991795456153902</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3898128898128945</v>
+        <v>-0.3221419111989619</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.531503125499043</v>
+        <v>-0.4625029952540842</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.01575919943266513</v>
+        <v>0.05351886540005779</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.411791175570698</v>
+        <v>-1.341725169281233</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.308131617349815</v>
+        <v>-1.238738738738739</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.9508248200982408</v>
+        <v>-0.8812553843157147</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.896393559537465</v>
+        <v>-1.968897070937892</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.784266017842661</v>
+        <v>-1.998705935713808</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.8564814814814881</v>
+        <v>-1.074759388645042</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.152768310232517</v>
+        <v>-1.37160531091083</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.9818097856282151</v>
+        <v>-1.05711467508678</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.0337061215946548</v>
+        <v>0.1034513832567399</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.6985055230669275</v>
+        <v>0.768359870774205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006933</t>
+          <t>X &lt; -0.006932</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.080495907742829</v>
+        <v>-2.257447903945796</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.314686141952002</v>
+        <v>-1.500376387029306</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.048997384481254</v>
+        <v>-2.239039786209595</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2372093023255744</v>
+        <v>0.135828467060584</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.07193951730153</v>
+        <v>0.9081304754840716</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.259104130308316</v>
+        <v>3.205616657446285</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.286237998254293</v>
+        <v>2.35263004940424</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6076833527357266</v>
+        <v>0.6744186046511587</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8491994177583635</v>
+        <v>0.9159057865658653</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.3246359930110643</v>
+        <v>-0.2570098894706234</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.450276725895733</v>
+        <v>-1.382950247308706</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6706293706293707</v>
+        <v>0.7383003492433033</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5461381521422268</v>
+        <v>0.6151382823871856</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.724781341107871</v>
+        <v>0.7940594059405939</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7390898483080477</v>
+        <v>-0.6696969696969717</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.2731835424569695</v>
+        <v>-0.2036141066744435</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.259128882399942</v>
+        <v>-0.3084548104956255</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.3250960044557729</v>
+        <v>-0.4925634295712982</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5847585513078499</v>
+        <v>0.2942823803967229</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.6451798726921822</v>
+        <v>0.3517362124306942</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.7704320605103376</v>
+        <v>0.5969323351899405</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.167716476035118</v>
+        <v>0.9929352446281499</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.898226749669874</v>
+        <v>1.843949209274342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005656</t>
+          <t>X &lt; -0.005655</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.621576249757361</v>
+        <v>-1.76482753757552</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.048770604605657</v>
+        <v>-1.197846134004003</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.906987499802518</v>
+        <v>-2.058487477997723</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01513351978852029</v>
+        <v>-0.0610232097637109</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2574334199921964</v>
+        <v>-0.4689555973019708</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.744912711166414</v>
+        <v>1.61931557539986</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.302079582412709</v>
+        <v>1.272234662254327</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.03694474643781831</v>
+        <v>-0.1591893030918357</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8310175995765476</v>
+        <v>0.801714367423962</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.8836284697988646</v>
+        <v>0.8538811996382876</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1662521997241129</v>
+        <v>0.1378418318992161</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.540050858232675</v>
+        <v>1.607721836846608</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.903162945530653</v>
+        <v>1.972163075775612</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.516516878297956</v>
+        <v>1.585794943130679</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.188164151657354</v>
+        <v>1.258230157946819</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7914886640886465</v>
+        <v>0.8608815426997225</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.483841250931455</v>
+        <v>1.553410686713981</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.314548273235829</v>
+        <v>1.283280726694457</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.9686361380445803</v>
+        <v>0.8380150828253932</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.754568106312291</v>
+        <v>1.520728661388461</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.875819524556867</v>
+        <v>1.63933951821582</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.633751512103622</v>
+        <v>1.499731310624242</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.177458304171019</v>
+        <v>2.041907252060859</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.267906315984078</v>
+        <v>2.234665600645826</v>
       </c>
     </row>
     <row r="18">
@@ -6812,79 +6812,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.043686623142108</v>
+        <v>-2.154360626945483</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.492290117674031</v>
+        <v>-1.607558959143077</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.451722180121585</v>
+        <v>-2.568114505528222</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5011263047685546</v>
+        <v>-0.6313459626164359</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.107295455376061</v>
+        <v>-0.3482570180201847</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.855825441783729</v>
+        <v>1.683762406763975</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7521750707577084</v>
+        <v>0.5820578423197773</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5528888321877901</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6738907757830646</v>
+        <v>0.5027910324675133</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7231006325033391</v>
+        <v>0.5495474875785646</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3115888433772511</v>
+        <v>0.2197857308034799</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9927144186403467</v>
+        <v>0.9793962396542639</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.788662157629197</v>
+        <v>1.857662287874156</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.430131135346556</v>
+        <v>1.499409200179279</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.457070952550687</v>
+        <v>1.527136958840153</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.229085734682357</v>
+        <v>1.298478613293433</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.506514674278286</v>
+        <v>1.576084110060812</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.485569305184022</v>
+        <v>1.47124340623963</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.510858542756459</v>
+        <v>1.412786364667383</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.919765840220386</v>
+        <v>1.736806385883696</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.927529618550253</v>
+        <v>1.742957062910811</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.402538750235472</v>
+        <v>2.301164976296327</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.763378322531224</v>
+        <v>2.661231538469266</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.687436983262756</v>
+        <v>2.671226925156411</v>
       </c>
     </row>
     <row r="19">
@@ -6894,79 +6894,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.261102326065057</v>
+        <v>-1.350344320135875</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.9755890552265782</v>
+        <v>-1.067346506860083</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.130662176382273</v>
+        <v>-2.222153599110648</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5321600670437903</v>
+        <v>-0.6333234376546173</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0455351162948503</v>
+        <v>-0.2334312238465586</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.446914514055493</v>
+        <v>1.252668620935047</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5133566423220941</v>
+        <v>0.3204590707765718</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.07374670115201809</v>
+        <v>-0.1183741881416225</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6333443781207748</v>
+        <v>0.4385664404553822</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.199259816728464</v>
+        <v>0.06940094574382982</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.319132898036159</v>
+        <v>-0.3818203038058741</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.258475952133935</v>
+        <v>-0.256269786503303</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.202536793138826</v>
+        <v>0.2715369233837848</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.4341811146073127</v>
+        <v>0.5034591794400356</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.3415012911985542</v>
+        <v>0.4115672974880198</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.03055907581426709</v>
+        <v>0.0999519544253431</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.2362162310424694</v>
+        <v>0.3057856668249954</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.1991573044862989</v>
+        <v>0.2009449630038134</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.4833591555713994</v>
+        <v>0.4168363439281393</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.19318181818182</v>
+        <v>1.056683286398993</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.104526863729319</v>
+        <v>0.9671382509357969</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.483117262632163</v>
+        <v>1.413758731747215</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.714066800817676</v>
+        <v>1.644349072470732</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.935885651866954</v>
+        <v>1.865441801189469</v>
       </c>
     </row>
     <row r="20">
@@ -6976,817 +6976,817 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.171846610482376</v>
+        <v>-1.238308582153635</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4573843520891074</v>
+        <v>-0.5273480497128205</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.845533391773877</v>
+        <v>-0.9177301542732579</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.315311492106602</v>
+        <v>0.2370393833808464</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.09294408351157557</v>
+        <v>-0.04746479584191121</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.337349102886016</v>
+        <v>1.192702594861082</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2512883184738754</v>
+        <v>0.1085097212365085</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3915661366185148</v>
+        <v>0.2474113053810925</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6693644040095137</v>
+        <v>0.5241249646480597</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2621651068972781</v>
+        <v>0.1696811525769064</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3800659101303694</v>
+        <v>-0.4178999270891168</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.01754661470518215</v>
+        <v>-0.003091592148628308</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2254475490493419</v>
+        <v>-0.1564474188043832</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1948088388163995</v>
+        <v>0.2640869036491225</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.08583177026489608</v>
+        <v>0.1558977765543617</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.05238040742811734</v>
+        <v>0.01701247118295868</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.1864741015770406</v>
+        <v>-0.1169046657945145</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.23688255488252</v>
+        <v>-0.2217453696156966</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.1257431648937981</v>
+        <v>0.08580503972293485</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.01102941176471</v>
+        <v>0.9142640485910505</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.9833635284445492</v>
+        <v>0.8300130226965052</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.331811386188164</v>
+        <v>1.176807682214253</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.478776383869217</v>
+        <v>1.323735027782803</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.182538141170888</v>
+        <v>1.028209180868615</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005466</t>
+          <t>X &lt; -0.0005469</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.662198902025011</v>
+        <v>-1.709197782079805</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4671641836315104</v>
+        <v>-0.5183748411498073</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5236242501528992</v>
+        <v>-0.5773334370032472</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.073206315021622</v>
+        <v>0.01636653426421475</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.474248823505647</v>
+        <v>-0.5756512381977146</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.026344220061503</v>
+        <v>0.9207010300880327</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1467170401704649</v>
+        <v>0.04218228821021341</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.0889458607474154</v>
+        <v>-0.1933931951994623</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2204138105619649</v>
+        <v>0.1150089255793247</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4034965627261968</v>
+        <v>-0.4653868528214034</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8787624830171623</v>
+        <v>-0.8967227023985131</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.082893867751437</v>
+        <v>-1.057954332404634</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.157909823869765</v>
+        <v>-1.088909693624807</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7795664849790782</v>
+        <v>-0.7102884201463553</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.7638350553507181</v>
+        <v>-0.6937690490612525</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.143287749357519</v>
+        <v>-1.073894870746443</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.502268999728329</v>
+        <v>-1.432699563945803</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.638632074831314</v>
+        <v>-1.612502786507619</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.078560312136958</v>
+        <v>-1.096761330620772</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6221825694966228</v>
+        <v>-0.6850279644308657</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.6700801082460686</v>
+        <v>-0.7777990199531075</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.1747423720897743</v>
+        <v>-0.2841997714840261</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.005524876471689311</v>
+        <v>-0.1151005019618125</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1871829787984183</v>
+        <v>-0.2964665384048288</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007307</t>
+          <t>X &lt; 0.0007301</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.438971375132304</v>
+        <v>-1.472246013859582</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5166498615715938</v>
+        <v>-0.5526410266962003</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8812475377614533</v>
+        <v>-0.9182301167760798</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5799686117848424</v>
+        <v>-0.6186410439030112</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.358631385092572</v>
+        <v>-0.4305442194898674</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.152961624165812</v>
+        <v>1.077519909765179</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1081187603932037</v>
+        <v>0.03417511378192017</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1352440765385552</v>
+        <v>-0.209016978170915</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1200313514724058</v>
+        <v>-0.1938548027527318</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3660153033558871</v>
+        <v>-0.4403022727629988</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7074195830385861</v>
+        <v>-0.745457930160569</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5554790037548685</v>
+        <v>-0.5586246200063911</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6947485473651582</v>
+        <v>-0.6617847945358903</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.039258067759114</v>
+        <v>-0.9699800029263912</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.9592730506387923</v>
+        <v>-0.8892070443493267</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.103129257175034</v>
+        <v>-1.033736378563958</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.139603751945565</v>
+        <v>-1.106077160861631</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.393456724273577</v>
+        <v>-1.395646928722229</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.8945545914254893</v>
+        <v>-0.9334501290786861</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7947530864197532</v>
+        <v>-0.8697570284702607</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.74587181109802</v>
+        <v>-0.8217696409272861</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.279693165505833</v>
+        <v>-1.354442671296525</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.030450180656885</v>
+        <v>-1.105526461542617</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.31759886514967</v>
+        <v>-1.392133956386289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002008</t>
+          <t>X &lt; 0.002007</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9336870727621687</v>
+        <v>-0.982096468104146</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5690486017194942</v>
+        <v>-0.6181858952528572</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.308210634998851</v>
+        <v>-1.35679541559314</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.233220526778517</v>
+        <v>-0.2837841570910911</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5176977883979461</v>
+        <v>-0.5389523777898617</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.26874643201905</v>
+        <v>0.1945580293608486</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1116873129490301</v>
+        <v>-0.1856402768515792</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4644494962523282</v>
+        <v>-0.5380166285094532</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6529812675998912</v>
+        <v>-0.7262922435015184</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5661944345695105</v>
+        <v>-0.6399974413378473</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4996273752463765</v>
+        <v>-0.5437182805209488</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8306693306693305</v>
+        <v>-0.8446695365303185</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5525631465590735</v>
+        <v>-0.53551106826216</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.929764113437578</v>
+        <v>-0.8300570181758218</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.9133706771502048</v>
+        <v>-0.8644996920557588</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.327031636249828</v>
+        <v>-1.309613809613808</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.430853849269248</v>
+        <v>-1.443530946591281</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.765679965836334</v>
+        <v>-1.756271858312672</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.623470136068114</v>
+        <v>-1.644330581338451</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.354166666666664</v>
+        <v>-1.427402486997963</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.241806453812963</v>
+        <v>-1.315485431690014</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.443581950563399</v>
+        <v>-1.517030102960703</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.346923334152173</v>
+        <v>-1.420468369829685</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.653359215715</v>
+        <v>-1.726509499203729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003285</t>
+          <t>X &lt; 0.003284</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6857181943324164</v>
+        <v>-0.7022896779911889</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9080028552456412</v>
+        <v>-0.9243989674610731</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7614973844812596</v>
+        <v>-0.7790618556434268</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3342958338959434</v>
+        <v>-0.3530793699122228</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5852544058441325</v>
+        <v>-0.6193901289847616</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1048654718374138</v>
+        <v>-0.1397675406902437</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3606314114058122</v>
+        <v>-0.395584236310043</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5690504280248874</v>
+        <v>-0.6038306137499134</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6811497317492368</v>
+        <v>-0.715729602174072</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6235164229259738</v>
+        <v>-0.6587085930915393</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.886550796652557</v>
+        <v>-0.8956514995448401</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.165644700127459</v>
+        <v>-1.148947972904345</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.036217423316799</v>
+        <v>-0.9932771160013516</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.436705447965124</v>
+        <v>-1.367427383132402</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.737374259774477</v>
+        <v>-1.667308253485011</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.608982321426318</v>
+        <v>-1.56553216898044</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.672287083469961</v>
+        <v>-1.654666502554427</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.020319424919961</v>
+        <v>-2.028204026796566</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.778284262197367</v>
+        <v>-1.81231264587224</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.565305206463194</v>
+        <v>-1.599624429639114</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.678415945594274</v>
+        <v>-1.712898480532097</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.773131205880453</v>
+        <v>-1.807517820727284</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.427245466697762</v>
+        <v>-1.462106997016761</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.701796457570779</v>
+        <v>-1.7362392825383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.004563</t>
+          <t>X &lt; 0.004561</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2981725443844354</v>
+        <v>-0.310173000946925</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9317589507708206</v>
+        <v>-0.9429024433061173</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7908606391793853</v>
+        <v>-0.8028645176989997</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3627906976744129</v>
+        <v>-0.3757982582107857</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5056515191130302</v>
+        <v>-0.5295069094548026</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1759639241352389</v>
+        <v>-0.2002813786158768</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.005231765462163196</v>
+        <v>-0.03017682784486198</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3410345959822152</v>
+        <v>-0.3655813953488334</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4770530872516545</v>
+        <v>-0.5013811282000376</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5865445736044848</v>
+        <v>-0.6110531240582873</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.8735325398492151</v>
+        <v>-0.8746602993711647</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8719528266440832</v>
+        <v>-0.8501611892182339</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.753460885548229</v>
+        <v>-0.7079078097971774</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.014913927536874</v>
+        <v>-0.945635862704151</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.249272240488587</v>
+        <v>-1.202816850741804</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.071995145258285</v>
+        <v>-1.049488469296008</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.142472984448133</v>
+        <v>-1.143309375319191</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.344432018793206</v>
+        <v>-1.368438772003245</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.104832064001315</v>
+        <v>-1.129145860377555</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.8540996784565849</v>
+        <v>-0.8787513274684429</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.172723931313996</v>
+        <v>-1.197119668741522</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.184823203980869</v>
+        <v>-1.2092503112274</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.047348104999479</v>
+        <v>-1.071892971409966</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.099669463513855</v>
+        <v>-1.124181116086184</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.00584</t>
+          <t>X &lt; 0.005838</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2712</v>
+        <v>2715</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.08962981833309414</v>
+        <v>-0.1150889840932692</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4783785157116185</v>
+        <v>-0.5034016895595599</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4343560960478712</v>
+        <v>-0.4593467999352612</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2492059301899801</v>
+        <v>-0.2743658171245755</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.520734475372457</v>
+        <v>-0.553130226311751</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3130468407433469</v>
+        <v>-0.345699451185645</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2222664005726784</v>
+        <v>-0.254986208376792</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2966070763071684</v>
+        <v>-0.3292443990118414</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4909326438703872</v>
+        <v>-0.5233760016349294</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3998653508092218</v>
+        <v>-0.4323764583855692</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6759647992902202</v>
+        <v>-0.6872406763515997</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5302516866393532</v>
+        <v>-0.5415235685850135</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4951398500612214</v>
+        <v>-0.505962635044007</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6581723693991037</v>
+        <v>-0.6687893458949361</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7074685307849933</v>
+        <v>-0.7395611309938559</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.6787957306609869</v>
+        <v>-0.7109749719004199</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.7176851974771949</v>
+        <v>-0.7498301243085379</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8377696075588688</v>
+        <v>-0.8697925539722888</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5263426546561263</v>
+        <v>-0.5587399001595301</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.464837997054488</v>
+        <v>-0.4973321837812748</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.728513484504397</v>
+        <v>-0.7606994019916726</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.8563514852743168</v>
+        <v>-0.888408608014096</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.85465490191811</v>
+        <v>-0.8867484385582003</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9826372716451957</v>
+        <v>-1.014601728025333</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.007117</t>
+          <t>X &lt; 0.007116</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2875</v>
+        <v>2879</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1199461124450707</v>
+        <v>-0.1260297460990856</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4021170791800728</v>
+        <v>-0.4078886480796058</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4075609203928607</v>
+        <v>-0.4136429608127656</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3078684178816644</v>
+        <v>-0.3142478943638238</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5156209526362687</v>
+        <v>-0.5272597785446749</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3782273594946588</v>
+        <v>-0.3900225784071694</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4747578523681142</v>
+        <v>-0.4865964699327705</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4570001477831198</v>
+        <v>-0.4689319998393415</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2919770528298713</v>
+        <v>-0.3041356785343439</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1807107593662067</v>
+        <v>-0.193200694862945</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2325481940397651</v>
+        <v>-0.2449142860362272</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1453041243481152</v>
+        <v>-0.1578601488542404</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1755527695486947</v>
+        <v>-0.1883219252252601</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2724456952872671</v>
+        <v>-0.2851375480227034</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.2867157786506525</v>
+        <v>-0.2995409553518726</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.2258744476836938</v>
+        <v>-0.2386612925234317</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.2352931885360832</v>
+        <v>-0.2481047511650942</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.4931964621968206</v>
+        <v>-0.5056818468907665</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.2564882400648756</v>
+        <v>-0.2692624586975185</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1530479333101766</v>
+        <v>-0.1659326733667115</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.2239683033690483</v>
+        <v>-0.2368828021425173</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2096577239384416</v>
+        <v>-0.2226172116649749</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.1574887821639948</v>
+        <v>-0.1704683698296776</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3170607678616904</v>
+        <v>-0.3298438093444958</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.008394</t>
+          <t>X &lt; 0.008393</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3013</v>
+        <v>3015</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4791279933660775</v>
+        <v>-0.4808734465458571</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6649806106751939</v>
+        <v>-0.6664372143830377</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5379888149361065</v>
+        <v>-0.5388076511948512</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3764405493064586</v>
+        <v>-0.3770088418700155</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6903296119860656</v>
+        <v>-0.6944243677665298</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4517503731558818</v>
+        <v>-0.4561004622214</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6121118367291984</v>
+        <v>-0.6159715337092138</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4758425634082073</v>
+        <v>-0.4466635464540829</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4155297764292101</v>
+        <v>-0.4194077447872644</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3446558146166083</v>
+        <v>-0.3481950991107681</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4477651594714089</v>
+        <v>-0.4513782525927184</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3773045136681432</v>
+        <v>-0.3808275001124883</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3252904192863397</v>
+        <v>-0.2952384525764629</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3948349341154156</v>
+        <v>-0.3646182800098217</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.3724027106362442</v>
+        <v>-0.3749304524865167</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.3202881270237015</v>
+        <v>-0.2900740785292513</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4016603636490146</v>
+        <v>-0.3713176142852959</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5863815991617258</v>
+        <v>-0.5558563331702331</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4831836233208904</v>
+        <v>-0.4528283302335439</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.4091398740470709</v>
+        <v>-0.3789206669699539</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3691287909608221</v>
+        <v>-0.3717893011544575</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.4253329107433785</v>
+        <v>-0.3947759737049523</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.4957572059222031</v>
+        <v>-0.465284903870355</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.4524739772875037</v>
+        <v>-0.4551521985090119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.009672</t>
+          <t>X &lt; 0.00967</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3099</v>
+        <v>3103</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4710464537969159</v>
+        <v>-0.4738605491325458</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5969290895716668</v>
+        <v>-0.5996239117817765</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5772025126863838</v>
+        <v>-0.5800962258575879</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3436178858757586</v>
+        <v>-0.346897972890801</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5306262299723556</v>
+        <v>-0.5366987916881172</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3896607076769243</v>
+        <v>-0.3958954736903451</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5669070595120687</v>
+        <v>-0.5730109762367874</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3457676906029548</v>
+        <v>-0.3521924886479724</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3501583214837609</v>
+        <v>-0.3565765739216289</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3347227260659906</v>
+        <v>-0.3412575635161801</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3309965202401912</v>
+        <v>-0.3375073718273072</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3023053770401845</v>
+        <v>-0.308890661992649</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2828007546101787</v>
+        <v>-0.2895502211452481</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4208603443215253</v>
+        <v>-0.4274632410237516</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3529401167196511</v>
+        <v>-0.3597137116913771</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.3501616217229113</v>
+        <v>-0.3568715116448899</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.465198996417044</v>
+        <v>-0.4717813092467864</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5511138184556259</v>
+        <v>-0.5576024463914138</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4769922492286796</v>
+        <v>-0.4835544205622924</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3353609410248097</v>
+        <v>-0.3420871078556047</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.2792577913319292</v>
+        <v>-0.2861259897586166</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.303733020267785</v>
+        <v>-0.3105831789300879</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.4290577175132739</v>
+        <v>-0.4357175107231512</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.453598500931264</v>
+        <v>-0.4602400902352528</v>
       </c>
     </row>
     <row r="30">
@@ -7796,161 +7796,161 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3163</v>
+        <v>3167</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4726148144136957</v>
+        <v>-0.4747029128050002</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6654978623103531</v>
+        <v>-0.6673768123775758</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6123139673958278</v>
+        <v>-0.6143957838993472</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4292060291227315</v>
+        <v>-0.4315859981406689</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4941195650366126</v>
+        <v>-0.4987967434493683</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4779596861016131</v>
+        <v>-0.482642616783906</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.509988416840045</v>
+        <v>-0.5147066340128461</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4247167730899974</v>
+        <v>-0.4295713419401039</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3023424324618986</v>
+        <v>-0.3073500273876206</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3342677210563849</v>
+        <v>-0.3393110526268615</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3880601012105913</v>
+        <v>-0.3930131403904582</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2711029128351967</v>
+        <v>-0.2762325227290177</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3061617848457914</v>
+        <v>-0.3113563683365328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4459088574423902</v>
+        <v>-0.4509516107418108</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3926618777528788</v>
+        <v>-0.3978370402545721</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.2833345660626989</v>
+        <v>-0.288594607492243</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4302813342550706</v>
+        <v>-0.4353721407009061</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4219031529353288</v>
+        <v>-0.4270176847471205</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3764377350143775</v>
+        <v>-0.3815924333544061</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2338569624250084</v>
+        <v>-0.2391770961091026</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1266653489853198</v>
+        <v>-0.1321754594935882</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.08894219449838658</v>
+        <v>-0.09451050631510327</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2061059618752523</v>
+        <v>-0.2115037233650341</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2316162943981297</v>
+        <v>-0.2369923923403974</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01223</t>
+          <t>X &lt; 0.01222</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3223</v>
+        <v>3227</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4085637963854225</v>
+        <v>-0.4100778826627405</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5116081684690812</v>
+        <v>-0.5130200336654411</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5784671748635049</v>
+        <v>-0.5798991184482389</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4119427174092323</v>
+        <v>-0.4136311656574208</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5132548071895116</v>
+        <v>-0.5166080319771496</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4630803806450885</v>
+        <v>-0.4664844408194284</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4162311375481735</v>
+        <v>-0.4197497286475453</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4611650572673582</v>
+        <v>-0.4646501588394329</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4329500572261864</v>
+        <v>-0.4364692905470235</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4786675036690795</v>
+        <v>-0.4821873038489031</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5264201127931258</v>
+        <v>-0.5298638275556087</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.447763210514367</v>
+        <v>-0.4513260786665398</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4412458923846714</v>
+        <v>-0.4448987775263333</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5516182877198332</v>
+        <v>-0.5551528276089854</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.5116251454541754</v>
+        <v>-0.5152581808859438</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4242647167698195</v>
+        <v>-0.4279659032363767</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4471773505065073</v>
+        <v>-0.4508620967795736</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4718801824605805</v>
+        <v>-0.4755442011544488</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3922792355212934</v>
+        <v>-0.3960287761059504</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3108537341183748</v>
+        <v>-0.3146931689687946</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.21578255406925</v>
+        <v>-0.2197808154330829</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2732252320824173</v>
+        <v>-0.2771602290031794</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2590825314090495</v>
+        <v>-0.2630179361245979</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.3165751279636666</v>
+        <v>-0.3204471471723664</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3276</v>
+        <v>3280</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2943093414888978</v>
+        <v>-0.2954035772527419</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3404066838881477</v>
+        <v>-0.3414627973057094</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5506049064709444</v>
+        <v>-0.5514799798978984</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.276868367577336</v>
+        <v>-0.2781121317706692</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4127342308016537</v>
+        <v>-0.4151003961189375</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4210415891816623</v>
+        <v>-0.4233897324422173</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4784750293800784</v>
+        <v>-0.4807942757398251</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5575657359641397</v>
+        <v>-0.5598046963197092</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4987799198289906</v>
+        <v>-0.5010896610820836</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5258517984821864</v>
+        <v>-0.5281695737450605</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.5988325179297718</v>
+        <v>-0.6010492451829705</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4955506780324299</v>
+        <v>-0.4979086422512253</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.476861543628992</v>
+        <v>-0.4793010977404322</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5281705761167146</v>
+        <v>-0.5305606548496726</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5298881018868116</v>
+        <v>-0.5323113163891193</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4647902137160784</v>
+        <v>-0.4672638796726361</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4895100730692121</v>
+        <v>-0.4919621443988049</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4850530036467049</v>
+        <v>-0.4875175006964767</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3422937194241484</v>
+        <v>-0.3449226380948929</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2591463414634134</v>
+        <v>-0.2618686549260474</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2048731750851687</v>
+        <v>-0.2076911406000619</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2626118404794866</v>
+        <v>-0.2653650810929733</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2747663219606906</v>
+        <v>-0.2774923970571521</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.3020371441424103</v>
+        <v>-0.3047355824025502</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2325824817952835</v>
+        <v>-0.2334619438132322</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3412271669375215</v>
+        <v>-0.3419902781481454</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3512530235790052</v>
+        <v>-0.3520629067424821</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2361962331738141</v>
+        <v>-0.2371739033324403</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3739828420123388</v>
+        <v>-0.3758229803050384</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3204262730631342</v>
+        <v>-0.3223244537168313</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.47419560608175</v>
+        <v>-0.4759413791671889</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4947262858184871</v>
+        <v>-0.4964598550359582</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4360672288219334</v>
+        <v>-0.4378709212282956</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4995606464167253</v>
+        <v>-0.5013205457018088</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5093059691878565</v>
+        <v>-0.5110441949148381</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4393826920967996</v>
+        <v>-0.4412177230458525</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.4322253813669548</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.452889147727376</v>
+        <v>-0.4547651871877889</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4903225511138558</v>
+        <v>-0.4921815702652239</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4509255971003157</v>
+        <v>-0.4528091530504099</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4463638505209957</v>
+        <v>-0.4482596572023425</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4126080461655448</v>
+        <v>-0.4145501635433035</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2994266907549132</v>
+        <v>-0.3014979300240626</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2758464328899564</v>
+        <v>-0.2779398418254928</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1963981713202969</v>
+        <v>-0.1986111146608209</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2542885559896249</v>
+        <v>-0.2564360329663202</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2942668337106227</v>
+        <v>-0.2963561002618391</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2916896761678203</v>
+        <v>-0.2937865158381214</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3329</v>
+        <v>3333</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3029996873737062</v>
+        <v>-0.3035407963878711</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2044625425974473</v>
+        <v>-0.2051321085030935</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1952660411976765</v>
+        <v>-0.1959923943249962</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1759289478983632</v>
+        <v>-0.1767013643891318</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2855276272623826</v>
+        <v>-0.2869697917049407</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2608241636863013</v>
+        <v>-0.2622908578722161</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3594284691695009</v>
+        <v>-0.3608027864166559</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.381853269087884</v>
+        <v>-0.383210538376602</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3830972329593365</v>
+        <v>-0.3844526363731973</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4518869651917328</v>
+        <v>-0.4531855691837947</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.459492764196149</v>
+        <v>-0.4607745150911242</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4819596745666814</v>
+        <v>-0.4832243144338264</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3616462789955008</v>
+        <v>-0.363091382684587</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4156199766519393</v>
+        <v>-0.4170084971404719</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4277388733638148</v>
+        <v>-0.4291347593838282</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.3841602708432603</v>
+        <v>-0.38559041477329</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3806175952147655</v>
+        <v>-0.3820572204468959</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3478821009810318</v>
+        <v>-0.3493652627268276</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.23390942249506</v>
+        <v>-0.2355232857726222</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1790804080407966</v>
+        <v>-0.1807550783985974</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.104274838769868</v>
+        <v>-0.1060575525573171</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.162273147018233</v>
+        <v>-0.1639898089484149</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1998607786389215</v>
+        <v>-0.2015246585719339</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1678058669252565</v>
+        <v>-0.1695116941600716</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01734</t>
+          <t>X &lt; 0.01733</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3342</v>
+        <v>3346</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1822937683065149</v>
+        <v>-0.1828477070799366</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1151233175413751</v>
+        <v>-0.115766429596512</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1412364567381701</v>
+        <v>-0.1418876890574978</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1247181218267102</v>
+        <v>-0.1254086261259886</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2352904737725439</v>
+        <v>-0.2365330694446897</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2099434887392988</v>
+        <v>-0.2112119920324034</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3111421744161476</v>
+        <v>-0.3123119666528567</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3643237943756432</v>
+        <v>-0.3654386231894051</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3653969480444346</v>
+        <v>-0.3665101610687671</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4369125126773312</v>
+        <v>-0.4379622704230073</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.4136150269389418</v>
+        <v>-0.414685882914533</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4072477909687109</v>
+        <v>-0.4083345524839146</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2917383763397225</v>
+        <v>-0.2929939785600837</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3463403772692146</v>
+        <v>-0.3475377335111247</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.360947868684427</v>
+        <v>-0.3621464847845175</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3450599975617763</v>
+        <v>-0.3462622648669083</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3420399174942901</v>
+        <v>-0.3432502534087121</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3098276515032552</v>
+        <v>-0.3110801088249744</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1954468431256586</v>
+        <v>-0.1968308124420801</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1699790794979066</v>
+        <v>-0.1713892613943173</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.06767724008913234</v>
+        <v>-0.06922526860842027</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1556387182290777</v>
+        <v>-0.1570846593726714</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1920096729714729</v>
+        <v>-0.1934055772791368</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.1603725051707698</v>
+        <v>-0.1618091904966761</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_10.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_10.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01906</t>
+          <t>X ≈ -0.01904</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.4641300633537</v>
+        <v>8.897229458236644</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.309844614503561</v>
+        <v>-3.762405735859232</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.5909960065134</v>
+        <v>7.412114907771375</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-9.587866890465321</v>
+        <v>-5.600658287663521</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-16.15572414135791</v>
+        <v>-12.09182512981543</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>24.84028999612825</v>
+        <v>31.57660666849902</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.64266126930998</v>
+        <v>18.35712141290827</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.07104776057777</v>
+        <v>5.618365621602081</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.029899767249972</v>
+        <v>-0.4744947166814839</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.0234921462458</v>
+        <v>-7.49130193660433</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>4.698714639315646</v>
+        <v>5.229611839670355</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.422073925674951</v>
+        <v>4.955274377205356</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.303945304163626</v>
+        <v>3.845510213150895</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-3.14699692002408</v>
+        <v>-2.632398942459126</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-3.803815394285856</v>
+        <v>-3.312953343132129</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.022853709798227</v>
+        <v>3.481037735737601</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.890278311038529</v>
+        <v>3.378594037749373</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.691016493847513</v>
+        <v>-9.230699919877281</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>3.002945754065657</v>
+        <v>-2.778614023494228</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-3.052078049009921</v>
+        <v>-2.565131003265506</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-3.595006706113914</v>
+        <v>-9.377292339464816</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-3.671909047909914</v>
+        <v>-9.455299603138023</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-3.398645585288804</v>
+        <v>-9.214628190722983</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.475467289719624</v>
+        <v>-9.379530298635864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01779</t>
+          <t>X ≈ -0.01777</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8992142106376804</v>
+        <v>0.996534698336319</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5672293843829337</v>
+        <v>0.753529685402377</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.17431758610406</v>
+        <v>8.54085533549658</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.94846112459205</v>
+        <v>3.436405558049422</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.65659454218843</v>
+        <v>12.20225245032582</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.799587741383689</v>
+        <v>3.318243030124066</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.554484455906909</v>
+        <v>7.05010709032603</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.279813607414589</v>
+        <v>6.748987870840672</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.323169837942366</v>
+        <v>6.878786818727001</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.029488271259041</v>
+        <v>1.561922820126696</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.830420202334182</v>
+        <v>6.361329141442958</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.02511930779373</v>
+        <v>1.558212511077166</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09397517201595917</v>
+        <v>0.4474904649914535</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3145475130519202</v>
+        <v>0.2000942736723914</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.9704968909294678</v>
+        <v>-0.4795941310391285</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-4.912586410168359</v>
+        <v>-4.454548883893814</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.5116839258838368</v>
+        <v>-0.02342757620095881</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.15359154140247</v>
+        <v>-4.693224871593578</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.939646161014196</v>
+        <v>-4.48055546473396</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.754523115422451</v>
+        <v>-4.267595187781687</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.297970340829849</v>
+        <v>-4.83582899891524</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.918107348017458</v>
+        <v>-9.455234337665289</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.102664553102805</v>
+        <v>-4.670505915361119</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-5.180012744264047</v>
+        <v>-4.834075753183775</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01651</t>
+          <t>X ≈ -0.01649</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8991424749272738</v>
+        <v>-1.358721610305821</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.083784927594102</v>
+        <v>7.035826174474721</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.173673382855448</v>
+        <v>10.11120606365616</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.98689677643428</v>
+        <v>13.84753107650369</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.614375394205801</v>
+        <v>4.930821543776233</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.79937599693752</v>
+        <v>5.087027099176574</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.012154755479671</v>
+        <v>-4.354255633050009</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.755971615822105</v>
+        <v>3.995055143206322</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.25161698145515</v>
+        <v>-4.532360958391415</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.029429458859603</v>
+        <v>3.332995891189455</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.752514811095814</v>
+        <v>-5.056602545793503</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.025064739622628</v>
+        <v>-1.001754986128695</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.436313770770184</v>
+        <v>6.553649693444392</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.2804501218578</v>
+        <v>14.97755718000067</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>8.095616948448956</v>
+        <v>9.966323238867339</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.378015523410518</v>
+        <v>1.85445433907573</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.511670282410158</v>
+        <v>1.751477195360145</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>8.45804420978989</v>
+        <v>10.29947217753754</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.137550931824741</v>
+        <v>6.175374987662039</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.2145181930652171</v>
+        <v>2.048952901541661</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.784711381394175</v>
+        <v>1.482615536404033</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.8326476830644367</v>
+        <v>-2.937355932970057</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.5585725732944553</v>
+        <v>-2.69479894265524</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.6345581988115612</v>
+        <v>-2.857791168201516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01523</t>
+          <t>X ≈ -0.01522</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-15.6880519395819</v>
+        <v>-11.15615447901305</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-8.089160472678827</v>
+        <v>-7.5826067314499</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.622826559001012</v>
+        <v>-1.188690273033053</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.594313282135538</v>
+        <v>5.868160737130466</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-14.64504474546028</v>
+        <v>-13.52465361985772</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-10.46625398079904</v>
+        <v>-9.548868565130483</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.02202201778001</v>
+        <v>-6.516655421762742</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.300450197179615</v>
+        <v>-6.822093997888395</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.278623565732872</v>
+        <v>-2.867427908551335</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.031231494837058</v>
+        <v>-7.490624949917724</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.7759019627456</v>
+        <v>-3.39066554089348</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.054571479861536</v>
+        <v>0.1645985706332027</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8119569061182759</v>
+        <v>-0.9466337099861306</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.396271925886694</v>
+        <v>-5.02907346544508</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>3.924990463444125</v>
+        <v>1.961111532220492</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>4.519072807958793</v>
+        <v>2.521659028286415</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>8.378352388034571</v>
+        <v>6.256868675378861</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.283685748971237</v>
+        <v>2.287086930999898</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.5066643629044165</v>
+        <v>-1.338399660299515</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>12.67876177640319</v>
+        <v>10.39994933962545</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>8.144288257571354</v>
+        <v>9.836169870448316</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>12.06853878471801</v>
+        <v>13.6077775531494</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>4.349015612801466</v>
+        <v>6.165391237249203</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.274532710281285</v>
+        <v>6.005085085978102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01396</t>
+          <t>X ≈ -0.01394</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>32</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-9.825655860443028</v>
+        <v>-9.722583451433586</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.16154070478629</v>
+        <v>-9.969372135302791</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.488260173655895</v>
+        <v>-8.114953998016524</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-6.092361704733648</v>
+        <v>-5.600365516575437</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.319243730035382</v>
+        <v>-2.768800363540876</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.351621941907453</v>
+        <v>-8.83077114840949</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-16.33700358519732</v>
+        <v>-15.84230704435527</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.070964071356528</v>
+        <v>-0.6021321228758012</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.250783915019795</v>
+        <v>-6.695690883086947</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.312383789926955</v>
+        <v>1.844740060927577</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.585688645589265</v>
+        <v>2.116396866693236</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.805371755784236</v>
+        <v>-1.272422363089063</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.925367581056058</v>
+        <v>-2.384030103668387</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.0315216591114762</v>
+        <v>0.4830783623623418</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.545281457340515</v>
+        <v>6.036273078431243</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.211971406645461</v>
+        <v>-2.753929261885958</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-6.464788189777394</v>
+        <v>-5.976640560715417</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-6.571282717215297</v>
+        <v>-6.110945023970913</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.357719995732957</v>
+        <v>-5.898652741345032</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.052025317448582</v>
+        <v>-2.56508907342031</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.4728372168787089</v>
+        <v>-0.01066862451136785</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.5487759889060229</v>
+        <v>-0.08586611966219238</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.849456197015812</v>
+        <v>3.28163019165293</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3504672897210455</v>
+        <v>-0.004530298637284602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01268</t>
+          <t>X ≈ -0.01266</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.896669320884484</v>
+        <v>6.116884828029832</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.336927280301246</v>
+        <v>1.54840739482318</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.09298927235197851</v>
+        <v>0.2768827913747671</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.544786670118334</v>
+        <v>5.202644449588107</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11.56181030708025</v>
+        <v>11.4138490380689</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7.514269938488425</v>
+        <v>7.248581789723808</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.97928352124416</v>
+        <v>10.78475804731642</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1199707158386332</v>
+        <v>-0.3316913771154617</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.073445578292876</v>
+        <v>-4.531162623724228</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.844178710193191</v>
+        <v>-5.325219048918022</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-10.92982674608375</v>
+        <v>-11.55119710096735</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.85223492026774</v>
+        <v>-5.333200411692708</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-10.21376606091385</v>
+        <v>-10.77894596488091</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.43766272650421</v>
+        <v>-11.029962910583</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-11.09686568161558</v>
+        <v>-11.71320435245691</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-8.384944227190893</v>
+        <v>-8.988203041699649</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.152123740647028</v>
+        <v>-2.586989735899699</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1336512736200817</v>
+        <v>-0.5504221445791941</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.08187369051708515</v>
+        <v>-0.3364503394579472</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.2683604762348963</v>
+        <v>-0.1224044572049792</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2735464332390407</v>
+        <v>-0.6893764176674395</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.77689818816971</v>
+        <v>1.40777091681862</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.051811968367694</v>
+        <v>1.65168015997039</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.104319944323407</v>
+        <v>3.663947962231781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0114</t>
+          <t>X ≈ -0.01139</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.788116438295916</v>
+        <v>-3.593646942188812</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.147134836498601</v>
+        <v>-3.846179619264056</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.949104972623061</v>
+        <v>-11.20420588229879</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-8.524529279968256</v>
+        <v>-5.71789283745678</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.324920153617498</v>
+        <v>-2.832458812617652</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.192458820794435</v>
+        <v>1.380207106254169</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4080917781269449</v>
+        <v>-1.440376098580309</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-8.528730290540146</v>
+        <v>-9.866292475007484</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.328888368364417</v>
+        <v>0.4149132337288606</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.952139183957527</v>
+        <v>-6.472932898744872</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3448401955468725</v>
+        <v>-2.138693654825062</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.958411950937112</v>
+        <v>-6.48174781514146</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>6.897108808118411</v>
+        <v>4.607745325728033</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.508401319340081</v>
+        <v>2.327134567882418</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.66818092594287</v>
+        <v>-4.456958423063995</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>4.443783625499094</v>
+        <v>2.208581814339183</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.309651279192984</v>
+        <v>2.105529162182997</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1376243925729099</v>
+        <v>-2.100228840219884</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.08231398236061693</v>
+        <v>-1.88676206413686</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.89654036334074</v>
+        <v>-3.711456052682045</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.451986284644946</v>
+        <v>-4.279549937869554</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.400221812329306</v>
+        <v>-6.395647811752127</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.126945356551964</v>
+        <v>-6.154202083561977</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-7.551554246241857</v>
+        <v>-10.39993846190212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01012</t>
+          <t>X ≈ -0.01011</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.67240364786646</v>
+        <v>1.693593632036148</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.40725852143445</v>
+        <v>5.962294730175685</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.349177588300861</v>
+        <v>3.191466277648985</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.841113520561493</v>
+        <v>4.101644069610394</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.502836899808585</v>
+        <v>2.317957185161248</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.50892308167801</v>
+        <v>9.342172276260833</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.518308333451394</v>
+        <v>5.540645811342792</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.237654050176737</v>
+        <v>5.239755769666175</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1431180072839453</v>
+        <v>-0.6621694329627132</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9271354600577908</v>
+        <v>-1.454392010784517</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.471538044955231</v>
+        <v>-5.710206963208599</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9313685012410247</v>
+        <v>-1.460136887053729</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.068064619287625</v>
+        <v>-2.571989132689119</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.900480472790768</v>
+        <v>-4.330633732415237</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-4.571974394001415</v>
+        <v>-5.011445577426883</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.35970390220028</v>
+        <v>-4.453399304391773</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-5.716149774223787</v>
+        <v>-7.582026109731608</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.215131840851761</v>
+        <v>-6.204650138804865</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-5.608870456147031</v>
+        <v>-7.50525027063351</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-5.419726549183281</v>
+        <v>-7.293525193741758</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.36101101089055</v>
+        <v>-6.349119423727657</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-4.437863892872613</v>
+        <v>-6.426394790635634</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.584636688897987</v>
+        <v>-3.155717774967194</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.564855290926268</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.008848</t>
+          <t>X ≈ -0.00884</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.349498053548082</v>
+        <v>0.7552974254735361</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1329495958064228</v>
+        <v>1.292659544280205</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.03197990483372593</v>
+        <v>0.836110733950072</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.232495801649563</v>
+        <v>1.707875460802001</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.897829017797804</v>
+        <v>1.433650891115164</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.637299892620348</v>
+        <v>1.587345826111466</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.424276975714839</v>
+        <v>2.260033124795036</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4840325822946028</v>
+        <v>-0.9674454069969514</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.082003288055404</v>
+        <v>-0.8393854021690714</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.313446309250324</v>
+        <v>-1.631497354510657</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.03043312205011972</v>
+        <v>-4.289195848809214</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7.538511543959302</v>
+        <v>2.756894686495059</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.747348741134893</v>
+        <v>-1.283942366169633</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.085695142032264</v>
+        <v>1.399677714371357</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.548422330539019</v>
+        <v>3.653258975761673</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.09442245972381613</v>
+        <v>1.280609827180911</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>2.891679803766976</v>
+        <v>4.111801328259922</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.3328323093928702</v>
+        <v>1.045324987990192</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.443673053954321</v>
+        <v>2.727931809547314</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.192220838959614</v>
+        <v>4.41155622741848</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.650895122983719</v>
+        <v>3.846036323372658</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>4.137051831999408</v>
+        <v>5.241654369688369</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.849394267978624</v>
+        <v>4.016644232705389</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.77453271028002</v>
+        <v>3.855763819009773</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.00757</t>
+          <t>X ≈ -0.007564</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.123435808485631</v>
+        <v>-2.985371491328813</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8670552075449365</v>
+        <v>1.045334638604913</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5799530808699345</v>
+        <v>-0.2013227444110086</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.113328086131347</v>
+        <v>4.551991034334797</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.857905703021572</v>
+        <v>5.346540496011457</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.211401133376313</v>
+        <v>7.63746084843266</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.270925596476388</v>
+        <v>4.711817731581675</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.908880264700251</v>
+        <v>3.341959865630592</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.363362930801628</v>
+        <v>8.820441860794709</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.586622891120925</v>
+        <v>8.031827731650438</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.697818754331593</v>
+        <v>6.165174306381878</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.421543034210899</v>
+        <v>5.890223157128254</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.374962034659809</v>
+        <v>5.852703741746048</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.070100225312501</v>
+        <v>4.535462135745917</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.575384062322847</v>
+        <v>6.001595698039317</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.836844406184838</v>
+        <v>2.273947471665814</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.788192150851351</v>
+        <v>3.243683586872493</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>7.025189464956256</v>
+        <v>8.477844607584231</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>6.159387111532503</v>
+        <v>7.621332065362097</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>6.351577385252881</v>
+        <v>7.837957119721807</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>7.978761756450474</v>
+        <v>9.422048740999003</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>7.902554799849646</v>
+        <v>9.34999501551156</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.920852884604471</v>
+        <v>6.371874676053757</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>6.578880536367585</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006294</t>
+          <t>X ≈ -0.006288</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5679272461349214</v>
+        <v>0.1620132455310994</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2306403998322253</v>
+        <v>0.8372374384318277</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.229969080776719</v>
+        <v>-1.328906262492509</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.998603736573628</v>
+        <v>-0.9999622898163949</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.027418908888961</v>
+        <v>-6.794561457888769</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.88358311938088</v>
+        <v>-4.801604938182415</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.82407974110518</v>
+        <v>-3.751801628872357</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.111978341192</v>
+        <v>-3.134002335381361</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2661541971387464</v>
+        <v>-0.244453876488862</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.13068424468922</v>
+        <v>5.413735971122186</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.356811167824453</v>
+        <v>6.609336286166176</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.728679558212178</v>
+        <v>5.412653727378839</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.409613497526998</v>
+        <v>7.993340571263381</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.342022239009793</v>
+        <v>4.980804502123334</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.538645329601302</v>
+        <v>7.07218103228805</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>8.134873026639838</v>
+        <v>7.634685031582976</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>9.905982029789186</v>
+        <v>9.380860102926697</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>8.853455666480258</v>
+        <v>8.327636752157858</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>7.168977402728153</v>
+        <v>6.696167435348912</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>7.358270714554422</v>
+        <v>6.912610045757503</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7.770783831478319</v>
+        <v>7.273134287230889</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>5.790175965307533</v>
+        <v>5.350000816637014</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>6.521012801714868</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>4.084056519803973</v>
+        <v>3.583432664325677</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005017</t>
+          <t>X ≈ -0.005013</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.125468258878215</v>
+        <v>-3.143531321620188</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.660160961143532</v>
+        <v>-3.388500942149001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.131276178723688</v>
+        <v>-5.380466870683009</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.438094146615086</v>
+        <v>-3.731062703983049</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2360969766186969</v>
+        <v>0.4774604945209902</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.04382452642696</v>
+        <v>1.3763520030327</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.764582688083856</v>
+        <v>-2.401012628861736</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.031290425184594</v>
+        <v>1.781137625439506</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9428718442290744</v>
+        <v>-1.829835120879764</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.9219841408091298</v>
+        <v>-1.874576378117432</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6210142798883282</v>
+        <v>-0.1068505720786561</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.069733716212383</v>
+        <v>-2.629303979087894</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.293515204662214</v>
+        <v>0.003145584960755343</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.073911862820133</v>
+        <v>-0.2436661949764982</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.831935954028687</v>
+        <v>2.074368063890518</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.426573015626538</v>
+        <v>2.635125543276303</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.68351591175275</v>
+        <v>1.032389473506761</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.38520705364639</v>
+        <v>2.400840982193508</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.213749642753285</v>
+        <v>4.117081668863854</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.789849079476184</v>
+        <v>2.831207409630991</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.248510405979083</v>
+        <v>2.26550423652094</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.20492250908611</v>
+        <v>5.947935302467918</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.672945608664932</v>
+        <v>5.442118073459277</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>4.79066174253844</v>
+        <v>5.282123836701054</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003739</t>
+          <t>X ≈ -0.003737</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.494642366807945</v>
+        <v>2.164352792860015</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.512064423135804</v>
+        <v>1.280490595265803</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5788119130269891</v>
+        <v>-0.6212313648569605</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.644951351402888</v>
+        <v>-0.5771107011976042</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3130106587157044</v>
+        <v>0.4198993838307601</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.7921724709373592</v>
+        <v>-1.328915599114048</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.9203895870595318</v>
+        <v>-1.135404199369987</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.494326642988995</v>
+        <v>-2.353453346691126</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1366386327681184</v>
+        <v>0.9597869433950166</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.206802187181218</v>
+        <v>-1.744170778874071</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.227941491779085</v>
+        <v>-2.748913289136844</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.095689059857122</v>
+        <v>-5.578304082180082</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-7.216051668933297</v>
+        <v>-6.691521215750704</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.201028688089956</v>
+        <v>-3.748285400119101</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.859071329568962</v>
+        <v>-4.429330491249218</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-5.563579646186689</v>
+        <v>-5.149209033361394</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-5.699403307470845</v>
+        <v>-5.254839296353808</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.806110689299778</v>
+        <v>-5.389345431294657</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.294778689019552</v>
+        <v>-3.897672197763924</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.16224690118797</v>
+        <v>-1.764899716073394</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-2.332217430902006</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.781252606121264</v>
+        <v>-2.408237956374414</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.156128542989855</v>
+        <v>-2.80626679619477</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.933259497511827</v>
+        <v>-1.687222606329442</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002463</t>
+          <t>X ≈ -0.002462</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7521704673757341</v>
+        <v>-0.7105639767719367</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.78845870658278</v>
+        <v>1.869207667557006</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.668735630626493</v>
+        <v>5.326307398056002</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.956185794140502</v>
+        <v>4.263081991144702</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7463366258073663</v>
+        <v>0.6915597857565174</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9308777141641329</v>
+        <v>0.8472165374933454</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.7955427068117871</v>
+        <v>-0.4168742057342669</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.802460186656866</v>
+        <v>2.575177458983752</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8848948913090879</v>
+        <v>1.761778733393072</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5942000069491584</v>
+        <v>1.70889571828431</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5695107008694151</v>
+        <v>0.5674591896088543</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.069036484294159</v>
+        <v>2.178164076389876</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.967380341605683</v>
+        <v>-0.8182558070764685</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7507943517023676</v>
+        <v>0.3496724559622919</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9278097013482665</v>
+        <v>0.1426638745157618</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.334745557641476</v>
+        <v>0.7025327951164186</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.908454816398965</v>
+        <v>-0.8183854634033665</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.01382519777642</v>
+        <v>-0.9512409026390785</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.31860139951808</v>
+        <v>-0.2648038265814137</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.309313899036944</v>
+        <v>1.368345590414179</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.2478900585845452</v>
+        <v>1.275717968516595</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1720440971753305</v>
+        <v>1.201115027248633</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.03425042111173582</v>
+        <v>0.9715598462354293</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.513928828181164</v>
+        <v>-1.559625085367244</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.001185</t>
+          <t>X ≈ -0.001186</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.829853745096166</v>
+        <v>-3.940915054153734</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4752539152916313</v>
+        <v>-0.5080154590929595</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.962429158334551</v>
+        <v>1.102350311845569</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9798803433805219</v>
+        <v>-0.7161348757256505</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.953665050287398</v>
+        <v>-2.625541226716464</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3099531716512587</v>
+        <v>-0.01811403661922384</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2570908086777024</v>
+        <v>0.007574561475351516</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.174279123793241</v>
+        <v>-1.931974543090291</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.723498099122722</v>
+        <v>-1.165104035037146</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.312708643330815</v>
+        <v>-2.772387598939602</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.038649001168892</v>
+        <v>-2.501240753137026</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.77676445983019</v>
+        <v>-5.23364814939184</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.255545158307349</v>
+        <v>-4.707353473887373</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.068867413917388</v>
+        <v>-4.547953644485574</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.496236764697933</v>
+        <v>-3.999691183256402</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-5.957854690722648</v>
+        <v>-5.491842422894869</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.32637183368923</v>
+        <v>-6.828090013034782</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.845383791645162</v>
+        <v>-7.374160770476912</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-6.400190258105987</v>
+        <v>-5.932425681791308</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.861896985643369</v>
+        <v>-7.364701896055493</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.996411935717539</v>
+        <v>-7.523654434473869</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-6.837689995891978</v>
+        <v>-6.368984887282394</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-6.563215283409924</v>
+        <v>-6.12831313631478</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-6.227524902888348</v>
+        <v>-5.881587911806101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 9.16e-05</t>
+          <t>X ≈ 8.97e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.381305519021538</v>
+        <v>-0.4607032539012721</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7143777870305286</v>
+        <v>-1.39157965071368</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.502378426215458</v>
+        <v>-2.989031054642588</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.56122316299426</v>
+        <v>-3.924005944160946</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2388455585262435</v>
+        <v>-0.08935112190776096</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.809374613967861</v>
+        <v>1.437917202008606</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.001950752271447698</v>
+        <v>-0.3849883745413081</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2816962743312743</v>
+        <v>-0.6899791460746982</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.618828823772496</v>
+        <v>-1.932121223841378</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3266273778372408</v>
+        <v>-0.3306825540093854</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.05256773567531781</v>
+        <v>0.1391034186091673</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.736527231393566</v>
+        <v>2.11766673478855</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.299010289982732</v>
+        <v>2.038726788978906</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.164847595080651</v>
+        <v>-1.637605489641416</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.78960719975295</v>
+        <v>-1.631138312193379</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.8506790310124899</v>
+        <v>-0.72899735313473</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3957700610474149</v>
+        <v>0.8852296296667745</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4010510786857324</v>
+        <v>0.06576166967358432</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.1842752656311859</v>
+        <v>0.2783524520989076</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.726369333526158</v>
+        <v>-1.228560764558203</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.024734375804513</v>
+        <v>-0.7630724895301455</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-6.290891755898741</v>
+        <v>-6.005859303251867</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.670396282171083</v>
+        <v>-5.765867268216731</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-6.438270057885632</v>
+        <v>-6.62090960898211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001369</t>
+          <t>X ≈ 0.001365</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.692487154387912</v>
+        <v>0.6127153517945558</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.9756269391718035</v>
+        <v>-1.289418598281934</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.746986127699508</v>
+        <v>-4.523392219853271</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.540072355842618</v>
+        <v>0.8415193460705623</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.129057020254308</v>
+        <v>-1.749578042416644</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.608762206660337</v>
+        <v>-4.577121495198377</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.3807058131462</v>
+        <v>-1.725728079368039</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.325586523477739</v>
+        <v>-2.690632215608893</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.617435522069876</v>
+        <v>-3.886476191552191</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.723680816587709</v>
+        <v>-2.03162412143174</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5503832819121328</v>
+        <v>0.2259344422052578</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.39503897742329</v>
+        <v>-2.366634466531792</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.148471070534562</v>
+        <v>0.162763999916109</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.07260891937779945</v>
+        <v>0.1135557678722847</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.7316424200680203</v>
+        <v>-0.2333942671124873</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.807752588922604</v>
+        <v>-1.99573204157786</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.27843493702359</v>
+        <v>-2.432569936774676</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.721205466888463</v>
+        <v>-2.566160270021712</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.513077243248667</v>
+        <v>-4.017156945282096</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.456219291844157</v>
+        <v>-2.809071294057361</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.995420978204713</v>
+        <v>-2.712332411961583</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.399026136938275</v>
+        <v>-1.124630453868271</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-3.127895906061568</v>
+        <v>-2.215241385115242</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.538176319820032</v>
+        <v>-2.712863631970507</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.002646</t>
+          <t>X ≈ 0.002641</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.052286520131986</v>
+        <v>1.006132567389983</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.828266852730927</v>
+        <v>-2.780065772873662</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.833371464139809</v>
+        <v>3.384135554104844</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7830605563506765</v>
+        <v>0.2109265244692011</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.116056471354575</v>
+        <v>-0.380146861333813</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.222909472080929</v>
+        <v>-1.522242628496898</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.70048005763892</v>
+        <v>-1.018911407407657</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.008816159844436</v>
+        <v>-0.3526405201409375</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6442235009167376</v>
+        <v>0.09881345315530154</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.7698103999098933</v>
+        <v>-0.04833949532262949</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.07556437027398</v>
+        <v>-2.353214472511134</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.029252106428657</v>
+        <v>-2.624867308269671</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.827073050237097</v>
+        <v>-3.737243833055594</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.690171044394738</v>
+        <v>-4.301815134567399</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-6.640718250192101</v>
+        <v>-6.271203067327335</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.147429311232962</v>
+        <v>-2.813641911713063</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.961604854871894</v>
+        <v>-2.596848110788798</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.716571181622861</v>
+        <v>-3.37700457479778</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.858259222451551</v>
+        <v>-2.521820735909564</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.671413412483524</v>
+        <v>-2.312431998909354</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.184833366857369</v>
+        <v>-3.853081546992613</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.613430137327917</v>
+        <v>-3.283895137995529</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.720832447499582</v>
+        <v>-1.422597569959812</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.796664700722857</v>
+        <v>-1.587322506429537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003922</t>
+          <t>X ≈ 0.003916</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>260</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.06327513813693</v>
+        <v>3.150478925749134</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.100817371498565</v>
+        <v>-0.5150785986393629</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.006475690731101</v>
+        <v>-0.6224998330987503</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5706193314724644</v>
+        <v>-0.4562760258608733</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2428705341515069</v>
+        <v>1.176981538256484</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7195611077896942</v>
+        <v>-0.5778173907005169</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.104632478775848</v>
+        <v>2.821128177784892</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.677845635056286</v>
+        <v>1.37885209145464</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.336448241789412</v>
+        <v>1.127467998115648</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2020799314535893</v>
+        <v>-0.4254594047067926</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6938677662332182</v>
+        <v>-0.9130171284439612</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.708475612240456</v>
+        <v>1.478425993495236</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.734593883555448</v>
+        <v>1.738861238208621</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.662834508569169</v>
+        <v>2.642005842385672</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.771132880970129</v>
+        <v>3.115891492064996</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.366789566624945</v>
+        <v>3.67087635479858</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.232823267977793</v>
+        <v>3.569990099557209</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.279177927137084</v>
+        <v>4.589281115199739</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.738205801197971</v>
+        <v>4.801937813467276</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5.309666995781399</v>
+        <v>5.399007951136582</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.228659289353821</v>
+        <v>3.304617349303598</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.922044097175437</v>
+        <v>3.998105746517354</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.273441886580621</v>
+        <v>2.705381165716602</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.120686556434215</v>
+        <v>4.082008162901218</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0052</t>
+          <t>X ≈ 0.005192</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.026652105605095</v>
+        <v>1.60525998922553</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.308519450270893</v>
+        <v>4.037734897174346</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.299022061755295</v>
+        <v>3.235774791792082</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8327886342058619</v>
+        <v>0.8658961741015219</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8315524342597271</v>
+        <v>-0.7267999412903521</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.951644036894521</v>
+        <v>-2.3549472012553</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.72738556911186</v>
+        <v>-3.143945655823465</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.05979731407659017</v>
+        <v>-0.3390428108959327</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7823087633281745</v>
+        <v>-0.6486390035598717</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.511434171352427</v>
+        <v>1.22152412954442</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.340536476915517</v>
+        <v>1.057754931216905</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.818859329901166</v>
+        <v>2.551044948547322</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.686847283615492</v>
+        <v>1.445278167593322</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.33545455595614</v>
+        <v>1.651298992085692</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.302833828979622</v>
+        <v>3.642428961491326</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.980571662672652</v>
+        <v>1.977121790212841</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.558128260027637</v>
+        <v>2.319855530466874</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.608725806244507</v>
+        <v>3.081428331122353</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.705674455891206</v>
+        <v>4.18116791313782</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.689877094053095</v>
+        <v>2.164104571100971</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.02838819480948</v>
+        <v>2.944432407726758</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.630956330316749</v>
+        <v>1.97568016645905</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.143316505353823</v>
+        <v>0.8744063012075571</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1864269834081256</v>
+        <v>-0.1867051865297142</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.006477</t>
+          <t>X ≈ 0.006468</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3111091084913014</v>
+        <v>0.07929949936821146</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.172944335669577</v>
+        <v>1.041959783909505</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3377226840847598</v>
+        <v>-0.2036739981660816</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9841175954046264</v>
+        <v>-1.39507457053756</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1090942479734522</v>
+        <v>-0.4650856969970434</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.135551394397538</v>
+        <v>-1.51067899803347</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.349133981074814</v>
+        <v>-4.683633864887341</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.801556483202383</v>
+        <v>-3.196089347514125</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.33314248675029</v>
+        <v>2.897662444960012</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.777129493292698</v>
+        <v>3.298097643564503</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.095620435687742</v>
+        <v>6.557774259471806</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.208854609707402</v>
+        <v>5.680683878134623</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.079603680250834</v>
+        <v>4.574852080499838</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.072817973840088</v>
+        <v>6.125123193059174</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7.00908684006739</v>
+        <v>7.012972786200073</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.603473762010282</v>
+        <v>7.574009450338053</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>8.079312722593855</v>
+        <v>8.081402499016157</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.535447628528772</v>
+        <v>5.56788561399371</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.531826814331147</v>
+        <v>4.574540425991671</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.328428721860078</v>
+        <v>5.392771424630467</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>8.444419139260042</v>
+        <v>8.459158377350747</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.8075975680948</v>
+        <v>10.20798431917755</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>11.6918283781378</v>
+        <v>11.07012559089846</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>11.00624002735351</v>
+        <v>10.92350000439301</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.007754</t>
+          <t>X ≈ 0.007743</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.052611819314301</v>
+        <v>-8.629311973561833</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.181506264722955</v>
+        <v>-6.61589562428189</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.207760607871592</v>
+        <v>-3.400752723988994</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.714832274373144</v>
+        <v>-2.515411597348177</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.256505099861627</v>
+        <v>-4.985213765387151</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.86365656082306</v>
+        <v>-1.884995850436788</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.37089936236049</v>
+        <v>-3.388443670529512</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.02735978112171722</v>
+        <v>0.01116281797263952</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.87232950755174</v>
+        <v>-2.848934501763466</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.645245183588273</v>
+        <v>-3.640918549667546</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.841773776720458</v>
+        <v>-4.109588921445386</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-5.120523180168412</v>
+        <v>-4.394305770547156</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.56721465878924</v>
+        <v>-2.521171658577792</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.052999417588836</v>
+        <v>-2.012230544367689</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.975848597522351</v>
+        <v>-1.93720975060959</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.381461675579303</v>
+        <v>-1.398304426856868</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.985967047850913</v>
+        <v>-2.993881758086324</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.620219516377972</v>
+        <v>-1.621599736995911</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-4.345504606041885</v>
+        <v>-4.425268418634104</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-4.893952913720902</v>
+        <v>-4.98122534545557</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.230616728745836</v>
+        <v>-3.295931693868383</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-4.041756807801974</v>
+        <v>-4.135000146646007</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-6.708458565908138</v>
+        <v>-6.926704070530612</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.107820230896074</v>
+        <v>-3.318924238031229</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.009031</t>
+          <t>X ≈ 0.009019</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2317562043410959</v>
+        <v>-0.2802006112191151</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.706194270036399</v>
+        <v>1.647557815139741</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.004552051721866</v>
+        <v>-1.780287355801924</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6915848379262783</v>
+        <v>1.973355486983792</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.901248910833608</v>
+        <v>4.958380938814017</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.679124187840053</v>
+        <v>0.7682411171929431</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9071755039497305</v>
+        <v>-0.02606960552087401</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.901691331923892</v>
+        <v>1.84173252594347</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.806814877474963</v>
+        <v>0.8829145034316284</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1024644349251602</v>
+        <v>-0.9996268274773712</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.580686116327669</v>
+        <v>1.445844955012575</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.165573076516033</v>
+        <v>0.08251606834532765</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.09395262670368254</v>
+        <v>-1.032204651434583</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.587758775877553</v>
+        <v>-2.366757150886421</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.1631888356327664</v>
+        <v>-0.8755033672150461</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-2.65151515151512</v>
+        <v>-2.921825029056279</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-3.921795924856262</v>
+        <v>-3.445693910500722</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.6175457195865306</v>
+        <v>-0.29819734780191</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.538017975025838</v>
+        <v>-1.200357749072033</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.9215551076694908</v>
+        <v>1.186626324206145</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.651736212430734</v>
+        <v>3.927888492952981</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.575890251021598</v>
+        <v>2.756200047002608</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.5776376907764131</v>
+        <v>0.7885424144099673</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6345581988104954</v>
+        <v>-0.4906414097483918</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01031</t>
+          <t>X ≈ 0.01029</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>64</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5158471134320095</v>
+        <v>3.728927944839931</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-1.210714400726744</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.288642960812773</v>
+        <v>0.590585188233355</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.564096980255556</v>
+        <v>-2.979421434580033</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.350112547197213</v>
+        <v>4.353648945711313</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.712921266705408</v>
+        <v>-3.129401675419949</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.327630049404242</v>
+        <v>5.196463824794648</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.200581395348834</v>
+        <v>-2.717085139004652</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.09090578656587</v>
+        <v>3.601220419229456</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2445098894706206</v>
+        <v>1.230138518476366</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.095450247308698</v>
+        <v>-1.569298011140418</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.313300349243264</v>
+        <v>2.800821984143155</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.372361717612854</v>
+        <v>0.1108994611586311</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.593440594059402</v>
+        <v>-1.743720712547024</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.25158389163996</v>
+        <v>-0.8978782490061334</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>3.030303030303031</v>
+        <v>4.325805572937668</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.333885893325558</v>
+        <v>1.087542203514339</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.916545189504376</v>
+        <v>4.972902967178342</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.569936570428702</v>
+        <v>3.671407871088078</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.756782380396729</v>
+        <v>2.404794828696744</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>7.339236212430656</v>
+        <v>6.518689447983988</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>10.3883902510216</v>
+        <v>10.50091331293795</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>10.66286496350365</v>
+        <v>11.68293023906053</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>10.58703271028038</v>
+        <v>10.93296970136272</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01158</t>
+          <t>X ≈ 0.01157</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.02581955323474</v>
+        <v>1.696781890295142</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.69104275488489</v>
+        <v>8.283259657092266</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.253023705853892</v>
+        <v>0.2403366330125678</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.5400696864111936</v>
+        <v>-0.3836053374476833</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>-2.343604799433201</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3912453999612566</v>
+        <v>-0.4896139628880789</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.619296716070913</v>
+        <v>3.82539957951149</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.325581395348827</v>
+        <v>-3.280365694746123</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.28409421343413</v>
+        <v>-8.275148248355137</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.057009889470599</v>
+        <v>-9.052275880583245</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-8.773732911648466</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.728366317423315</v>
+        <v>-9.075546683441438</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.51819505094614</v>
+        <v>-6.777400476806889</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.072607260726066</v>
+        <v>-5.297037536040897</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-6.730750558306624</v>
+        <v>-5.979191917925952</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-7.803030303030297</v>
+        <v>-7.146484901305392</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.270280773341128</v>
+        <v>-0.4305966191902115</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.04178814382896</v>
+        <v>-2.260537954898844</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.159230096237941</v>
+        <v>-2.08171430332272</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.305717619603264</v>
+        <v>-5.333764011217944</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.848263787569252</v>
+        <v>-7.66172533663643</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-9.924109748978402</v>
+        <v>-11.18516372066068</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-2.982968369829685</v>
+        <v>-5.769115442278803</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.725467289719617</v>
+        <v>-5.931254436568324</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01286</t>
+          <t>X ≈ 0.01285</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.736511377134072</v>
+        <v>6.067240044316847</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.17531948444463</v>
+        <v>9.678721581868786</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.190130624092923</v>
+        <v>0.6834013790717179</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.024346415970896</v>
+        <v>7.834210216608383</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.801763490593437</v>
+        <v>3.685754090616861</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.215144771030438</v>
+        <v>1.912701042267337</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.217181271350476</v>
+        <v>-2.747524149539359</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-6.382185168933738</v>
+        <v>-4.990186053613705</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.453905534188827</v>
+        <v>-4.857087273050873</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.340028757395174</v>
+        <v>-3.728321984801326</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.952761568063416</v>
+        <v>-5.391243495423396</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.344718518681226</v>
+        <v>-5.657485708137173</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.581088132707151</v>
+        <v>-6.77496276102729</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.9714178965066367</v>
+        <v>-3.168393384643963</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.573517853904114</v>
+        <v>-5.783119356316021</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.865923384791309</v>
+        <v>-7.144047185525793</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-2.999840521768746</v>
+        <v>-5.317940942903178</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.217888772759778</v>
+        <v>-3.52083839371717</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.771587513824905</v>
+        <v>3.725605237752859</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.958433323792953</v>
+        <v>3.924423942451895</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.529094702996737</v>
+        <v>1.39845045781928</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.4532487415876361</v>
+        <v>-0.6374963778614884</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.159068998760503</v>
+        <v>-0.3938618925831108</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.6518912008464142</v>
+        <v>1.404783426852909</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01414</t>
+          <t>X ≈ 0.01412</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.073438600853777</v>
+        <v>11.05347416894949</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4041953403531551</v>
+        <v>4.185531628476191</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>23.1577856106158</v>
+        <v>25.91134201188519</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.58768873403023</v>
+        <v>8.960471032545811</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.251898261482921</v>
+        <v>8.599425726623664</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>11.5817215904375</v>
+        <v>15.36129760422667</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.09548719226143731</v>
+        <v>1.322144182454863</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.960132890365458</v>
+        <v>7.570869711157428</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.001620072280105</v>
+        <v>7.732993487170752</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.657275824815088</v>
+        <v>3.600277989819759</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.07419260983416</v>
+        <v>10.44325640969991</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.224014634957641</v>
+        <v>3.630125916281969</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.10085256810148</v>
+        <v>5.800605501469001</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.451202263083459</v>
+        <v>8.820645709509272</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.221630394074332</v>
+        <v>4.818924758657182</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.244588744588739</v>
+        <v>2.129051941168058</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.68210017903985</v>
+        <v>2.02517152944305</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.148688046647237</v>
+        <v>5.194756560083889</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.793150856143036</v>
+        <v>2.192236817250198</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.162860476746133</v>
+        <v>-2.099417155984163</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.8660219267164635</v>
+        <v>0.6141367323291291</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.7901759653073057</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.506777893639153</v>
+        <v>-2.550724637681114</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.9888184245661407</v>
+        <v>0.620469701362758</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.01542</t>
+          <t>X ≈ 0.01539</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.640847113432024</v>
+        <v>-9.347624496963753</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>18.02437608821816</v>
+        <v>18.10258647188388</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.58635703918717</v>
+        <v>20.81085533295524</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.873403019744458</v>
+        <v>8.318408511210862</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.53761254719721</v>
+        <v>12.05043627026369</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7.724578733294535</v>
+        <v>8.233251179251468</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14.95263004940418</v>
+        <v>15.40871802913392</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.67441860465117</v>
+        <v>15.1149533197726</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.71590578656587</v>
+        <v>7.31695630353078</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.942990110529379</v>
+        <v>6.554372010453321</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.217049752691302</v>
+        <v>6.826607025057655</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.061699650756751</v>
+        <v>-5.327708084255157</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.815138282387217</v>
+        <v>9.364628713956698</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.594059405940598</v>
+        <v>5.175743157655212</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.93591610836004</v>
+        <v>8.467707472780411</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>8.530303030303031</v>
+        <v>9.006700023505459</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.396385893325558</v>
+        <v>8.902819611780451</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.291545189504404</v>
+        <v>8.758779772571586</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.507436570428617</v>
+        <v>8.928619063528132</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.69428238039673</v>
+        <v>13.08385700345546</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>12.15173621243064</v>
+        <v>12.61413673232903</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>12.0758902510216</v>
+        <v>12.5389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>12.35036496350359</v>
+        <v>12.78260869565212</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.27453271028032</v>
+        <v>16.62046970136266</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0167</t>
+          <t>X ≈ 0.01667</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>30.97453750195265</v>
+        <v>32.70235319156809</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.94745301129515</v>
+        <v>32.85805278156703</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.81712626995645</v>
+        <v>14.93669201300879</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>13.10417225051371</v>
+        <v>14.44469142062636</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.76838177796644</v>
+        <v>13.76752685482408</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.95534796406376</v>
+        <v>14.02486206724799</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.18339928017352</v>
+        <v>12.82817362931246</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.212880143112706</v>
+        <v>4.089518246144749</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>4.217447155828857</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.481451648990976</v>
+        <v>3.120190841332395</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.44781898346053</v>
+        <v>11.72575918927012</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.86137727232024</v>
+        <v>19.6821089617064</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.73821520546401</v>
+        <v>10.63548993662513</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>17.51713632901753</v>
+        <v>10.18645266234058</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>16.85899303143697</v>
+        <v>9.403896674029887</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.761072261072258</v>
+        <v>1.83267057236759</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>9.627155124094784</v>
+        <v>1.728790160642582</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.522314420273545</v>
+        <v>1.696307661906673</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.738205801198042</v>
+        <v>2.312376314755205</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>-5.60556736066777</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.382505443199925</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.614351789483138</v>
+        <v>-1.127692456292863</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>1.888826501965248</v>
+        <v>-0.8840579710144851</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>-1.046196965303949</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1149 +3180,1149 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.0197</t>
+          <t>X &gt; -0.01968</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3346</v>
+        <v>3370</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1139762762979188</v>
+        <v>0.1266924584499733</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1217632616148876</v>
+        <v>0.220900398449686</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1848126376428283</v>
+        <v>0.279685929103735</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.141971053018402</v>
+        <v>0.2640751502349943</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.03092606874253079</v>
+        <v>0.1525476106121246</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.003126379666163359</v>
+        <v>0.06038550693347844</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1041644792903753</v>
+        <v>-0.09819971170445285</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1274850241412153</v>
+        <v>-0.1206478761115619</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.09873271388043037</v>
+        <v>-0.06458496082090193</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.05105750851823387</v>
+        <v>-0.0460201017306261</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.002104828606753983</v>
+        <v>0.006728173097791057</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.0807586144255481</v>
+        <v>-0.0755140792450959</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08447446709151052</v>
+        <v>-0.07906304014443322</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1687534665266242</v>
+        <v>-0.1324561088387881</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.004471373011050161</v>
+        <v>0.06102058250778697</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.0779259500189724</v>
+        <v>0.01830832765159585</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.01518583348625668</v>
+        <v>0.1095801253578159</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.01275075321639463</v>
+        <v>0.1423429880453426</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.01206205535857663</v>
+        <v>0.1669947886508325</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.02213553005103819</v>
+        <v>0.1916582935794153</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.02035371019122323</v>
+        <v>0.2050053952404411</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.007741768094291501</v>
+        <v>0.1475151356407096</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1037730705566986</v>
+        <v>0.05285491339171955</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1916956220567414</v>
+        <v>-0.09169647074410392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01843</t>
+          <t>X &gt; -0.01841</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3330</v>
+        <v>3354</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.0882698316754329</v>
+        <v>0.08485328373423329</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1574706868454925</v>
+        <v>0.2399024551428823</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.16844659142604</v>
+        <v>0.2456612231828359</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1887210251192215</v>
+        <v>0.2920524117157228</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1086997634457205</v>
+        <v>0.2109584525461869</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1224941460363453</v>
+        <v>-0.08996021118966979</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1606056840884449</v>
+        <v>-0.1862394069918167</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1229513893715506</v>
+        <v>-0.1480254002509227</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.09425863794832878</v>
+        <v>-0.06262951773986458</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.0127515162648848</v>
+        <v>-0.010502955231523</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.02046146477803745</v>
+        <v>-0.0181871932305242</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1023938458494484</v>
+        <v>-0.09951307009280441</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1007551626891328</v>
+        <v>-0.09778491612913598</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1544435880713806</v>
+        <v>-0.1205303231089303</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.01378373339748151</v>
+        <v>0.07711586658955127</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.09282459102710305</v>
+        <v>0.001789642341698539</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.02914602156806012</v>
+        <v>0.09398554497669664</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.03375142451636037</v>
+        <v>0.1870563710288735</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.002308557007580703</v>
+        <v>0.1810465897821203</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.007577247677659216</v>
+        <v>0.2048093456812339</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.03772481129058036</v>
+        <v>0.2507170123410063</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.009863840457370543</v>
+        <v>0.1933246275370948</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08794185126669163</v>
+        <v>0.09706473141969241</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1759177401700711</v>
+        <v>-0.04738957114771836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01715</t>
+          <t>X &gt; -0.01713</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3308</v>
+        <v>3332</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.08287661029176263</v>
+        <v>0.07883377859580776</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1547455685426442</v>
+        <v>0.2365111589046691</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1152031930333806</v>
+        <v>0.1908910339658831</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1703672517853647</v>
+        <v>0.2712913765358493</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.03189997954839185</v>
+        <v>0.1317842424768116</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1419275805959685</v>
+        <v>-0.1124633538394022</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2052646874378681</v>
+        <v>-0.2340184054735062</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1655332605714577</v>
+        <v>-0.1935639032413263</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1369380292631988</v>
+        <v>-0.1084611982327459</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.01968297797152019</v>
+        <v>-0.0208851182140819</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.05937301153633712</v>
+        <v>-0.06030884970195416</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1098924218410318</v>
+        <v>-0.110458437075323</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1008002533163364</v>
+        <v>-0.1013851737475804</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1533788098520432</v>
+        <v>-0.1226472922353352</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.02032973513122016</v>
+        <v>0.0807916228764114</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.06077055232664463</v>
+        <v>0.03121324605633902</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.02593688193839228</v>
+        <v>0.09476078167115531</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.06825007785681692</v>
+        <v>0.219279116328309</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.03052742463938074</v>
+        <v>0.2118254748959671</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.02399252532426743</v>
+        <v>0.2343390274748103</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.0732100873929511</v>
+        <v>0.2843016498703079</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>0.2570305990960549</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.05459121661118616</v>
+        <v>0.1285432891115263</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1426377854874659</v>
+        <v>-0.01578480043799857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01587</t>
+          <t>X &gt; -0.01586</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3286</v>
+        <v>3309</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.07741165319438892</v>
+        <v>0.08882585292181489</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.121745305031034</v>
+        <v>0.18925088529992</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.06125117106865474</v>
+        <v>0.1219374994591149</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.09125475953268847</v>
+        <v>0.1769264587059141</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.01461012588970334</v>
+        <v>0.09842738000178031</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1616198139209004</v>
+        <v>-0.1486036622163667</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1596920819914587</v>
+        <v>-0.2053797060977871</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1783978702125566</v>
+        <v>-0.2226779068884355</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.08930475569405161</v>
+        <v>-0.07771181942233341</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02670685916758941</v>
+        <v>-0.04419707445956078</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.007866888715184928</v>
+        <v>-0.02558090923351131</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1174910394771231</v>
+        <v>-0.1042632661390215</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1311765492779671</v>
+        <v>-0.1476425934953625</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2433192348361004</v>
+        <v>-0.2276048935836101</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.03373487798290142</v>
+        <v>0.01207985884867924</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.05864657504001514</v>
+        <v>0.01854037052311241</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.0226848628238514</v>
+        <v>0.08324537595496651</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.0120798189089939</v>
+        <v>0.1492143111279916</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.003030614792123743</v>
+        <v>0.1703743903406334</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.02558937127818695</v>
+        <v>0.2217261175009426</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.04836132644712166</v>
+        <v>0.2759724811213573</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.08197297608242593</v>
+        <v>0.2792339506335395</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.05121702615257107</v>
+        <v>0.1481676080388823</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1393443438888227</v>
+        <v>0.003969248053557806</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01459</t>
+          <t>X &gt; -0.01458</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3261</v>
+        <v>3283</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1982753728568838</v>
+        <v>0.1778814388585488</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1846930647497587</v>
+        <v>0.2508007780917296</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.07416191723601173</v>
+        <v>0.1323171284828106</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.04906633172984698</v>
+        <v>0.1318542408444969</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1269963177890432</v>
+        <v>0.2063165380877834</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.08262077860290873</v>
+        <v>-0.07415745829440823</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1224157102052814</v>
+        <v>-0.155397016908843</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1391303730723621</v>
+        <v>-0.1704132652905059</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.08018700952693081</v>
+        <v>-0.05561842365098357</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.01932598839197652</v>
+        <v>0.01477554959219418</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.005687504676643584</v>
+        <v>0.001069167045251618</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1026406834484206</v>
+        <v>-0.1063925405088213</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1384069498866509</v>
+        <v>-0.1413149148390289</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2191475644048637</v>
+        <v>-0.1895792515280519</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.003355664607816777</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.09374101986522021</v>
+        <v>-0.00128329231632307</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.08709023886538603</v>
+        <v>0.03435283687942814</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.02066784998139326</v>
+        <v>0.1322832456035741</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.0008304228352287168</v>
+        <v>0.1823232558041212</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.07141440367677632</v>
+        <v>0.1411188059641617</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.01370496403988852</v>
+        <v>0.2002596781598882</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.009920352717294634</v>
+        <v>0.1736774067208273</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.08495079370052139</v>
+        <v>0.1005136895620424</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1731827144359741</v>
+        <v>-0.04355710338903407</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01332</t>
+          <t>X &gt; -0.0133</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3229</v>
+        <v>3251</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2976144250295718</v>
+        <v>0.2753329542351537</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2872261959436742</v>
+        <v>0.3513992195646978</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.159017137709391</v>
+        <v>0.2134960506753671</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1099290437666554</v>
+        <v>0.188277197546256</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1611492077024508</v>
+        <v>0.2356009862120843</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.009236773960026312</v>
+        <v>0.01203498651754842</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03827391878193964</v>
+        <v>-0.0009887976291480527</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1298957250868895</v>
+        <v>-0.1661638025274428</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.009125039574698235</v>
+        <v>0.009740640852839988</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.006511541303360957</v>
+        <v>-0.003237020190248074</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.009970605112521014</v>
+        <v>-0.0197522683250142</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.08576629685357773</v>
+        <v>-0.09491516298727021</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1107876435387354</v>
+        <v>-0.1192395884648221</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2210069725712884</v>
+        <v>-0.1962003046330878</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1196737619302581</v>
+        <v>-0.06280448644025682</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.06283876765804308</v>
+        <v>0.02581134657209816</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.02388604734193933</v>
+        <v>0.09351979742172745</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0442499808490453</v>
+        <v>0.1937361230647809</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.06216755373110772</v>
+        <v>0.2421790638351169</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.04187598644521984</v>
+        <v>0.1677563489171945</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.009154876678209689</v>
+        <v>0.2023358718496766</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.004580191565835889</v>
+        <v>0.1762321261438586</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1140313213260669</v>
+        <v>0.06920156158083302</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1714257908035464</v>
+        <v>-0.04394124911406294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01204</t>
+          <t>X &gt; -0.01203</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3182</v>
+        <v>3205</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2149131113572977</v>
+        <v>0.1914916480902065</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2717214973375164</v>
+        <v>0.3342190710274409</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1627394196933238</v>
+        <v>0.2125862877823295</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.02965301974448664</v>
+        <v>0.1163081199818521</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.007245220855303103</v>
+        <v>0.07516435270649424</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1016169528573343</v>
+        <v>-0.09182808772504103</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1233311884825952</v>
+        <v>-0.1557920284770447</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1335863984757921</v>
+        <v>-0.1637880557470837</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.05090735053208562</v>
+        <v>0.07491429145208883</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.07815907173088021</v>
+        <v>0.07314712125170786</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1513220531607828</v>
+        <v>0.1457536481497286</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.01536276910358936</v>
+        <v>-0.01973228578276576</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.03843925326096809</v>
+        <v>0.03375463721852867</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.0701009950619067</v>
+        <v>-0.04070792401726919</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.0424657793095875</v>
+        <v>0.1044087409659156</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.06008359456635759</v>
+        <v>0.1551856560449494</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.007549267424025174</v>
+        <v>0.1319920091324249</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.04687768636760836</v>
+        <v>0.2044167097454803</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.06187648257179035</v>
+        <v>0.2504838852240425</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>0.1719209033888447</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.005249658840888571</v>
+        <v>0.2151342385634933</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.03089366857638964</v>
+        <v>0.1585563743900167</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.1460220927326077</v>
+        <v>0.04648892023109141</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.234581054647343</v>
+        <v>-0.09715900378548525</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01076</t>
+          <t>X &gt; -0.01075</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3136</v>
+        <v>3156</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2589626519453248</v>
+        <v>0.2502596426794526</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3218705379486266</v>
+        <v>0.3991238669160069</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3110636677949046</v>
+        <v>0.3898432004356849</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1551289080693579</v>
+        <v>0.2068898205250989</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.04141965379618995</v>
+        <v>0.1203080583785194</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1205989316800284</v>
+        <v>-0.1146828800269972</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1311262957734201</v>
+        <v>-0.1358475989982537</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.0104433439365863</v>
+        <v>-0.01314714429469177</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01749308815316652</v>
+        <v>0.06963547390722624</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1519453344099801</v>
+        <v>0.1747814434886692</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1585999432885075</v>
+        <v>0.1812219364405223</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.05714369210952697</v>
+        <v>0.08059685266418626</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.06216623128095478</v>
+        <v>-0.03726106105046512</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1372601489083678</v>
+        <v>-0.07747100453156008</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.0822265409300087</v>
+        <v>0.1752284466178295</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.004218127826149498</v>
+        <v>0.1233046637266995</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.05555554524860185</v>
+        <v>0.1013509063125682</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.04958403063777439</v>
+        <v>0.240198595660658</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.0615766978172374</v>
+        <v>0.283666727910564</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.01932067790209402</v>
+        <v>0.2322141451022333</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.03063997278761832</v>
+        <v>0.2849186253331979</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.01852887434855433</v>
+        <v>0.2603168322863993</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.1022968152658734</v>
+        <v>0.1427607387310488</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1272530040053326</v>
+        <v>0.06280176726892961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.009487</t>
+          <t>X &gt; -0.009477</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3074</v>
+        <v>3090</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2102855726521824</v>
+        <v>0.2194311497029062</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1991333697716158</v>
+        <v>0.2802988581861783</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2497874598992027</v>
+        <v>0.3300027075243293</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.04044737066710979</v>
+        <v>0.1237008948164871</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.06873254830295394</v>
+        <v>0.07336797994237543</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3349874693599872</v>
+        <v>-0.3166739610350859</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.265239811392135</v>
+        <v>-0.2570930893162213</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1364622243643723</v>
+        <v>-0.1253450706122976</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02073247914766085</v>
+        <v>0.08526625832580237</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1737094883647643</v>
+        <v>0.209579323094502</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2721551011515899</v>
+        <v>0.3070582818699279</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0770811533937632</v>
+        <v>0.1135057286581613</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.0217089443400269</v>
+        <v>0.01687876183890324</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.06135915343643461</v>
+        <v>0.01337324790867456</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1760978675291369</v>
+        <v>0.2860117752867524</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.0432900432900496</v>
+        <v>0.221059505764174</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.05861388942819445</v>
+        <v>0.2654618717037991</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1355997704010647</v>
+        <v>0.3778555589210839</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1759448577215252</v>
+        <v>0.4500319453551995</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.08960097597540084</v>
+        <v>0.3929580921455056</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.1192158872274547</v>
+        <v>0.426616525410239</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.1084105762248484</v>
+        <v>0.4031397989895851</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.07239926413861753</v>
+        <v>0.2132136778585831</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.1613814081321223</v>
+        <v>0.07030788906497776</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008209</t>
+          <t>X &gt; -0.008202</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3010</v>
+        <v>3022</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2434504072291972</v>
+        <v>0.2073732718894021</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2061942700364057</v>
+        <v>0.257519067764477</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2557785267905359</v>
+        <v>0.3186144395571091</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.02742342653650809</v>
+        <v>0.08805434601204354</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1318089404060956</v>
+        <v>0.04275936380744838</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4407105229037569</v>
+        <v>-0.3595175565102622</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3862129258023757</v>
+        <v>-0.3137325938031665</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1496554694229033</v>
+        <v>-0.1063964197604861</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.02309520582578983</v>
+        <v>0.1060724505540165</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.149475881541953</v>
+        <v>0.2510065944635116</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2772947046939507</v>
+        <v>0.410481604466284</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.08156720042556742</v>
+        <v>0.05402510353145118</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.05932345991158172</v>
+        <v>0.04614938947111824</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1282732647022158</v>
+        <v>-0.01782089627380401</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.06186904173756602</v>
+        <v>0.210243142053038</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.0462181496664229</v>
+        <v>0.1972178704708796</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.001624056923198225</v>
+        <v>0.1789128700341109</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1455597880445296</v>
+        <v>0.3628363924165541</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1489898395956502</v>
+        <v>0.398775429549417</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.02363164998504175</v>
+        <v>0.3025329851969403</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.06538616261336472</v>
+        <v>0.349673922411732</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.02275175882631686</v>
+        <v>0.2942652156648009</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1345237777783126</v>
+        <v>0.1276301974715608</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.2238061601515184</v>
+        <v>-0.01487113252213135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006932</t>
+          <t>X &gt; -0.006926</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2918</v>
+        <v>2929</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3496030912065038</v>
+        <v>0.3087475508171238</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1853583528839735</v>
+        <v>0.2325047802642501</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2821278440985537</v>
+        <v>0.3351231995806785</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1579748793005322</v>
+        <v>-0.05368212104634296</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2891268798150577</v>
+        <v>-0.1256433829644763</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6819696978104588</v>
+        <v>-0.613433224540195</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5330452575534608</v>
+        <v>-0.4733011087436978</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2460863424658584</v>
+        <v>-0.2158867354113525</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2875071827174054</v>
+        <v>-0.1706214228336194</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.08500579250920737</v>
+        <v>0.003954233330574652</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1063940149863853</v>
+        <v>0.2277617610800888</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2550717040535915</v>
+        <v>-0.1312826530354556</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2306580265670206</v>
+        <v>-0.1382171365656077</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2606414487602535</v>
+        <v>-0.1623942393867566</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1119635086030257</v>
+        <v>0.02635929510638135</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.01023751023750918</v>
+        <v>0.1312786922833951</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.08958262139039164</v>
+        <v>0.08160195277020676</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.07134423192663775</v>
+        <v>0.1051731066498718</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.04050863505074886</v>
+        <v>0.1694487763809036</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.1758786336491767</v>
+        <v>0.06327233497132312</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.1841102577543552</v>
+        <v>0.06161285784068582</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2256861711853873</v>
+        <v>0.006732654590791753</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2939119384840154</v>
+        <v>-0.07063362516693417</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4382842876634285</v>
+        <v>-0.2467204659298758</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005655</t>
+          <t>X &gt; -0.005651</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2813</v>
+        <v>2821</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3414537715237813</v>
+        <v>0.3143651704452282</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1836681236164495</v>
+        <v>0.2093530159671531</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3385694285677587</v>
+        <v>0.3988293966398473</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1265969802555063</v>
+        <v>-0.01745445063615136</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.03760869174084291</v>
+        <v>0.1296714529418779</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4878106472363797</v>
+        <v>-0.4530920174954076</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4102018090028352</v>
+        <v>-0.347786023251345</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1017853613545014</v>
+        <v>-0.1041687330020125</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3081735335474463</v>
+        <v>-0.1677947992977167</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3170169741323292</v>
+        <v>-0.203155453901438</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1642401126524291</v>
+        <v>-0.01655232921034155</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4784253771918472</v>
+        <v>-0.3435283563621994</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5531708278574072</v>
+        <v>-0.4495281016296033</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4697703812934435</v>
+        <v>-0.3592979841875774</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.3975354702139242</v>
+        <v>-0.2433850323007789</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.3142675871561522</v>
+        <v>-0.1559839396358953</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.4626840392268008</v>
+        <v>-0.2744136020744961</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4044775377683507</v>
+        <v>-0.2096181282720835</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3096149393403991</v>
+        <v>-0.08042205494434995</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.4571035471086091</v>
+        <v>-0.1989497397415008</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4810401828768036</v>
+        <v>-0.214475165687908</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4502384372116026</v>
+        <v>-0.1978306071961597</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.5668053173353158</v>
+        <v>-0.32299017040026</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.6070883348671572</v>
+        <v>-0.3933551834299109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004378</t>
+          <t>X &gt; -0.004375</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5474405070276305</v>
+        <v>0.4854590072922136</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3609216775436437</v>
+        <v>0.3873718316031187</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5908047782532009</v>
+        <v>0.6847841598667515</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.02610872767628791</v>
+        <v>0.1662917910659161</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.05023029935578904</v>
+        <v>0.1124631409887513</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6045539575875409</v>
+        <v>-0.5436113830944578</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3016323672006536</v>
+        <v>-0.246194081827916</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2462633820056155</v>
+        <v>-0.1974521205290571</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.278905184523822</v>
+        <v>-0.08555842921944645</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.2891196410464545</v>
+        <v>-0.1204549394219967</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2004511742645718</v>
+        <v>-0.01208444740175452</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4050441075605491</v>
+        <v>-0.2304300833627551</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6383285325924248</v>
+        <v>-0.4719260184140168</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5409554308546518</v>
+        <v>-0.3650193487579116</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5464586597290193</v>
+        <v>-0.3580655240394108</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.4867719511372073</v>
+        <v>-0.2940857109258275</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.5616534679815359</v>
+        <v>-0.3390731292516946</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.5331204865728907</v>
+        <v>-0.3387814696753395</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.5182044552123202</v>
+        <v>-0.2881110412786114</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.6068328612389564</v>
+        <v>-0.3488793903614962</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6069101244975315</v>
+        <v>-0.3371824798596919</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.7571331777623342</v>
+        <v>-0.5019179829347493</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.8545439245588256</v>
+        <v>-0.6082429220495698</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.855999085926392</v>
+        <v>-0.6741731557801458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003101</t>
+          <t>X &gt; -0.003099</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4291489542046847</v>
+        <v>0.3820200536790423</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2909903233735491</v>
+        <v>0.3323455570646487</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6618584155144021</v>
+        <v>0.7652495713426219</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.06687529658287161</v>
+        <v>0.2120938403522885</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.07229700844573017</v>
+        <v>0.09352157152454055</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5931562254155978</v>
+        <v>-0.4952277110174137</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2640431712013438</v>
+        <v>-0.1914086243490232</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1096946474133276</v>
+        <v>-0.06461792176078518</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.304149266521037</v>
+        <v>-0.1499635943568194</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1726213719716014</v>
+        <v>-0.02041557490599644</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.01653263032088859</v>
+        <v>0.1565353390558641</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.0593402327464787</v>
+        <v>0.09905978386295544</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2387350955129293</v>
+        <v>-0.08872821004730724</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3186077852474511</v>
+        <v>-0.1565716773470314</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.284469566571083</v>
+        <v>-0.1072292938321695</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.1783583870197987</v>
+        <v>0.005045109887731769</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2495376986397773</v>
+        <v>-0.03620601943023161</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2127889318510228</v>
+        <v>-0.02760928246656391</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.2887794327246311</v>
+        <v>-0.06572101741932812</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.5123422252815004</v>
+        <v>-0.2616364319053162</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.4794274956560827</v>
+        <v>-0.2142656345348186</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.6341689205760375</v>
+        <v>-0.3844669893104964</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.7147237938928015</v>
+        <v>-0.4728196501827995</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.7905560471160769</v>
+        <v>-0.6117577867889494</v>
       </c>
     </row>
     <row r="20">
@@ -4332,1309 +4332,1309 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2327</v>
+        <v>2321</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5347417516643915</v>
+        <v>0.4813458746291275</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1571384008520482</v>
+        <v>0.1926308197471727</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3037017929345467</v>
+        <v>0.3506079507323108</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2807725691206073</v>
+        <v>-0.1561778097197504</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1454709645800847</v>
+        <v>0.03915446113981602</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7293827228081966</v>
+        <v>-0.6172680972456632</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2165348328227452</v>
+        <v>-0.1709117533140017</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.2806135152631839</v>
+        <v>-0.3045993200102828</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4104325431985885</v>
+        <v>-0.3237583514249991</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2411640650594791</v>
+        <v>-0.1776256924687516</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.03289557710244395</v>
+        <v>0.11917862536923</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1602007214205017</v>
+        <v>-0.08994969727585556</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.08421931932587512</v>
+        <v>-0.02240751940828289</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2799765837766302</v>
+        <v>-0.2025938712842432</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.2269643031273176</v>
+        <v>-0.1299468545910756</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.1643796455117226</v>
+        <v>-0.05836286149668979</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.1012546043149385</v>
+        <v>0.03490120274913977</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.05180244998060601</v>
+        <v>0.05635722845821789</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1967283072011909</v>
+        <v>-0.04762258022277166</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5857863481256089</v>
+        <v>-0.4098166157525398</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.544439120616147</v>
+        <v>-0.3497186893576583</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7062326540063282</v>
+        <v>-0.5286108089976977</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7755482294486526</v>
+        <v>-0.6041268771299073</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.6365115527191989</v>
+        <v>-0.5255880323727453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005469</t>
+          <t>X &gt; -0.0005481</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2084</v>
+        <v>2078</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.043665314866317</v>
+        <v>0.998482258505085</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2308770442411614</v>
+        <v>0.2745639505258737</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2268924120361788</v>
+        <v>0.262699676550163</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.19925472404136</v>
+        <v>-0.09069678612039667</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1819720118243637</v>
+        <v>0.3507622821932799</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7782893355390641</v>
+        <v>-0.6873327924969743</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2118058970584755</v>
+        <v>-0.1917838295862921</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.05980701676374878</v>
+        <v>-0.1142950951746471</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2573255709867084</v>
+        <v>-0.2253719216282022</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1169862864376086</v>
+        <v>0.12580411661326</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3910459285995316</v>
+        <v>0.4256088029327643</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4947057029717996</v>
+        <v>0.5115511323026709</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5187711695764818</v>
+        <v>0.5254470845081727</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2784209554384418</v>
+        <v>0.3055497403076401</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.270844338025114</v>
+        <v>0.3225785890401482</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.5111551126390736</v>
+        <v>0.5770247869247527</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.7412134795324548</v>
+        <v>0.8374550359712245</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8569500769025566</v>
+        <v>0.9252772831941272</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5266120258457647</v>
+        <v>0.64054255629366</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2626277041377421</v>
+        <v>0.4034832510008854</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.3244809341197623</v>
+        <v>0.4891967996044286</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.008711748142523845</v>
+        <v>0.1543588257584148</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.1006906986844456</v>
+        <v>0.04186795491143158</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.0154156277467834</v>
+        <v>0.1007391912568494</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007301</t>
+          <t>X &gt; 0.0007275</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1795</v>
+        <v>1788</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.273089588400346</v>
+        <v>1.235151049667181</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.383065705097728</v>
+        <v>0.5447997695188675</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6663126194204239</v>
+        <v>0.7901056676272873</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3420315594446564</v>
+        <v>0.5310368021523928</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1728152123832274</v>
+        <v>0.4221453287197292</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.194910439387257</v>
+        <v>-1.032032176393294</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2455931599239065</v>
+        <v>-0.1604475219593553</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.02408222821945571</v>
+        <v>-0.02092352092352456</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.03811975480003582</v>
+        <v>0.05144983320503371</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1884093220785203</v>
+        <v>0.1998427824301316</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4624689642404434</v>
+        <v>0.4720777970344656</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2947689777830078</v>
+        <v>0.2510513981187188</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.3931504978230578</v>
+        <v>0.2800046268479335</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6717939978339942</v>
+        <v>0.6207147384537279</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.6025827750267112</v>
+        <v>0.639456609933724</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7304142031768492</v>
+        <v>0.7888516440932349</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.796830832146469</v>
+        <v>0.8297063602599763</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.059491767133757</v>
+        <v>1.064684178004505</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.6410668599609934</v>
+        <v>0.6992870362805093</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5828617675833527</v>
+        <v>0.6681883765669596</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.5417083572774928</v>
+        <v>0.6923053532112746</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.022965459935243</v>
+        <v>1.153499350038608</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.7960474147571333</v>
+        <v>0.9838384329355776</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.054476999973964</v>
+        <v>1.190939500020441</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002007</t>
+          <t>X &gt; 0.002003</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1496</v>
+        <v>1488</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.18926614439615</v>
+        <v>1.360642117786668</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6546225905499981</v>
+        <v>0.9146018598012802</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.548382355642929</v>
+        <v>1.861375403006427</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1025835660469454</v>
+        <v>0.468439515072113</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4330156118207995</v>
+        <v>0.8599927825778622</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5125964832277248</v>
+        <v>-0.3172964266342078</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.01872238230795631</v>
+        <v>0.1551332355827171</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4359109430921961</v>
+        <v>0.5173241997791678</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6772648805032375</v>
+        <v>0.8453865317447935</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.570571722787875</v>
+        <v>0.6497353033700151</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4448978539571229</v>
+        <v>0.5217034734113142</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.8323709688302543</v>
+        <v>0.7788106450240662</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4420536721273649</v>
+        <v>0.3036418500196802</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8205750621697803</v>
+        <v>0.7229645309096711</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8692494416933698</v>
+        <v>0.8154346093382046</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.437574544645926</v>
+        <v>1.350259645236598</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.611339164353595</v>
+        <v>1.487423355629872</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.014992083291943</v>
+        <v>1.796709268332378</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.871072934065069</v>
+        <v>1.650183000305219</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.590004305530421</v>
+        <v>1.369248794031535</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.448527656280959</v>
+        <v>1.378724257479988</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.706906293802348</v>
+        <v>1.612799713729508</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.580311487567826</v>
+        <v>1.628814202703886</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.972393672847218</v>
+        <v>1.97799658308314</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003284</t>
+          <t>X &gt; 0.003279</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.224924698648564</v>
+        <v>1.453175119076647</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.561288839896065</v>
+        <v>1.878972733414749</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.21387381771072</v>
+        <v>1.463909194075647</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3331345633686453</v>
+        <v>0.5356547702464383</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8362702653180207</v>
+        <v>1.183690248954818</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.06736757543023231</v>
+        <v>-0.002785045131062702</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4190730024243763</v>
+        <v>0.4615787864649405</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8120024972686153</v>
+        <v>0.7443997368430573</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.021274914082653</v>
+        <v>1.040254759037659</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.9195001776434779</v>
+        <v>0.8319446576050566</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.361345054704728</v>
+        <v>1.272105784719891</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.837629208303717</v>
+        <v>1.667228280290566</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.553393315944234</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.255133231443949</v>
+        <v>2.034517189356222</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.82424524354056</v>
+        <v>2.665167155450902</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.631143366437485</v>
+        <v>2.437108526203126</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.801768567841954</v>
+        <v>2.55348743330525</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.50703340499259</v>
+        <v>3.147136271454478</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.102213318533167</v>
+        <v>2.739146687385009</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.699337140295633</v>
+        <v>2.330229882358474</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.915004957165323</v>
+        <v>2.744314247121984</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.091896990701464</v>
+        <v>2.890920064857724</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.439665721717631</v>
+        <v>2.425284394212724</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.953555456699917</v>
+        <v>2.908605294583055</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.004561</t>
+          <t>X &gt; 0.004554</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7093140036464405</v>
+        <v>0.9735023041474662</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.307942146220363</v>
+        <v>2.555552457690908</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.836625567651247</v>
+        <v>2.053546527842336</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.5866146201741316</v>
+        <v>0.8159830387115434</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.002703846874972</v>
+        <v>1.185586188934778</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1155561769036169</v>
+        <v>0.1597240960081265</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3341583501661134</v>
+        <v>-0.205250389342865</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.569155446756433</v>
+        <v>0.5650979844528194</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9328767854917572</v>
+        <v>1.015607539298216</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.234074965524002</v>
+        <v>1.187297979562743</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.937780150113433</v>
+        <v>1.889640521048804</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.873853517879184</v>
+        <v>1.720585448297939</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.50257115027118</v>
+        <v>1.250854621169744</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.140783358679592</v>
+        <v>1.862835613500081</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.839141914811655</v>
+        <v>2.537788538581701</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.424813256352543</v>
+        <v>2.088435009426156</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.680868651946241</v>
+        <v>2.266214940668824</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.290466440852818</v>
+        <v>2.739573598222123</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.643358900525783</v>
+        <v>2.156183977840023</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.967205789242463</v>
+        <v>1.462966515095104</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.827032868309871</v>
+        <v>2.585967718244575</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.859061772057196</v>
+        <v>2.578019763519137</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.486287293600732</v>
+        <v>2.346126610961633</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.6262047706903</v>
+        <v>2.576991440493146</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.005838</t>
+          <t>X &gt; 0.00583</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2821200762969838</v>
+        <v>0.7713761007437157</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.659183506192541</v>
+        <v>2.081339137741402</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.36239127599179</v>
+        <v>1.675301330050672</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5067839041952666</v>
+        <v>0.800013699842161</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.597526955185799</v>
+        <v>1.797440001044109</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.7859196748067205</v>
+        <v>0.9642745971411983</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.441931047977711</v>
+        <v>0.7349634477090419</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.7343330126397518</v>
+        <v>0.854371151400855</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.489086956323362</v>
+        <v>1.548070923885525</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.144131337348213</v>
+        <v>1.176347575766606</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.131457741279043</v>
+        <v>2.155796168871646</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.567401633123474</v>
+        <v>1.454886067299931</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.442813032743821</v>
+        <v>1.18865024405001</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.077654270419913</v>
+        <v>1.930515192517888</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>2.36448753693147</v>
+        <v>2.184366997249064</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.244588744588739</v>
+        <v>2.124048851441316</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.396385893325558</v>
+        <v>2.249053030303031</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.862973760932945</v>
+        <v>2.630199702330096</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.650293713285848</v>
+        <v>1.508305329961381</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.408568094682437</v>
+        <v>1.23864257465133</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.43745049814499</v>
+        <v>2.471279589471941</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.933033108164452</v>
+        <v>2.770733867026166</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.92179353493222</v>
+        <v>2.816992649806906</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.417389853137522</v>
+        <v>3.461215755882087</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.007116</t>
+          <t>X &gt; 0.007105</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4636304985083299</v>
+        <v>0.9860239188394999</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.807958177770459</v>
+        <v>2.403703035076475</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.675909277993199</v>
+        <v>2.258066234478797</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9629552585504584</v>
+        <v>1.480821152121592</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.119702099436019</v>
+        <v>2.499163196865133</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.373832464637879</v>
+        <v>1.731882385118297</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.907853930001259</v>
+        <v>2.415543441277457</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.816209649427279</v>
+        <v>2.110622997868838</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.9248610104464703</v>
+        <v>1.129494606259037</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3385124985890826</v>
+        <v>0.5182859945886875</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6125721407510056</v>
+        <v>0.7905210091930215</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1472555731239069</v>
+        <v>0.144253287623755</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3300636555215206</v>
+        <v>0.1384184714668848</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8552534357913473</v>
+        <v>0.6295559442297076</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.9433787949271988</v>
+        <v>0.686773096540584</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.6049298959746778</v>
+        <v>0.4337415228361152</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.6575799231763071</v>
+        <v>0.4401476499690702</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.045276532787959</v>
+        <v>1.719075312434427</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.768630600279451</v>
+        <v>0.5573113622076349</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2092077535310608</v>
+        <v>-0.04976204987227106</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.5994974064605429</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.523651445051442</v>
+        <v>0.4640678433326073</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.2384246649961881</v>
+        <v>0.2572803654458014</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.095428232668439</v>
+        <v>1.1467854908364</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.008393</t>
+          <t>X &gt; 0.008381</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>400</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.359152886568026</v>
+        <v>4.159084763331947</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.524376088218219</v>
+        <v>5.380170592664747</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.336357039187227</v>
+        <v>4.125476490773167</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.87340301974448</v>
+        <v>2.799577959446609</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.28761254719722</v>
+        <v>4.969007594408396</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.474578733294592</v>
+        <v>2.925452202851474</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.702630049404249</v>
+        <v>4.330859188173761</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.424418604651166</v>
+        <v>2.803444857234581</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.21590578656587</v>
+        <v>2.442376211906463</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.692990110529379</v>
+        <v>1.890823494193242</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.467049752691302</v>
+        <v>2.407557286303685</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.938300349243306</v>
+        <v>1.641977776820163</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.315138282387188</v>
+        <v>1.016083214381617</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.844059405940605</v>
+        <v>1.501345485466842</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.93591610836004</v>
+        <v>1.552687436100129</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.280303030303038</v>
+        <v>1.038316686234808</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.896385893325558</v>
+        <v>1.573377354627347</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.291545189504376</v>
+        <v>2.821498078746444</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.507436570428702</v>
+        <v>2.201562689885407</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.944282380396736</v>
+        <v>1.577620837670217</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.901736212430706</v>
+        <v>1.904459312974247</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.075890251021598</v>
+        <v>1.981760280025547</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.600364963503658</v>
+        <v>2.627995229318017</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.524532710280383</v>
+        <v>2.620469701362715</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.00967</t>
+          <t>X &gt; 0.009657</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.371973399388551</v>
+        <v>5.447909549491925</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.319247883090014</v>
+        <v>6.463832366784906</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.842767295597483</v>
+        <v>5.840053091391745</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.206736353077822</v>
+        <v>3.039448999839045</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.114535624120286</v>
+        <v>4.972092752484187</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.69893770765357</v>
+        <v>3.551739292236213</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.491091587865782</v>
+        <v>5.595773999246397</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.289803220035779</v>
+        <v>3.082651663093301</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.331290401950483</v>
+        <v>2.89512315952819</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.199400366939635</v>
+        <v>2.729986490807285</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.152947188588733</v>
+        <v>2.686764092162406</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.874197785140737</v>
+        <v>2.094724724441889</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.712574179823079</v>
+        <v>1.61074743348955</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>2.624343025053278</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>2.257646056417443</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.389277389277396</v>
+        <v>2.188035248738672</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.537411534351193</v>
+        <v>3.030527076761302</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.394109292068478</v>
+        <v>3.727216105808864</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.648462211454337</v>
+        <v>3.189217010873058</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>1.691135373837206</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>1.317012131690106</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.934864609995962</v>
+        <v>1.756922928322524</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.170877784016469</v>
+        <v>3.162029917517131</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.415558351306011</v>
+        <v>3.523695507814331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01095</t>
+          <t>X &gt; 0.01093</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.633346434955136</v>
+        <v>5.895124275905459</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.717924475314994</v>
+        <v>8.460462420121274</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.683131232735612</v>
+        <v>7.205768318229694</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.954048181034814</v>
+        <v>4.605333990907418</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.827935127842373</v>
+        <v>5.132988702213709</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.611675507488144</v>
+        <v>5.289922308211793</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.049404242952626</v>
+        <v>5.699659573087501</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.964741185296326</v>
+        <v>4.591526278273257</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.393325141404581</v>
+        <v>2.711423059443305</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.830086884722931</v>
+        <v>3.120190841332409</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.507372333336463</v>
+        <v>3.794032281639559</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.018945510533634</v>
+        <v>1.911024624357005</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.508686669483964</v>
+        <v>2.000951784014674</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.303736825295438</v>
+        <v>3.760749851095625</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>3.64559352771488</v>
+        <v>3.078595469210569</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>2.223851417399807</v>
+        <v>1.631867359516171</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.106063312680398</v>
+        <v>3.536019076305223</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.001222608859216</v>
+        <v>3.403134971143622</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.410662376880317</v>
+        <v>3.063768982199221</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.58137915459028</v>
+        <v>1.505467873385939</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.2323813737210259</v>
+        <v>-0.03626977173595236</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2466903941396907</v>
+        <v>-0.5179363587318875</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.237461737697203</v>
+        <v>0.9452103216684478</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.564855290925536</v>
+        <v>1.596079457460277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01222</t>
+          <t>X &gt; 0.01221</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>188</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.465535865291436</v>
+        <v>7.190357565083119</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>7.726503747792684</v>
+        <v>8.515131357651505</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.416144273229783</v>
+        <v>9.354678093456251</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.043615785701931</v>
+        <v>6.144474847527611</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.835484887622748</v>
+        <v>7.439597335700526</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.958621286486085</v>
+        <v>7.072970732274527</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.186672602595735</v>
+        <v>6.277888720041808</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.972290945076701</v>
+        <v>7.020088695481363</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.481863233374376</v>
+        <v>6.100897186317297</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.304692238188949</v>
+        <v>6.875526319370209</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.1106667739679</v>
+        <v>7.671321543398633</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.768087583285862</v>
+        <v>5.300498751230997</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.708755303663786</v>
+        <v>4.709166843204308</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.615336001685279</v>
+        <v>6.555173619467531</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6.95719270410472</v>
+        <v>5.873019237582476</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.423920051579628</v>
+        <v>4.340082418705805</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.821917808219183</v>
+        <v>4.759762216404887</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.248991998015015</v>
+        <v>5.150438320667362</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.869138698088271</v>
+        <v>4.651205314966624</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.460239827205235</v>
+        <v>3.615443667572251</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.853863872005164</v>
+        <v>2.316264391903552</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.841847697830104</v>
+        <v>2.773016763565295</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.584407516695144</v>
+        <v>3.016651248843672</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.57240505070591</v>
+        <v>3.91834204178825</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.0135</t>
+          <t>X &gt; 0.01348</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>7.60845240858005</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.765116828958959</v>
+        <v>8.08197003330784</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>12.58267161486949</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>5.515449272176376</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.241316250900923</v>
+        <v>8.837013434235317</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.428282436998302</v>
+        <v>8.993947040233401</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.878555975330165</v>
+        <v>9.63771394886399</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.82256675279932</v>
+        <v>11.49106688675033</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>10.18014687557113</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.09113825867753</v>
+        <v>10.8229443012151</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.84667938232094</v>
+        <v>12.53402823668274</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.345707756650711</v>
+        <v>9.379748440484832</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.963286430535341</v>
+        <v>8.984280783465714</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.22368903557023</v>
+        <v>10.17489564289591</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.30628647873041</v>
+        <v>10.21216572144251</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.678451178451184</v>
+        <v>8.615196358967211</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>9.285274782214444</v>
+        <v>8.511315947242203</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.180434078393262</v>
+        <v>8.378431842080602</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.692621755613892</v>
+        <v>4.995771767068106</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.657245343359691</v>
+        <v>3.500421813419962</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.37395843465292</v>
+        <v>2.657932352767048</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>3.779593954725307</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.05406866720736</v>
+        <v>4.286258330688675</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.718977154724818</v>
+        <v>4.854046343698478</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01478</t>
+          <t>X &gt; 0.01476</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>107</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.172236998717558</v>
+        <v>6.642558457074585</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.641198518124753</v>
+        <v>9.174429399148494</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.1377589083461</v>
+        <v>8.845661223182837</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.686487131894012</v>
+        <v>4.549555320670912</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.023593855608425</v>
+        <v>8.903626810201203</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.341401163201127</v>
+        <v>7.20870856434744</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.17692911482479</v>
+        <v>11.96918210767028</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.83329710932406</v>
+        <v>12.59018759018758</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.00562541273409</v>
+        <v>10.86626464801984</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.03644805445461</v>
+        <v>12.84799093057828</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.31050769661653</v>
+        <v>13.12022594518261</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.16259941466386</v>
+        <v>10.99179213885947</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.974016787060087</v>
+        <v>9.876900021408694</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.68751734986583</v>
+        <v>10.55459188590151</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.89853293078995</v>
+        <v>11.7242893558683</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.62376097422826</v>
+        <v>10.43374152283612</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>10.48984383725079</v>
+        <v>10.32986111111111</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.450423694177275</v>
+        <v>9.271051080023582</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.927997318092245</v>
+        <v>5.781809603465646</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>5.180263688807941</v>
+        <v>5.070470122598707</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.768558642337233</v>
+        <v>3.230959162235621</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.561871559432809</v>
+        <v>5.024955518785013</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.770925711167195</v>
+        <v>6.203169443315723</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.695093457943919</v>
+        <v>6.041030449026259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.01606</t>
+          <t>X &gt; 0.01603</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>10.99329922803145</v>
+        <v>11.51761423574482</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.780473649193823</v>
+        <v>6.452430291607222</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.342454600162831</v>
+        <v>5.197736189715641</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.40998838559814</v>
+        <v>3.400514713798984</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.952246693538676</v>
+        <v>7.944233682133373</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.919700684514105</v>
+        <v>6.896348011023036</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.02580078111156</v>
+        <v>10.92054310722405</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.96710153148044</v>
+        <v>11.82044194092386</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.00858871339514</v>
+        <v>11.94837085060797</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.8942096227245</v>
+        <v>14.76677718671394</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.16826926488643</v>
+        <v>15.03901220131827</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.10903205656038</v>
+        <v>15.9672495239554</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.3273334043384</v>
+        <v>10.03308029807089</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.54527891813572</v>
+        <v>12.19448479085465</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.10664781567711</v>
+        <v>12.71714968607804</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>11.2620103473762</v>
+        <v>10.86881515068083</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.12809321039873</v>
+        <v>10.76493473895582</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>9.803740311455584</v>
+        <v>9.42723135668578</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.141582911892122</v>
+        <v>4.822416475397816</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>2.889404331616241</v>
+        <v>2.627364366239938</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.09216622659369733</v>
+        <v>0.3702342933046907</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>2.27101220224111</v>
+        <v>2.734096161593314</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>3.764999109845114</v>
+        <v>4.197242841993642</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.469654661499888</v>
+        <v>2.815591652582228</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01733</t>
+          <t>X &gt; 0.01731</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>7.228718103959345</v>
+        <v>7.885944700460833</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.546115218653</v>
+        <v>1.925752150471247</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.557371531940852</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.395142150179268</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.856453126907354</v>
+        <v>6.945954852529248</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.594143950685904</v>
+        <v>5.674317029955908</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>10.5935207320089</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.23963599595551</v>
+        <v>13.14574314574314</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>12.28112317787021</v>
+        <v>13.27367205542725</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.85603358879024</v>
+        <v>16.7633348459222</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>14.68081786863333</v>
+        <v>15.60699843195509</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.40206846518534</v>
+        <v>15.33041647748379</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.931080311372703</v>
+        <v>9.929810074318745</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.60855215956379</v>
+        <v>12.5387188700285</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.39968422430207</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>11.54479578392622</v>
+        <v>12.4178685069631</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.41087864694875</v>
+        <v>12.31398809523809</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>9.85676258080872</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.275552512457679</v>
+        <v>5.252709074365129</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>4.038724090852675</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-1.877249294815677</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>2.394730830731739</v>
+        <v>3.396117067516656</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.118480905532628</v>
+        <v>5.068322981366471</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>2.593373289990517</v>
+        <v>3.477612558505569</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1149 +5824,1149 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.0197</t>
+          <t>X &lt; -0.01968</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-7.828341013824883</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.048087679897726</v>
+        <v>-9.502819278100183</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.3846574535664</v>
+        <v>-13.61465623713462</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.64833611069029</v>
+        <v>-12.77848700737142</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-7.339759433185037</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.550783585545986</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.6454330974047906</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.984546121354676</v>
+        <v>-3.236665154077805</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.609037203830439</v>
+        <v>-5.821572996616332</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.912899985650739</v>
+        <v>2.538718870028497</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.991620123524015</v>
+        <v>-5.286292654713705</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.498682476943344</v>
+        <v>-1.867845778751189</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-4.531150338558497</v>
+        <v>-4.828869047619051</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.635991042379679</v>
+        <v>-4.961753152780652</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.86937502377419</v>
+        <v>-4.747290925634879</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-4.233253851487326</v>
+        <v>-4.532704480575894</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-6.225075381772193</v>
+        <v>-5.100148981956629</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-4.851645980862457</v>
+        <v>-3.746740075340483</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.2293451814238878</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>4.042648652309353</v>
+        <v>4.906183987077007</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01843</t>
+          <t>X &lt; -0.01841</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.803637811106391</v>
+        <v>-4.705417425785022</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.626786702479457</v>
+        <v>-8.439696354512144</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.06480575151045</v>
+        <v>-9.694390456403724</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.94055046862761</v>
+        <v>-11.44958335288636</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.787968848151621</v>
+        <v>-8.236769399962441</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1951669685887083</v>
+        <v>1.222489787430987</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.776159461168952</v>
+        <v>2.75298917054711</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3214774281805717</v>
+        <v>1.285278029464074</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8135059781400145</v>
+        <v>-0.9123744562006593</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.939362830647092</v>
+        <v>-4.034007346768838</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.665303188485169</v>
+        <v>-3.761772332164504</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.4146408272272879</v>
+        <v>-0.5499821936125429</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3613323058481015</v>
+        <v>-0.5020836133888906</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.770529994175895</v>
+        <v>1.575263720526827</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.769966244581134</v>
+        <v>-4.920844149730321</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-0.8711680378873936</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-3.133025871380326</v>
+        <v>-3.300629844961243</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.590807751672095</v>
+        <v>-5.759095345471685</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.198445782512472</v>
+        <v>-4.381842420651495</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.011599972544445</v>
+        <v>-4.167255975592511</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.730616728745773</v>
+        <v>-5.897491174647662</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.629992101919576</v>
+        <v>-4.80986299892853</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.826105624731639</v>
+        <v>-1.077856420626887</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>2.627473886750963</v>
+        <v>2.248376678106901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01715</t>
+          <t>X &lt; -0.01713</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.75340168955956</v>
+        <v>-6.566311341592247</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-6.339568886738697</v>
+        <v>-5.969153591631972</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.904374758033292</v>
+        <v>-8.41340764229205</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.610535600950939</v>
+        <v>-4.059336152761759</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.7339245276871083</v>
+        <v>1.653153008791882</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.765714161553767</v>
+        <v>3.635848774336942</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.552923277548359</v>
+        <v>2.405002405002392</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.6598310202107243</v>
+        <v>0.6810794628346528</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.916822973582775</v>
+        <v>-2.892749810162464</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.708183892168513</v>
+        <v>-1.694588869632199</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1177744171118391</v>
+        <v>-0.1193189722516479</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3063570447156181</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.341722957342462</v>
+        <v>1.295332626642249</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-3.989317536499776</v>
+        <v>-4.016451384872433</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.525771736052114</v>
+        <v>-1.603295514200923</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.594268312281926</v>
+        <v>-2.633101851851862</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.502847333860117</v>
+        <v>-5.543763734791227</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.352376513683453</v>
+        <v>-4.403375581719537</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-4.165530703715426</v>
+        <v>-4.188789136660553</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-5.642656310933795</v>
+        <v>-5.682159563967204</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-5.718502272342896</v>
+        <v>-5.757322085922489</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.705709802851494</v>
+        <v>-1.809983896940416</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.02219626168224</v>
+        <v>0.8056548865478987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01587</t>
+          <t>X &lt; -0.01586</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.8716163442012</v>
+        <v>-3.160947338797627</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.744854681012548</v>
+        <v>-4.170212953127447</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.87518142235124</v>
+        <v>-3.134830719141164</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.357366211024747</v>
+        <v>-4.490591696575343</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.385464375879707</v>
+        <v>-2.476073500796815</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.088919818565913</v>
+        <v>2.261012776956996</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.092164933125176</v>
+        <v>2.229289543350234</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.589147286821714</v>
+        <v>2.687727878567564</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.694946926612424</v>
+        <v>-0.2377783262521334</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.243056401098528</v>
+        <v>-1.797188600097428</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.744190557386219</v>
+        <v>-2.288312364119051</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.07783523296424022</v>
+        <v>-0.2748179827124915</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5050607630073358</v>
+        <v>0.9003662357145998</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.384757080359201</v>
+        <v>3.705567288785318</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.924549007919026</v>
+        <v>-1.556739764855472</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.330162085976035</v>
+        <v>-0.9954357460358096</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.239273021403122</v>
+        <v>-1.862674936386775</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.119307523673918</v>
+        <v>-2.758917820174318</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-2.903416142749592</v>
+        <v>-2.544455593028545</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.491764131231179</v>
+        <v>-3.093227926595517</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-4.034310299197209</v>
+        <v>-4.424031206602208</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-4.885350059055924</v>
+        <v>-5.26255250718345</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.510100152775415</v>
+        <v>-1.96548290740126</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.7396489893501368</v>
+        <v>0.1624544341871399</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01459</t>
+          <t>X &lt; -0.01458</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.922898395483251</v>
+        <v>-4.498040740849454</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.257675193833066</v>
+        <v>-4.743947576553325</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.490566037735846</v>
+        <v>-2.813928302648726</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.562494416152944</v>
+        <v>-2.769387826297709</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.180336170751509</v>
+        <v>-4.318831316715517</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7915502989634717</v>
+        <v>0.2967010153972183</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.7755043534829653</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4666263968589632</v>
+        <v>1.107526585233586</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7905877199276361</v>
+        <v>-0.6753725305600113</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.862204694665422</v>
+        <v>-2.745309376097822</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.588145052503499</v>
+        <v>-2.473074361493488</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2694918585488963</v>
+        <v>-0.2018856153278463</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5553980226469264</v>
+        <v>0.5940502926990874</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.282371094252291</v>
+        <v>2.256644256743691</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.9731748007308667</v>
+        <v>-0.9732808257783105</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.3787878787878753</v>
+        <v>-0.4119768069586485</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.5127050157653485</v>
+        <v>-0.5158572186836565</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.916247018287827</v>
+        <v>-1.92262667416373</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-2.34510712217719</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.8641591780448294</v>
+        <v>-0.8566353267997329</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.056055995361504</v>
+        <v>-2.061022503339707</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.131901956770605</v>
+        <v>-2.136185025294992</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.5587259455872555</v>
+        <v>-0.6186651896981417</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.31349374924141</v>
+        <v>1.1300238414901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01332</t>
+          <t>X &lt; -0.0133</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.76850668790005</v>
+        <v>-5.394478579962453</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.103283486249865</v>
+        <v>-5.640385415666323</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.349813173578731</v>
+        <v>-3.720476342954726</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.998937405787423</v>
+        <v>-3.254677483561885</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.866642771951724</v>
+        <v>-4.059336152761759</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.264726079539628</v>
+        <v>-1.256899901261022</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.746294681778558</v>
+        <v>-2.051981913493741</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2013003250812773</v>
+        <v>0.8177008177008105</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.907750127412626</v>
+        <v>-1.699872918117727</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.143031394846972</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.868971752685049</v>
+        <v>-1.694588869632199</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5348179303265823</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.04507677137625166</v>
+        <v>0.08854023304891001</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.884381986585758</v>
+        <v>1.956708288017914</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.1509698718009034</v>
+        <v>0.2163528479318018</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.8675464320625537</v>
+        <v>-0.809644720550132</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.539097977642179</v>
+        <v>-1.442625661375665</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.719207498667664</v>
+        <v>-2.633710824738323</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.040950526345483</v>
+        <v>-2.948349126693081</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.241201490571008</v>
+        <v>-1.146461094332508</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.783747658537038</v>
+        <v>-1.713905595713243</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.859593619946139</v>
+        <v>-1.789068117668528</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.02778431834236272</v>
+        <v>0.04186795491143158</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.027220882323391</v>
+        <v>0.9379300188230317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01204</t>
+          <t>X &lt; -0.01203</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.428081155985161</v>
+        <v>-3.118897914551276</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.613921784122205</v>
+        <v>-4.21226237737379</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.498749343791502</v>
+        <v>-2.924583597909432</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.084043788766152</v>
+        <v>-1.59307667302491</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.56877043152619</v>
+        <v>-1.017570983337009</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2925152837994247</v>
+        <v>0.4159583673419291</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.03417511378192017</v>
+        <v>0.4719401848964466</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1851482183850663</v>
+        <v>0.5925516563814455</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.348471895837562</v>
+        <v>-2.258242838189773</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.69220302251783</v>
+        <v>-2.628762418515493</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.705697028424574</v>
+        <v>-3.633123148592013</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.40933913573523</v>
+        <v>-1.356513613701601</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.103316653235133</v>
+        <v>-2.045873816258755</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6076573322568279</v>
+        <v>-0.5919802181174063</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.124169728549823</v>
+        <v>-2.125198429789684</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.38815190531929</v>
+        <v>-2.414958240757258</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.663699943584305</v>
+        <v>-1.66777482269503</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-2.226190842750249</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-2.41101836519362</v>
+        <v>-2.437260530498094</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.9366189071569195</v>
+        <v>-0.9460783407582696</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.47916507512295</v>
+        <v>-1.513522842139004</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.125826487175829</v>
+        <v>-1.163153449200671</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.4362018733748982</v>
+        <v>0.3570767807585611</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.647923268220289</v>
+        <v>1.471533531149952</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01076</t>
+          <t>X &lt; -0.01075</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.288734437375631</v>
+        <v>-3.192976378460244</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.327736587838118</v>
+        <v>-4.138183913464815</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.530250734664371</v>
+        <v>-4.343926966405348</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.12306341135092</v>
+        <v>-2.302296531180936</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.852458374788604</v>
+        <v>-1.333723215881207</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04766325958797069</v>
+        <v>0.5837737703985653</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.1408044342221828</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.254152823920265</v>
+        <v>-1.220454037355445</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.569808499148415</v>
+        <v>-1.796750479784016</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.057009889470613</v>
+        <v>-3.297027327116027</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.140093104451559</v>
+        <v>-3.376904988568043</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.990271079328124</v>
+        <v>-2.245036238813981</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6134331461842351</v>
+        <v>-0.895139623870385</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2369165487977369</v>
+        <v>-0.08703565713448569</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.206941034497099</v>
+        <v>-2.52975341930123</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.255411255411254</v>
+        <v>-1.616336724425224</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.6750426781030114</v>
+        <v>-1.01599178403756</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.851311953352763</v>
+        <v>-2.205213917368177</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.992563429571305</v>
+        <v>-2.342864366278739</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.091431905317556</v>
+        <v>-1.424052569107076</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.633978073283586</v>
+        <v>-1.99149707048781</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.501170680878047</v>
+        <v>-2.066659592443095</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.1514271511916974</v>
+        <v>-0.7666870789957088</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1311635346531332</v>
+        <v>-0.5767133972288363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.009487</t>
+          <t>X &lt; -0.009477</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.20406550423656</v>
+        <v>-2.267839192699839</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.390609502559883</v>
+        <v>-2.23045990942353</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.101504232489077</v>
+        <v>-2.918581773354774</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.502319523608115</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5203584672955444</v>
+        <v>-0.640532733958338</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.864113617015526</v>
+        <v>2.245745601384471</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.261667950278877</v>
+        <v>1.164949303437474</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1088209370126805</v>
+        <v>0.002886002886000938</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.307417828594481</v>
+        <v>-1.583470801715613</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.663423883639709</v>
+        <v>-2.95095086836352</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.555544999495289</v>
+        <v>-3.821572996616332</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.793478076412669</v>
+        <v>-2.098154951087622</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8758238167381762</v>
+        <v>-1.213047068538394</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5138123141760218</v>
+        <v>-0.8898525585429411</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.629681559278445</v>
+        <v>-3.00057836899942</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.452204258326702</v>
+        <v>-2.153560064465466</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.586121395304176</v>
+        <v>-2.257440476190474</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.274052478134109</v>
+        <v>-2.961753152780652</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.641251476218528</v>
+        <v>-3.318719497063448</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.871315287241757</v>
+        <v>-2.532704480575894</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.122316265703404</v>
+        <v>-2.814434696242344</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.029372906873135</v>
+        <v>-2.889597218197629</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.4120983796048492</v>
+        <v>-1.217391304347828</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3918347630662993</v>
+        <v>-0.5223874414944305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008209</t>
+          <t>X &lt; -0.008202</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.066997234497336</v>
+        <v>-1.769577082720531</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.033876338966252</v>
+        <v>-1.655832142013516</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.615589432832238</v>
+        <v>-2.311636216774936</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7607433217189197</v>
+        <v>-0.6356298645142644</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01683015110918973</v>
+        <v>-0.3025961191720796</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.303010105843612</v>
+        <v>2.140482443489745</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.920689017463211</v>
+        <v>1.345400431257026</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.168276098508656</v>
+        <v>-0.1556922609554263</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7730377023776214</v>
+        <v>-1.463170049835902</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.037353869814602</v>
+        <v>-2.737690444576778</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.991795456153902</v>
+        <v>-3.900862128537042</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3221419111989619</v>
+        <v>-1.306630685879149</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4625029952540842</v>
+        <v>-1.225350554526095</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.05351886540005779</v>
+        <v>-0.5166468169161362</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.341725169281233</v>
+        <v>-1.916504548083495</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.238738738738739</v>
+        <v>-1.594434979024598</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.8812553843157147</v>
+        <v>-1.219846491228068</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.968897070937892</v>
+        <v>-2.309668395432737</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.998705935713808</v>
+        <v>-2.334440618047729</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.074759388645042</v>
+        <v>-1.40215082370645</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.37160531091083</v>
+        <v>-1.730360875326419</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.05711467508678</v>
+        <v>-1.566288947520931</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.1034513832567399</v>
+        <v>-0.3657166631994997</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.768359870774205</v>
+        <v>0.1898476917933394</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006932</t>
+          <t>X &lt; -0.006926</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.257447903945796</v>
+        <v>-1.99223913121137</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.500376387029306</v>
+        <v>-1.167174340513498</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.239039786209595</v>
+        <v>-1.930387198779975</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.135828467060584</v>
+        <v>0.3097892387995742</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9081304754840716</v>
+        <v>0.7294369953863935</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.205616657446285</v>
+        <v>3.149855190425576</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.35263004940424</v>
+        <v>1.963383745707532</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6744186046511587</v>
+        <v>0.4842950048429486</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9159057865658653</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2570098894706234</v>
+        <v>-0.7709117294202699</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.382950247308706</v>
+        <v>-2.064234444757233</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7383003492433033</v>
+        <v>0.007520195683412112</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6151382823871856</v>
+        <v>0.06679637568860386</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7940594059405939</v>
+        <v>0.4056464629834906</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.4722026351442352</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.6696969696969717</v>
+        <v>-0.8893721975378739</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.2036141066744435</v>
+        <v>-0.4061684605349072</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.3084548104956255</v>
+        <v>-0.3433578494538381</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.4925634295712982</v>
+        <v>-0.5202850547933906</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2942823803967229</v>
+        <v>0.2813855389935753</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.3517362124306942</v>
+        <v>0.30102518634083</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.5969323351899405</v>
+        <v>0.4215573806282009</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.9929352446281499</v>
+        <v>0.8608865821492486</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.843949209274342</v>
+        <v>1.48152645283043</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005655</t>
+          <t>X &lt; -0.005651</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.76482753757552</v>
+        <v>-1.619549805033671</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.197846134004003</v>
+        <v>-0.8190311561098156</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.058487477997723</v>
+        <v>-1.827793582104761</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0610232097637109</v>
+        <v>0.08095628685449441</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4689555973019708</v>
+        <v>-0.5886073594523182</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.61931557539986</v>
+        <v>1.757861918024219</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.272234662254327</v>
+        <v>0.9627799057914999</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1591893030918357</v>
+        <v>-0.1498949802665521</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.801714367423962</v>
+        <v>0.3011357064773321</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.8538811996382876</v>
+        <v>0.312838653907427</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1378418318992161</v>
+        <v>-0.5457825511974477</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.607721836846608</v>
+        <v>0.9546952681600089</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.972163075775612</v>
+        <v>1.45531203600811</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.585794943130679</v>
+        <v>1.207077974575</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.258230157946819</v>
+        <v>0.8480253697497204</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8608815426997225</v>
+        <v>0.6015749459199498</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.553410686713981</v>
+        <v>1.305448976844374</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.283280726694457</v>
+        <v>1.172564871682773</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.8380150828253932</v>
+        <v>0.740823544708995</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.520728661388461</v>
+        <v>1.440062655357636</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.63933951821582</v>
+        <v>1.518821708096453</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.499731310624242</v>
+        <v>1.282108297611281</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.041907252060859</v>
+        <v>1.848844559949434</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.234665600645826</v>
+        <v>1.848256454189858</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004378</t>
+          <t>X &lt; -0.004375</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.154360626945483</v>
+        <v>-1.891371774345743</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.607558959143077</v>
+        <v>-1.275306050586956</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.568114505528222</v>
+        <v>-2.460446208752408</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6313459626164359</v>
+        <v>-0.5958420661057815</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3482570180201847</v>
+        <v>-0.3998998240027234</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.683762406763975</v>
+        <v>1.692554112022783</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5820578423197773</v>
+        <v>0.3655572061730368</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.1936154861686745</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5027910324675133</v>
+        <v>-0.07739177435998101</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5495474875785646</v>
+        <v>-0.07557092915378405</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2197857308034799</v>
+        <v>-0.4682295315707279</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9793962396542639</v>
+        <v>0.3190183011920098</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.857662287874156</v>
+        <v>1.198807034805071</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.499409200179279</v>
+        <v>0.9505729733719619</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.527136958840153</v>
+        <v>1.066290931912441</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.298478613293433</v>
+        <v>0.9627013337108252</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.576084110060812</v>
+        <v>1.257757092198574</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.47124340623963</v>
+        <v>1.390830433845494</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.412786364667383</v>
+        <v>1.339335214182746</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.736806385883696</v>
+        <v>1.686900382645987</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.742957062910811</v>
+        <v>1.651370774882274</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.301164976296327</v>
+        <v>2.108123146544017</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.661231538469266</v>
+        <v>2.484736355226644</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.671226925156411</v>
+        <v>2.455576084341438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003101</t>
+          <t>X &lt; -0.003099</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>880</v>
+        <v>908</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.350344320135875</v>
+        <v>-1.192899952154313</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.067346506860083</v>
+        <v>-0.8344854237707011</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.222153599110648</v>
+        <v>-2.140708498126642</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6333234376546173</v>
+        <v>-0.5917702153914632</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2334312238465586</v>
+        <v>-0.2580595743172367</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.252668620935047</v>
+        <v>1.168822524461397</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3204590707765718</v>
+        <v>0.1063291557084156</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1183741881416225</v>
+        <v>-0.2463273388383627</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4385664404553822</v>
+        <v>0.1018658880263672</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.06940094574382982</v>
+        <v>-0.3637891314220525</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3818203038058741</v>
+        <v>-0.8624792269498656</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.256269786503303</v>
+        <v>-0.6985325470599335</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2715369233837848</v>
+        <v>-0.1614422856560722</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5034591794400356</v>
+        <v>0.1409844458623581</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.4115672974880198</v>
+        <v>0.1196230155191458</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.0999519544253431</v>
+        <v>-0.08999807579335339</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3057856668249954</v>
+        <v>0.1365179882525709</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.2009449630038134</v>
+        <v>0.2238982002715773</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.4168363439281393</v>
+        <v>0.4383604274173507</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.056683286398993</v>
+        <v>1.093475506837571</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.9671382509357969</v>
+        <v>0.9665596398180725</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.413758731747215</v>
+        <v>1.331925752224016</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.644349072470732</v>
+        <v>1.575560237502394</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.865441801189469</v>
+        <v>1.743817718983863</v>
       </c>
     </row>
     <row r="20">
@@ -6976,1309 +6976,1309 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1088</v>
+        <v>1119</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.238308582153635</v>
+        <v>-1.102520250737037</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5273480497128205</v>
+        <v>-0.3249456419672256</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9177301542732579</v>
+        <v>-0.7321165545949384</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2370393833808464</v>
+        <v>0.3252242280124165</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.04746479584191121</v>
+        <v>-0.07859673123871858</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.192702594861082</v>
+        <v>1.10849069942369</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1085097212365085</v>
+        <v>0.007309441069686784</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2474113053810925</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5241249646480597</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1696811525769064</v>
+        <v>0.0290057255340983</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4178999270891168</v>
+        <v>-0.5924143090126037</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.003091592148628308</v>
+        <v>-0.1540722241630661</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1564474188043832</v>
+        <v>-0.2859437875477155</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2640869036491225</v>
+        <v>0.1807461903399954</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.1558977765543617</v>
+        <v>0.1241503428606663</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.01701247118295868</v>
+        <v>0.05989582727460174</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.1169046657945145</v>
+        <v>-0.04398458445040632</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2217453696156966</v>
+        <v>0.001862320218194213</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.08580503972293485</v>
+        <v>0.3056900522790755</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.9142640485910505</v>
+        <v>1.145835031743786</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.8300130226965052</v>
+        <v>1.025218054938556</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.176807682214253</v>
+        <v>1.307517552643688</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.323735027782803</v>
+        <v>1.461786533006958</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.028209180868615</v>
+        <v>1.120916528887292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005469</t>
+          <t>X &lt; -0.0005481</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1331</v>
+        <v>1362</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.709197782079805</v>
+        <v>-1.60973103153875</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5183748411498073</v>
+        <v>-0.3578766295079063</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5773334370032472</v>
+        <v>-0.4048054597162718</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.01636653426421475</v>
+        <v>0.1392239366553198</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5756512381977146</v>
+        <v>-0.5344506234870536</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9207010300880327</v>
+        <v>0.9075318385733482</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.04218228821021341</v>
+        <v>0.007440145928313768</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1933931951994623</v>
+        <v>-0.1093888190662398</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1150089255793247</v>
+        <v>0.1335399937984931</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4653868528214034</v>
+        <v>-0.4739212900123562</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8967227023985131</v>
+        <v>-0.9359006660100704</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.057954332404634</v>
+        <v>-1.065639742360965</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.088909693624807</v>
+        <v>-1.07921027390865</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7102884201463553</v>
+        <v>-0.6666513837999091</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.6937690490612525</v>
+        <v>-0.6145913750829024</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.073894870746443</v>
+        <v>-0.9343446249857195</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.432699563945803</v>
+        <v>-1.258489353891335</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.612502786507619</v>
+        <v>-1.317952019992738</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.096761330620772</v>
+        <v>-0.8098040366061383</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6850279644308657</v>
+        <v>-0.3749532743665398</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.7777990199531075</v>
+        <v>-0.5018691413860381</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.2841997714840261</v>
+        <v>-0.06308158991988932</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.1151005019618125</v>
+        <v>0.1071314562982835</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.2964665384048288</v>
+        <v>-0.128428977051378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007301</t>
+          <t>X &lt; 0.0007275</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1620</v>
+        <v>1652</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.472246013859582</v>
+        <v>-1.407930396180355</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5526410266962003</v>
+        <v>-0.5394360908902769</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9182301167760798</v>
+        <v>-0.8590012960492217</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6186410439030112</v>
+        <v>-0.5753889006588508</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4305442194898674</v>
+        <v>-0.4560945748366407</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.077519909765179</v>
+        <v>1.000872260009324</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.03417511378192017</v>
+        <v>-0.06170816703411219</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.209016978170915</v>
+        <v>-0.2117447769621776</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1938548027527318</v>
+        <v>-0.2308596666271399</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4403022727629988</v>
+        <v>-0.4486188593809644</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.745457930160569</v>
+        <v>-0.7468171414612002</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5586246200063911</v>
+        <v>-0.5049346121045772</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6617847945358903</v>
+        <v>-0.5302383518313789</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9699800029263912</v>
+        <v>-0.8390051009158128</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8892070443493267</v>
+        <v>-0.7947672309848954</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.033736378563958</v>
+        <v>-0.8993227763298819</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.106077160861631</v>
+        <v>-0.8821378127522266</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.395646928722229</v>
+        <v>-1.075554605565152</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.9334501290786861</v>
+        <v>-0.618961627814052</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.8697570284702607</v>
+        <v>-0.5254405580577313</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.8217696409272861</v>
+        <v>-0.5480908705764804</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.354442671296525</v>
+        <v>-1.107514893742426</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.105526461542617</v>
+        <v>-0.9244130961153729</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.392133956386289</v>
+        <v>-1.268150153358839</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002007</t>
+          <t>X &lt; 0.002003</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1919</v>
+        <v>1952</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.982096468104146</v>
+        <v>-1.098634874750104</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6181858952528572</v>
+        <v>-0.6555738083381542</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.35679541559314</v>
+        <v>-1.424471294656101</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2837841570910911</v>
+        <v>-0.3577104356514482</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5389523777898617</v>
+        <v>-0.6560859637972811</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1945580293608486</v>
+        <v>0.1416108387504806</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1856402768515792</v>
+        <v>-0.3184886069667314</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5380166285094532</v>
+        <v>-0.5946758629436317</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.7262922435015184</v>
+        <v>-0.7958575969244848</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6399974413378473</v>
+        <v>-0.6937349385133231</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5437182805209488</v>
+        <v>-0.597124977900144</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8446695365303185</v>
+        <v>-0.7934954528797391</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.53551106826216</v>
+        <v>-0.4234925370483822</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8300570181758218</v>
+        <v>-0.6931312470675266</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8644996920557588</v>
+        <v>-0.7093020223952067</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.309613809613808</v>
+        <v>-1.070129151116532</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.443530946591281</v>
+        <v>-1.122780054644814</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.756271858312672</v>
+        <v>-1.306893668003141</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.644330581338451</v>
+        <v>-1.14366094905408</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.427402486997963</v>
+        <v>-0.8778449957983838</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.315485431690014</v>
+        <v>-0.8817649070151674</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.517030102960703</v>
+        <v>-1.110615953560625</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.420468369829685</v>
+        <v>-1.123129009265853</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.726509499203729</v>
+        <v>-1.490186036342202</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003284</t>
+          <t>X &lt; 0.003279</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2228</v>
+        <v>2260</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7022896779911889</v>
+        <v>-0.8137534886739743</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9243989674610731</v>
+        <v>-0.9483750433388991</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7790618556434268</v>
+        <v>-0.7700999124020882</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3530793699122228</v>
+        <v>-0.2808480222930285</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6193901289847616</v>
+        <v>-0.6201827136083153</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1397675406902437</v>
+        <v>-0.08597032274432337</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.395584236310043</v>
+        <v>-0.4151793058173467</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6038306137499134</v>
+        <v>-0.5628661257800402</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.715729602174072</v>
+        <v>-0.6750911954561474</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6587085930915393</v>
+        <v>-0.6067806770877127</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8956514995448401</v>
+        <v>-0.839888014931347</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.148947972904345</v>
+        <v>-1.047292500844364</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9932771160013516</v>
+        <v>-0.8795663078130502</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.367427383132402</v>
+        <v>-1.190737514295151</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.667308253485011</v>
+        <v>-1.474661807684626</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.56553216898044</v>
+        <v>-1.311587877360544</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.654666502554427</v>
+        <v>-1.326972713864301</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.028204026796566</v>
+        <v>-1.592600181857769</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.81231264587224</v>
+        <v>-1.33389016710138</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.599624429639114</v>
+        <v>-1.075055934431774</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.712898480532097</v>
+        <v>-1.28851813492755</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.807517820727284</v>
+        <v>-1.407928444493457</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.462106997016761</v>
+        <v>-1.16429395921508</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.7362392825383</v>
+        <v>-1.503424103947019</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.004561</t>
+          <t>X &lt; 0.004554</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2488</v>
+        <v>2520</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.310173000946925</v>
+        <v>-0.4040558635231548</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9429024433061173</v>
+        <v>-0.9054371973057798</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8028645176989997</v>
+        <v>-0.7563845207040742</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3757982582107857</v>
+        <v>-0.2996614850676309</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5295069094548026</v>
+        <v>-0.4347150904182797</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2002813786158768</v>
+        <v>-0.1371657910205855</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.03017682784486198</v>
+        <v>-0.07921373573941537</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3655813953488334</v>
+        <v>-0.3617786278118871</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5013811282000376</v>
+        <v>-0.488704182196507</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6110531240582873</v>
+        <v>-0.5889404540551624</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.8746602993711647</v>
+        <v>-0.8490346352551299</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8501611892182339</v>
+        <v>-0.7860443812450981</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7079078097971774</v>
+        <v>-0.6090917220205725</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.945635862704151</v>
+        <v>-0.794614463304832</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.202816850741804</v>
+        <v>-1.000578368999413</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.049488469296008</v>
+        <v>-0.7964172073226123</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.143309375319191</v>
+        <v>-0.8209325396825378</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.368438772003245</v>
+        <v>-0.9538166448441388</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.129145860377555</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.8787513274684429</v>
+        <v>-0.4057203535917608</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.197119668741522</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.2092503112274</v>
+        <v>-0.8499146785150842</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.071892971409966</v>
+        <v>-0.7650103519668647</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.124181116086184</v>
+        <v>-0.9271493462563285</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.005838</t>
+          <t>X &lt; 0.00583</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2715</v>
+        <v>2743</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1150889840932692</v>
+        <v>-0.2407399356577642</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5034016895595599</v>
+        <v>-0.5035970846856159</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4593467999352612</v>
+        <v>-0.4317534463886901</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2743658171245755</v>
+        <v>-0.2051903439912053</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.553130226311751</v>
+        <v>-0.4606066092647652</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.345699451185645</v>
+        <v>-0.3198669031593298</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.254986208376792</v>
+        <v>-0.3311545926664152</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3292443990118414</v>
+        <v>-0.3609865741549996</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5233760016349294</v>
+        <v>-0.5036205209919657</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4323764583855692</v>
+        <v>-0.4419280382631499</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6872406763515997</v>
+        <v>-0.6951553501695429</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5415235685850135</v>
+        <v>-0.5139759242856456</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.505962635044007</v>
+        <v>-0.4419100422993267</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6687893458949361</v>
+        <v>-0.596013695983693</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7395611309938559</v>
+        <v>-0.6219522557761437</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.7109749719004199</v>
+        <v>-0.5710383208062808</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.7498301243085379</v>
+        <v>-0.5655494288491951</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8697925539722888</v>
+        <v>-0.6255206648894003</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5587399001595301</v>
+        <v>-0.3016891340615189</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4973321837812748</v>
+        <v>-0.1964719926846428</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.7606994019916726</v>
+        <v>-0.5087214521404704</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.888408608014096</v>
+        <v>-0.6203404086564603</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8867484385582003</v>
+        <v>-0.6319009653029752</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.014601728025333</v>
+        <v>-0.8669528287138419</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.007116</t>
+          <t>X &lt; 0.007105</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2879</v>
+        <v>2908</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1260297460990856</v>
+        <v>-0.2229826487129216</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4078886480796058</v>
+        <v>-0.4164007325922796</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4136429608127656</v>
+        <v>-0.4199399944731681</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3142478943638238</v>
+        <v>-0.2742047189164651</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5272597785446749</v>
+        <v>-0.4622503761009256</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3900225784071694</v>
+        <v>-0.3891532673162459</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4865964699327705</v>
+        <v>-0.582258221547832</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4689319998393415</v>
+        <v>-0.5249258079446761</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3041356785343439</v>
+        <v>-0.3090321312577231</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.193200694862945</v>
+        <v>-0.2274944415085329</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2449142860362272</v>
+        <v>-0.2789905790339091</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1578601488542404</v>
+        <v>-0.1581245246264231</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1883219252252601</v>
+        <v>-0.153645988518754</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2851375480227034</v>
+        <v>-0.2098938098320389</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.2995409553518726</v>
+        <v>-0.1841114796301895</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.2386612925234317</v>
+        <v>-0.1042379972616914</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.2481047511650942</v>
+        <v>-0.07056682714351581</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5056818468907665</v>
+        <v>-0.2722267232267086</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.2692624586975185</v>
+        <v>-0.02337660062013924</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1659326733667115</v>
+        <v>0.122434053517253</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.2368828021425173</v>
+        <v>0.002032193126886739</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2226172116649749</v>
+        <v>-0.004354537906806399</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.1704683698296776</v>
+        <v>0.03295257460678158</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3298438093444958</v>
+        <v>-0.197962210604274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.008393</t>
+          <t>X &lt; 0.008381</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3015</v>
+        <v>3040</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4808734465458571</v>
+        <v>-0.5956719147510725</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6664372143830377</v>
+        <v>-0.6932174812727041</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5388076511948512</v>
+        <v>-0.5543679016169207</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3770088418700155</v>
+        <v>-0.375059559696183</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6944243677665298</v>
+        <v>-0.6652863652693455</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4561004622214</v>
+        <v>-0.4574357695568168</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6159715337092138</v>
+        <v>-0.7094413977248735</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4466635464540829</v>
+        <v>-0.5037481571777676</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4194077447872644</v>
+        <v>-0.4229792906003311</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3481950991107681</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4513782525927184</v>
+        <v>-0.4498816130984054</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3808275001124883</v>
+        <v>-0.3463123145916853</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2952384525764629</v>
+        <v>-0.2589754990822115</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3646182800098217</v>
+        <v>-0.2907075404567792</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.3749304524865167</v>
+        <v>-0.262796414112195</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2900740785292513</v>
+        <v>-0.1620187110820126</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3713176142852959</v>
+        <v>-0.2001096491228154</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5558563331702331</v>
+        <v>-0.3329937542844164</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4528283302335439</v>
+        <v>-0.2172157376649508</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3789206669699539</v>
+        <v>-0.1013135031322818</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.3717893011544575</v>
+        <v>-0.1424422150393312</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3947759737049523</v>
+        <v>-0.1847100001525135</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.465284903870355</v>
+        <v>-0.2700228832951979</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.4551521985090119</v>
+        <v>-0.3334776670583324</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.00967</t>
+          <t>X &lt; 0.009657</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3103</v>
+        <v>3130</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4738605491325458</v>
+        <v>-0.5864919537940096</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5996239117817765</v>
+        <v>-0.6247815765330742</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5800962258575879</v>
+        <v>-0.5903014570546503</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.346897972890801</v>
+        <v>-0.3063266510239728</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5366987916881172</v>
+        <v>-0.5006214864722907</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3958954736903451</v>
+        <v>-0.421557805173947</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5730109762367874</v>
+        <v>-0.689463799383276</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3521924886479724</v>
+        <v>-0.4350150575063054</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3565765739216289</v>
+        <v>-0.3847090790533159</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3412575635161801</v>
+        <v>-0.3977380626801974</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3375073718273072</v>
+        <v>-0.3942770782489831</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.308890661992649</v>
+        <v>-0.3337439235187034</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2895502211452481</v>
+        <v>-0.2816950765610073</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4274632410237516</v>
+        <v>-0.3517102029731873</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3597137116913771</v>
+        <v>-0.2808192009643875</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.3568715116448899</v>
+        <v>-0.243535882323755</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4717813092467864</v>
+        <v>-0.2966919595314224</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5576024463914138</v>
+        <v>-0.3337294193256071</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4835544205622924</v>
+        <v>-0.2470627193363839</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3420871078556047</v>
+        <v>-0.06442515606653387</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.2861259897586166</v>
+        <v>-0.02484090345365786</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3105831789300879</v>
+        <v>-0.1000034254089428</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.4357175107231512</v>
+        <v>-0.2397555216002161</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.4602400902352528</v>
+        <v>-0.3379967523114118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01095</t>
+          <t>X &lt; 0.01093</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3167</v>
+        <v>3194</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4747029128050002</v>
+        <v>-0.4934668027839066</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6673768123775758</v>
+        <v>-0.6294921694789508</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6143957838993472</v>
+        <v>-0.5600396208741714</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4315859981406689</v>
+        <v>-0.3569004967160723</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4987967434493683</v>
+        <v>-0.3971693130248184</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.482642616783906</v>
+        <v>-0.4722350779548776</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5147066340128461</v>
+        <v>-0.5642990043644431</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4295713419401039</v>
+        <v>-0.4775808330532385</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3073500273876206</v>
+        <v>-0.3008756675920949</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3393110526268615</v>
+        <v>-0.361693012334996</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3930131403904582</v>
+        <v>-0.4149384326783903</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2762325227290177</v>
+        <v>-0.2679065232744193</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3113563683365328</v>
+        <v>-0.2718496026688513</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4509516107418108</v>
+        <v>-0.3768878600112231</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3978370402545721</v>
+        <v>-0.2907569404279897</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.288594607492243</v>
+        <v>-0.1485585014770407</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4353721407009061</v>
+        <v>-0.2653025328330187</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4270176847471205</v>
+        <v>-0.2233823587326569</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3815924333544061</v>
+        <v>-0.1653167534198516</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2391770961091026</v>
+        <v>-0.01328895709405487</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1321754594935882</v>
+        <v>0.1074116775902709</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.09451050631510327</v>
+        <v>0.1134422954801835</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2115037233650341</v>
+        <v>0.00013608219364869</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2369923923403974</v>
+        <v>-0.112153968017374</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01222</t>
+          <t>X &lt; 0.01221</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3227</v>
+        <v>3252</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4100778826627405</v>
+        <v>-0.4558296620959297</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5130200336654411</v>
+        <v>-0.471505132142191</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5798991184482389</v>
+        <v>-0.5478148216693555</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4136311656574208</v>
+        <v>-0.3587867932386573</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.5166080319771496</v>
+        <v>-0.4338318234630592</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4664844408194284</v>
+        <v>-0.4741809367238758</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4197497286475453</v>
+        <v>-0.4868746839652047</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4646501588394329</v>
+        <v>-0.5296014178096939</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4364692905470235</v>
+        <v>-0.4456906896707835</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4821873038489031</v>
+        <v>-0.5196212418147681</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5298638275556087</v>
+        <v>-0.5671278709265692</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4513260786665398</v>
+        <v>-0.4276770083005772</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4448987775263333</v>
+        <v>-0.3900847547785418</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5551528276089854</v>
+        <v>-0.4670234698654241</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.5152581808859438</v>
+        <v>-0.3945974867754387</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4279659032363767</v>
+        <v>-0.27567068335226</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4508620967795736</v>
+        <v>-0.2693744881244982</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4755442011544488</v>
+        <v>-0.261292323287563</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3960287761059504</v>
+        <v>-0.2004399271709758</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3146931689687946</v>
+        <v>-0.1087413469353464</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2197808154330829</v>
+        <v>-0.03102455799349713</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2771602290031794</v>
+        <v>-0.08794650259484627</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2630179361245979</v>
+        <v>-0.1027279167056463</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.3204471471723664</v>
+        <v>-0.2159386627209301</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.0135</t>
+          <t>X &lt; 0.01348</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3280</v>
+        <v>3303</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2954035772527419</v>
+        <v>-0.3536977269072281</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3414627973057094</v>
+        <v>-0.3127586616176501</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5514799798978984</v>
+        <v>-0.5278754682346474</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2781121317706692</v>
+        <v>-0.230631370084879</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4151003961189375</v>
+        <v>-0.3690193299148063</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4233897324422173</v>
+        <v>-0.4363875712578817</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4807942757398251</v>
+        <v>-0.5216088641333485</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5598046963197092</v>
+        <v>-0.5986041560355773</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.5010896610820836</v>
+        <v>-0.5140239638731146</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5281695737450605</v>
+        <v>-0.5691366041963164</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6010492451829705</v>
+        <v>-0.6418161210235951</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4979086422512253</v>
+        <v>-0.5089177469998347</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4793010977404322</v>
+        <v>-0.4894445840663408</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5305606548496726</v>
+        <v>-0.5086988285519922</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5323113163891193</v>
+        <v>-0.47835135130412</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4672638796726361</v>
+        <v>-0.3827186363257624</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4919621443988049</v>
+        <v>-0.3479569729947656</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4875175006964767</v>
+        <v>-0.3118762682499963</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3449226380948929</v>
+        <v>-0.1400832512765646</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2618686549260474</v>
+        <v>-0.04648894172876794</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2076911406000619</v>
+        <v>-0.008972765553551199</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2653650810929733</v>
+        <v>-0.09642669734177645</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2774923970571521</v>
+        <v>-0.1072218128224023</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.3047355824025502</v>
+        <v>-0.1909138893124265</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01478</t>
+          <t>X &lt; 0.01476</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3308</v>
+        <v>3333</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2334619438132322</v>
+        <v>-0.2490350738632046</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3419902781481454</v>
+        <v>-0.2703463246969946</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3520629067424821</v>
+        <v>-0.2862935768304169</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2371739033324403</v>
+        <v>-0.1463697213161765</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3758229803050384</v>
+        <v>-0.2860014931244947</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3223244537168313</v>
+        <v>-0.2915678314513457</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4759413791671889</v>
+        <v>-0.5027553418724295</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4964598550359582</v>
+        <v>-0.5221182640537521</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4378709212282956</v>
+        <v>-0.4371137228816906</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5013205457018088</v>
+        <v>-0.528954454735306</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5110441949148381</v>
+        <v>-0.5386347091937296</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4412177230458525</v>
+        <v>-0.4693101117164673</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4322253813669548</v>
+        <v>-0.4304309410224718</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4547651871877889</v>
+        <v>-0.4218693149762132</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4921815702652239</v>
+        <v>-0.4280380688326559</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4528091530504099</v>
+        <v>-0.3580083108298808</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4482596572023425</v>
+        <v>-0.3245264300688788</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4145501635433035</v>
+        <v>-0.2600498231564146</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3014979300240626</v>
+        <v>-0.1178119239652773</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2779398418254928</v>
+        <v>-0.0654211643717133</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1986111146608209</v>
+        <v>-0.003369262874755918</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2564360329663202</v>
+        <v>-0.09071094704749072</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.2963561002618391</v>
+        <v>-0.1292089408205257</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2937865158381214</v>
+        <v>-0.1836107066780812</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.01606</t>
+          <t>X &lt; 0.01603</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3333</v>
+        <v>3358</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3035407963878711</v>
+        <v>-0.3177746571046853</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2051321085030935</v>
+        <v>-0.1336060704732489</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1959923943249962</v>
+        <v>-0.129077280862937</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1767013643891318</v>
+        <v>-0.08336454026198226</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2869697917049407</v>
+        <v>-0.1943633600638393</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2622908578722161</v>
+        <v>-0.2283284726895971</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3608027864166559</v>
+        <v>-0.3845468435690478</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.383210538376602</v>
+        <v>-0.4059912153597409</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3844526363731973</v>
+        <v>-0.3799459754149836</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4531855691837947</v>
+        <v>-0.4769923143100385</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4607745150911242</v>
+        <v>-0.4845657901729226</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4832243144338264</v>
+        <v>-0.5068391727727288</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.363091382684587</v>
+        <v>-0.3577705161121969</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4170084971404719</v>
+        <v>-0.3807940494844217</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4291347593838282</v>
+        <v>-0.3622624365658424</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.38559041477329</v>
+        <v>-0.2885632485028253</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3820572204468959</v>
+        <v>-0.256081549742369</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3493652627268276</v>
+        <v>-0.1930517382273251</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2355232857726222</v>
+        <v>-0.05025684728015989</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1807550783985974</v>
+        <v>0.03311351576873989</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1060575525573171</v>
+        <v>0.09048305782744848</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1639898089484149</v>
+        <v>0.003259924659516855</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2015246585719339</v>
+        <v>-0.03311026832519559</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1695116941600716</v>
+        <v>-0.058505879340089</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01733</t>
+          <t>X &lt; 0.01731</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3346</v>
+        <v>3370</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1828477070799366</v>
+        <v>-0.1975044174710519</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.115766429596512</v>
+        <v>-0.01494865815408986</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1418876890574978</v>
+        <v>-0.07419198301657559</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1254086261259886</v>
+        <v>-0.03091010050246723</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2365330694446897</v>
+        <v>-0.142524682099598</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2112119920324034</v>
+        <v>-0.1757420019213072</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3123119666528567</v>
+        <v>-0.3343969363870656</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3654386231894051</v>
+        <v>-0.3864482305120305</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3665101610687671</v>
+        <v>-0.3600059357101273</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4379622704230073</v>
+        <v>-0.4597316856549725</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.414685882914533</v>
+        <v>-0.436665264679327</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4083345524839146</v>
+        <v>-0.4303337125981415</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2929939785600837</v>
+        <v>-0.3156794258291384</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3475377335111247</v>
+        <v>-0.3395567005547662</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3621464847845175</v>
+        <v>-0.3237086273176004</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3462622648669083</v>
+        <v>-0.2777248280618565</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3432502534087121</v>
+        <v>-0.2457648553943343</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3110801088249744</v>
+        <v>-0.1834863958409159</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1968308124420801</v>
+        <v>-0.04041261875656943</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1713892613943173</v>
+        <v>0.01382782529251614</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.06922526860842027</v>
+        <v>0.1160638002211698</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1570846593726714</v>
+        <v>-0.0007648169097151936</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1934055772791368</v>
+        <v>-0.03613945029857746</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.1618091904966761</v>
+        <v>-0.06202288023965252</v>
       </c>
     </row>
   </sheetData>
